--- a/Översikt YDRE.xlsx
+++ b/Översikt YDRE.xlsx
@@ -601,7 +601,7 @@
         <v>44503</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -729,7 +729,7 @@
         <v>45153</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -848,7 +848,7 @@
         <v>44621</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -957,7 +957,7 @@
         <v>46282</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>45378</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1184,7 +1184,7 @@
         <v>45954</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1301,7 +1301,7 @@
         <v>45709</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1408,7 +1408,7 @@
         <v>45198</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1519,7 +1519,7 @@
         <v>46189</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1626,7 +1626,7 @@
         <v>45883</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1738,7 +1738,7 @@
         <v>44509</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1844,7 +1844,7 @@
         <v>45091</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1955,7 +1955,7 @@
         <v>44789</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2066,7 +2066,7 @@
         <v>45415</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2172,7 +2172,7 @@
         <v>45973</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2283,7 +2283,7 @@
         <v>45348</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2389,7 +2389,7 @@
         <v>45611</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2504,7 +2504,7 @@
         <v>45251</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2614,7 +2614,7 @@
         <v>44874</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2720,7 +2720,7 @@
         <v>44732</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2831,7 +2831,7 @@
         <v>45792</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2937,7 +2937,7 @@
         <v>45614</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3048,7 +3048,7 @@
         <v>45846</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3159,7 +3159,7 @@
         <v>44468</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3269,7 +3269,7 @@
         <v>44515</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3374,7 +3374,7 @@
         <v>44858</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3484,7 +3484,7 @@
         <v>45727</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3589,7 +3589,7 @@
         <v>45922</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3694,7 +3694,7 @@
         <v>45769</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3799,7 +3799,7 @@
         <v>45916</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3904,7 +3904,7 @@
         <v>45611</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4014,7 +4014,7 @@
         <v>45371</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4119,7 +4119,7 @@
         <v>45922</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4224,7 +4224,7 @@
         <v>45561</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4329,7 +4329,7 @@
         <v>45965</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4438,7 +4438,7 @@
         <v>45964</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4548,7 +4548,7 @@
         <v>45754</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4653,7 +4653,7 @@
         <v>46045</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4767,7 +4767,7 @@
         <v>45733</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4872,7 +4872,7 @@
         <v>46069</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4977,7 +4977,7 @@
         <v>46069</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5087,7 +5087,7 @@
         <v>45192</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5192,7 +5192,7 @@
         <v>46202</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5297,7 +5297,7 @@
         <v>45777</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5402,7 +5402,7 @@
         <v>46075</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5511,7 +5511,7 @@
         <v>44508</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5584,7 +5584,7 @@
         <v>44582</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5657,7 +5657,7 @@
         <v>44693</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5730,7 +5730,7 @@
         <v>44827</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5808,7 +5808,7 @@
         <v>44476</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5886,7 +5886,7 @@
         <v>44491</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5964,7 +5964,7 @@
         <v>44585</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6037,7 +6037,7 @@
         <v>44502</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6110,7 +6110,7 @@
         <v>44820</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6183,7 +6183,7 @@
         <v>44827</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6261,7 +6261,7 @@
         <v>44687</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6339,7 +6339,7 @@
         <v>44503</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6417,7 +6417,7 @@
         <v>44868</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6490,7 +6490,7 @@
         <v>44879</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6568,7 +6568,7 @@
         <v>44879</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6641,7 +6641,7 @@
         <v>44879</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6714,7 +6714,7 @@
         <v>44468</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6792,7 +6792,7 @@
         <v>44789</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6870,7 +6870,7 @@
         <v>44474</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6943,7 +6943,7 @@
         <v>44477</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7016,7 +7016,7 @@
         <v>44516</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7089,7 +7089,7 @@
         <v>44816</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7162,7 +7162,7 @@
         <v>44483</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7235,7 +7235,7 @@
         <v>44538</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7308,7 +7308,7 @@
         <v>44728</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7381,7 +7381,7 @@
         <v>44593</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7459,7 +7459,7 @@
         <v>44698</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7532,7 +7532,7 @@
         <v>44650</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7605,7 +7605,7 @@
         <v>44827</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7683,7 +7683,7 @@
         <v>44743</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7756,7 +7756,7 @@
         <v>44538</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7829,7 +7829,7 @@
         <v>44469</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7902,7 +7902,7 @@
         <v>44531</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7975,7 +7975,7 @@
         <v>45432</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8048,7 +8048,7 @@
         <v>45597</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8121,7 +8121,7 @@
         <v>44476</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8199,7 +8199,7 @@
         <v>45110</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8272,7 +8272,7 @@
         <v>45664</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8345,7 +8345,7 @@
         <v>44606</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8418,7 +8418,7 @@
         <v>44538</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8491,7 +8491,7 @@
         <v>45110</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8564,7 +8564,7 @@
         <v>45714</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8637,7 +8637,7 @@
         <v>45596</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8710,7 +8710,7 @@
         <v>45138</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8783,7 +8783,7 @@
         <v>45707</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8856,7 +8856,7 @@
         <v>45355</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8929,7 +8929,7 @@
         <v>45355</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9002,7 +9002,7 @@
         <v>45665</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9075,7 +9075,7 @@
         <v>44796</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9148,7 +9148,7 @@
         <v>45665</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9221,7 +9221,7 @@
         <v>45666</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9294,7 +9294,7 @@
         <v>44903</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9367,7 +9367,7 @@
         <v>44592</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9440,7 +9440,7 @@
         <v>45231</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9513,7 +9513,7 @@
         <v>45701</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9586,7 +9586,7 @@
         <v>45208</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9659,7 +9659,7 @@
         <v>45596</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9732,7 +9732,7 @@
         <v>45335</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9805,7 +9805,7 @@
         <v>45261</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9878,7 +9878,7 @@
         <v>45419</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9951,7 +9951,7 @@
         <v>45475</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10024,7 +10024,7 @@
         <v>45278</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10097,7 +10097,7 @@
         <v>45236</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10170,7 +10170,7 @@
         <v>45000</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10243,7 +10243,7 @@
         <v>45105</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10316,7 +10316,7 @@
         <v>45355</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10389,7 +10389,7 @@
         <v>44504</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10462,7 +10462,7 @@
         <v>45414</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10535,7 +10535,7 @@
         <v>45170</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10608,7 +10608,7 @@
         <v>45170</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10681,7 +10681,7 @@
         <v>44503</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10759,7 +10759,7 @@
         <v>44980</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10832,7 +10832,7 @@
         <v>44831</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10905,7 +10905,7 @@
         <v>44743</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10978,7 +10978,7 @@
         <v>45434</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11051,7 +11051,7 @@
         <v>44749</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11124,7 +11124,7 @@
         <v>45218</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11197,7 +11197,7 @@
         <v>45216</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11270,7 +11270,7 @@
         <v>45216</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11343,7 +11343,7 @@
         <v>45510</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11416,7 +11416,7 @@
         <v>45194</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11489,7 +11489,7 @@
         <v>45666</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11562,7 +11562,7 @@
         <v>45119</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11640,7 +11640,7 @@
         <v>44966</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11713,7 +11713,7 @@
         <v>44480</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11791,7 +11791,7 @@
         <v>44939</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11864,7 +11864,7 @@
         <v>45831</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11937,7 +11937,7 @@
         <v>45917</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12010,7 +12010,7 @@
         <v>44994</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12083,7 +12083,7 @@
         <v>44980</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12156,7 +12156,7 @@
         <v>45616</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12229,7 +12229,7 @@
         <v>45091</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12307,7 +12307,7 @@
         <v>44480</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12380,7 +12380,7 @@
         <v>45889</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12453,7 +12453,7 @@
         <v>44576</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12526,7 +12526,7 @@
         <v>44994</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12599,7 +12599,7 @@
         <v>44994</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12672,7 +12672,7 @@
         <v>44635</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12745,7 +12745,7 @@
         <v>45575</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12818,7 +12818,7 @@
         <v>45891</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12891,7 +12891,7 @@
         <v>45910</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12964,7 +12964,7 @@
         <v>44789</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13042,7 +13042,7 @@
         <v>45965</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13115,7 +13115,7 @@
         <v>45871</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13188,7 +13188,7 @@
         <v>45365</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13261,7 +13261,7 @@
         <v>44908</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13334,7 +13334,7 @@
         <v>45898</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13407,7 +13407,7 @@
         <v>45153</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13480,7 +13480,7 @@
         <v>45831</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13553,7 +13553,7 @@
         <v>45474</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13626,7 +13626,7 @@
         <v>45077</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13699,7 +13699,7 @@
         <v>45793</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13772,7 +13772,7 @@
         <v>45246</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13850,7 +13850,7 @@
         <v>45841</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13923,7 +13923,7 @@
         <v>45909</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14001,7 +14001,7 @@
         <v>45909</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14079,7 +14079,7 @@
         <v>45910</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14152,7 +14152,7 @@
         <v>45701</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14225,7 +14225,7 @@
         <v>45910</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14298,7 +14298,7 @@
         <v>45910</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14371,7 +14371,7 @@
         <v>45916</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14449,7 +14449,7 @@
         <v>45916</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14527,7 +14527,7 @@
         <v>45647</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14600,7 +14600,7 @@
         <v>45916</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14673,7 +14673,7 @@
         <v>45916</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14751,7 +14751,7 @@
         <v>45634</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14824,7 +14824,7 @@
         <v>45922</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14897,7 +14897,7 @@
         <v>45406</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14970,7 +14970,7 @@
         <v>45460</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15043,7 +15043,7 @@
         <v>45924</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15116,7 +15116,7 @@
         <v>45924</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15194,7 +15194,7 @@
         <v>45096</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15267,7 +15267,7 @@
         <v>45273</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15340,7 +15340,7 @@
         <v>44953</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15413,7 +15413,7 @@
         <v>44600</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15486,7 +15486,7 @@
         <v>44894</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15559,7 +15559,7 @@
         <v>44480</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15657,7 +15657,7 @@
         <v>45145</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15730,7 +15730,7 @@
         <v>45931</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15803,7 +15803,7 @@
         <v>45931</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15876,7 +15876,7 @@
         <v>45932</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15949,7 +15949,7 @@
         <v>45666</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16022,7 +16022,7 @@
         <v>46146</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16095,7 +16095,7 @@
         <v>46146</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16168,7 +16168,7 @@
         <v>46146</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16241,7 +16241,7 @@
         <v>46146</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16314,7 +16314,7 @@
         <v>46146</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16387,7 +16387,7 @@
         <v>45938</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16465,7 +16465,7 @@
         <v>45714</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16538,7 +16538,7 @@
         <v>46146</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16611,7 +16611,7 @@
         <v>45943</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16684,7 +16684,7 @@
         <v>45940</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16762,7 +16762,7 @@
         <v>45940</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16840,7 +16840,7 @@
         <v>45054</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16913,7 +16913,7 @@
         <v>44502</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16986,7 +16986,7 @@
         <v>44965</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17059,7 +17059,7 @@
         <v>45954</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17137,7 +17137,7 @@
         <v>45954</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17215,7 +17215,7 @@
         <v>45310</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17288,7 +17288,7 @@
         <v>46153</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17366,7 +17366,7 @@
         <v>45428</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17439,7 +17439,7 @@
         <v>45737</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17512,7 +17512,7 @@
         <v>45965</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17590,7 +17590,7 @@
         <v>45965</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17668,7 +17668,7 @@
         <v>45965</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17746,7 +17746,7 @@
         <v>45965</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17819,7 +17819,7 @@
         <v>45965</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17897,7 +17897,7 @@
         <v>45965</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17970,7 +17970,7 @@
         <v>45194</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18043,7 +18043,7 @@
         <v>45965</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18121,7 +18121,7 @@
         <v>45965</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18194,7 +18194,7 @@
         <v>45964</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18272,7 +18272,7 @@
         <v>45964</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18350,7 +18350,7 @@
         <v>45964</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18428,7 +18428,7 @@
         <v>46154</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18506,7 +18506,7 @@
         <v>45587</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18584,7 +18584,7 @@
         <v>45194</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18657,7 +18657,7 @@
         <v>44916</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18730,7 +18730,7 @@
         <v>44562</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18803,7 +18803,7 @@
         <v>45272</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18881,7 +18881,7 @@
         <v>45414</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18954,7 +18954,7 @@
         <v>44536</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19027,7 +19027,7 @@
         <v>45701</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19100,7 +19100,7 @@
         <v>45090</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19178,7 +19178,7 @@
         <v>44908</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19251,7 +19251,7 @@
         <v>44908</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19324,7 +19324,7 @@
         <v>44624</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19397,7 +19397,7 @@
         <v>45994</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19470,7 +19470,7 @@
         <v>45994</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19543,7 +19543,7 @@
         <v>45994</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19616,7 +19616,7 @@
         <v>45994</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19689,7 +19689,7 @@
         <v>46001</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19767,7 +19767,7 @@
         <v>45302</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19840,7 +19840,7 @@
         <v>46007</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19913,7 +19913,7 @@
         <v>46006</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19986,7 +19986,7 @@
         <v>46007</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20059,7 +20059,7 @@
         <v>46007</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20132,7 +20132,7 @@
         <v>46007</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20205,7 +20205,7 @@
         <v>44994</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20278,7 +20278,7 @@
         <v>46006</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20351,7 +20351,7 @@
         <v>45371</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20424,7 +20424,7 @@
         <v>46038</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20502,7 +20502,7 @@
         <v>46013</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20575,7 +20575,7 @@
         <v>46010</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20648,7 +20648,7 @@
         <v>46010</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20721,7 +20721,7 @@
         <v>46013</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20794,7 +20794,7 @@
         <v>46013</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20867,7 +20867,7 @@
         <v>46010</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20940,7 +20940,7 @@
         <v>46010</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -21013,7 +21013,7 @@
         <v>46021</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21086,7 +21086,7 @@
         <v>45537</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21159,7 +21159,7 @@
         <v>44868</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21237,7 +21237,7 @@
         <v>45110</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21310,7 +21310,7 @@
         <v>45965</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21388,7 +21388,7 @@
         <v>46171</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21466,7 +21466,7 @@
         <v>46036</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21539,7 +21539,7 @@
         <v>45583</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21612,7 +21612,7 @@
         <v>45099</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21685,7 +21685,7 @@
         <v>45595</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21758,7 +21758,7 @@
         <v>46044</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21836,7 +21836,7 @@
         <v>46045</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21914,7 +21914,7 @@
         <v>46045</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21992,7 +21992,7 @@
         <v>44966</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -22065,7 +22065,7 @@
         <v>44572</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -22138,7 +22138,7 @@
         <v>44491</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22216,7 +22216,7 @@
         <v>46055</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22289,7 +22289,7 @@
         <v>44501</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22362,7 +22362,7 @@
         <v>46058</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22435,7 +22435,7 @@
         <v>46062</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22513,7 +22513,7 @@
         <v>46062</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22591,7 +22591,7 @@
         <v>46062</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22669,7 +22669,7 @@
         <v>46177</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22747,7 +22747,7 @@
         <v>45701</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22820,7 +22820,7 @@
         <v>46069</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22898,7 +22898,7 @@
         <v>46069</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22976,7 +22976,7 @@
         <v>45335</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -23049,7 +23049,7 @@
         <v>46069</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -23122,7 +23122,7 @@
         <v>45575</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -23195,7 +23195,7 @@
         <v>46071</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23273,7 +23273,7 @@
         <v>46077</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23351,7 +23351,7 @@
         <v>44874</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23424,7 +23424,7 @@
         <v>46076</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23502,7 +23502,7 @@
         <v>46076</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23580,7 +23580,7 @@
         <v>46183</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23658,7 +23658,7 @@
         <v>44711</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23736,7 +23736,7 @@
         <v>46190</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23809,7 +23809,7 @@
         <v>45649</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23882,7 +23882,7 @@
         <v>46029</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23955,7 +23955,7 @@
         <v>46097</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -24028,7 +24028,7 @@
         <v>46191</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -24101,7 +24101,7 @@
         <v>46099</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -24174,7 +24174,7 @@
         <v>45460</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -24247,7 +24247,7 @@
         <v>45580</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24320,7 +24320,7 @@
         <v>46101</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24393,7 +24393,7 @@
         <v>45170</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24466,7 +24466,7 @@
         <v>45707</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24539,7 +24539,7 @@
         <v>46101</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24612,7 +24612,7 @@
         <v>46106</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24685,7 +24685,7 @@
         <v>45664</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24758,7 +24758,7 @@
         <v>45436</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24831,7 +24831,7 @@
         <v>46202</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24904,7 +24904,7 @@
         <v>46116</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24977,7 +24977,7 @@
         <v>44530</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -25050,7 +25050,7 @@
         <v>46119</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -25123,7 +25123,7 @@
         <v>46119</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -25196,7 +25196,7 @@
         <v>45261</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25269,7 +25269,7 @@
         <v>46202</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25342,7 +25342,7 @@
         <v>46121</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25415,7 +25415,7 @@
         <v>46125</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25488,7 +25488,7 @@
         <v>46125</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25561,7 +25561,7 @@
         <v>46126</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25634,7 +25634,7 @@
         <v>46202</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25707,7 +25707,7 @@
         <v>45649</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25780,7 +25780,7 @@
         <v>46202</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25853,7 +25853,7 @@
         <v>45965</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25926,7 +25926,7 @@
         <v>46202</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -25999,7 +25999,7 @@
         <v>45398</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -26072,7 +26072,7 @@
         <v>44987</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -26145,7 +26145,7 @@
         <v>45762</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -26218,7 +26218,7 @@
         <v>45755</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -26291,7 +26291,7 @@
         <v>45758</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -26364,7 +26364,7 @@
         <v>45104</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -26437,7 +26437,7 @@
         <v>45600</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -26515,7 +26515,7 @@
         <v>45638</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -26588,7 +26588,7 @@
         <v>45414</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26661,7 +26661,7 @@
         <v>45334</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26734,7 +26734,7 @@
         <v>44816</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26807,7 +26807,7 @@
         <v>45016</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -26885,7 +26885,7 @@
         <v>45831</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -26958,7 +26958,7 @@
         <v>45916</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -27031,7 +27031,7 @@
         <v>44655</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -27104,7 +27104,7 @@
         <v>45348</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -27177,7 +27177,7 @@
         <v>45085</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -27250,7 +27250,7 @@
         <v>45414</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -27323,7 +27323,7 @@
         <v>44987</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -27396,7 +27396,7 @@
         <v>44980</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -27469,7 +27469,7 @@
         <v>44908</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -27542,7 +27542,7 @@
         <v>45634</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -27615,7 +27615,7 @@
         <v>45218</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -27688,7 +27688,7 @@
         <v>45414</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -27761,7 +27761,7 @@
         <v>44651</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -27834,7 +27834,7 @@
         <v>44844</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -27907,7 +27907,7 @@
         <v>45257</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -27980,7 +27980,7 @@
         <v>45698</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -28053,7 +28053,7 @@
         <v>45159</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -28126,7 +28126,7 @@
         <v>45558</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -28199,7 +28199,7 @@
         <v>45054</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -28272,7 +28272,7 @@
         <v>46258</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -28345,7 +28345,7 @@
         <v>44994</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -28418,7 +28418,7 @@
         <v>45273</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -28491,7 +28491,7 @@
         <v>45692</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -28564,7 +28564,7 @@
         <v>44670</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -28637,7 +28637,7 @@
         <v>44953</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -28710,7 +28710,7 @@
         <v>44651</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -28783,7 +28783,7 @@
         <v>45671</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -28856,7 +28856,7 @@
         <v>44490</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -28929,7 +28929,7 @@
         <v>45159</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -29002,7 +29002,7 @@
         <v>45831</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -29075,7 +29075,7 @@
         <v>45096</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -29148,7 +29148,7 @@
         <v>45677</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -29221,7 +29221,7 @@
         <v>45736</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -29299,7 +29299,7 @@
         <v>45748</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -29372,7 +29372,7 @@
         <v>45264</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -29445,7 +29445,7 @@
         <v>46269</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -29518,7 +29518,7 @@
         <v>44483</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -29591,7 +29591,7 @@
         <v>46269</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -29664,7 +29664,7 @@
         <v>45492</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -29737,7 +29737,7 @@
         <v>45468</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -29810,7 +29810,7 @@
         <v>46273</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -29883,7 +29883,7 @@
         <v>46273</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -29956,7 +29956,7 @@
         <v>46273</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -30029,7 +30029,7 @@
         <v>46275</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -30102,7 +30102,7 @@
         <v>45544</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -30175,7 +30175,7 @@
         <v>45714</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -30248,7 +30248,7 @@
         <v>45666</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -30321,7 +30321,7 @@
         <v>45719</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -30399,7 +30399,7 @@
         <v>45475</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -30472,7 +30472,7 @@
         <v>46280</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -30545,7 +30545,7 @@
         <v>45365</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -30618,7 +30618,7 @@
         <v>46283</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -30696,7 +30696,7 @@
         <v>46282</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -30769,7 +30769,7 @@
         <v>45796</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -30842,7 +30842,7 @@
         <v>45796</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -30915,7 +30915,7 @@
         <v>46282</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -30988,7 +30988,7 @@
         <v>46282</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -31061,7 +31061,7 @@
         <v>45726</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -31134,7 +31134,7 @@
         <v>46240</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -31207,7 +31207,7 @@
         <v>46283</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -31285,7 +31285,7 @@
         <v>46283</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -31363,7 +31363,7 @@
         <v>46283</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -31441,7 +31441,7 @@
         <v>46282</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -31514,7 +31514,7 @@
         <v>46240</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -31587,7 +31587,7 @@
         <v>46282</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -31660,7 +31660,7 @@
         <v>46282</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -31733,7 +31733,7 @@
         <v>46283</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -31811,7 +31811,7 @@
         <v>45239</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -31884,7 +31884,7 @@
         <v>45821</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -31962,7 +31962,7 @@
         <v>45831</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -32035,7 +32035,7 @@
         <v>45831</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -32108,7 +32108,7 @@
         <v>45831</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -32181,7 +32181,7 @@
         <v>45831</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -32254,7 +32254,7 @@
         <v>45831</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -32327,7 +32327,7 @@
         <v>45831</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -32400,7 +32400,7 @@
         <v>45831</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -32473,7 +32473,7 @@
         <v>45838</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -32551,7 +32551,7 @@
         <v>45790</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -32624,7 +32624,7 @@
         <v>45810</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -32697,7 +32697,7 @@
         <v>45769</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -32770,7 +32770,7 @@
         <v>44585</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -32843,7 +32843,7 @@
         <v>45839</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -32921,7 +32921,7 @@
         <v>45916</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -32999,7 +32999,7 @@
         <v>45964</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -33072,7 +33072,7 @@
         <v>46066</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>

--- a/Översikt YDRE.xlsx
+++ b/Översikt YDRE.xlsx
@@ -601,7 +601,7 @@
         <v>44503</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -729,7 +729,7 @@
         <v>45153</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -848,7 +848,7 @@
         <v>44621</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -957,7 +957,7 @@
         <v>46282</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>45378</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1184,7 +1184,7 @@
         <v>45954</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1301,7 +1301,7 @@
         <v>45198</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1412,7 +1412,7 @@
         <v>45709</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1519,7 +1519,7 @@
         <v>46189</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1626,7 +1626,7 @@
         <v>45883</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1738,7 +1738,7 @@
         <v>44509</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1844,7 +1844,7 @@
         <v>44789</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1955,7 +1955,7 @@
         <v>44874</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2061,7 +2061,7 @@
         <v>45251</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2171,7 +2171,7 @@
         <v>45415</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2277,7 +2277,7 @@
         <v>45973</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2388,7 +2388,7 @@
         <v>45792</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2494,7 +2494,7 @@
         <v>45348</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2600,7 +2600,7 @@
         <v>45611</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2715,7 +2715,7 @@
         <v>45091</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2826,7 +2826,7 @@
         <v>44732</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2937,7 +2937,7 @@
         <v>45614</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3048,7 +3048,7 @@
         <v>45846</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3159,7 +3159,7 @@
         <v>44468</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3269,7 +3269,7 @@
         <v>44515</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3374,7 +3374,7 @@
         <v>45371</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3479,7 +3479,7 @@
         <v>46045</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3593,7 +3593,7 @@
         <v>45916</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3698,7 +3698,7 @@
         <v>45922</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3803,7 +3803,7 @@
         <v>46069</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3908,7 +3908,7 @@
         <v>46069</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4018,7 +4018,7 @@
         <v>45964</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4128,7 +4128,7 @@
         <v>45965</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4237,7 +4237,7 @@
         <v>45192</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4342,7 +4342,7 @@
         <v>45769</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4447,7 +4447,7 @@
         <v>45922</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4552,7 +4552,7 @@
         <v>45727</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4657,7 +4657,7 @@
         <v>45754</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4762,7 +4762,7 @@
         <v>44858</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4872,7 +4872,7 @@
         <v>46202</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4977,7 +4977,7 @@
         <v>45733</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5082,7 +5082,7 @@
         <v>45611</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5192,7 +5192,7 @@
         <v>45561</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5297,7 +5297,7 @@
         <v>45777</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5402,7 +5402,7 @@
         <v>46075</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5511,7 +5511,7 @@
         <v>44508</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5584,7 +5584,7 @@
         <v>44693</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5657,7 +5657,7 @@
         <v>44827</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5735,7 +5735,7 @@
         <v>44582</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5808,7 +5808,7 @@
         <v>44476</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5886,7 +5886,7 @@
         <v>44491</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5964,7 +5964,7 @@
         <v>44585</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6037,7 +6037,7 @@
         <v>44502</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6110,7 +6110,7 @@
         <v>44820</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6183,7 +6183,7 @@
         <v>44827</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6261,7 +6261,7 @@
         <v>44687</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6339,7 +6339,7 @@
         <v>44503</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6417,7 +6417,7 @@
         <v>44868</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6490,7 +6490,7 @@
         <v>44879</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6568,7 +6568,7 @@
         <v>44879</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6641,7 +6641,7 @@
         <v>44879</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6714,7 +6714,7 @@
         <v>44468</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6792,7 +6792,7 @@
         <v>44789</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6870,7 +6870,7 @@
         <v>44474</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6943,7 +6943,7 @@
         <v>44477</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7016,7 +7016,7 @@
         <v>44516</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7089,7 +7089,7 @@
         <v>44816</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7162,7 +7162,7 @@
         <v>44483</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7235,7 +7235,7 @@
         <v>44538</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7308,7 +7308,7 @@
         <v>44728</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7381,7 +7381,7 @@
         <v>44593</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7459,7 +7459,7 @@
         <v>44698</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7532,7 +7532,7 @@
         <v>44650</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7605,7 +7605,7 @@
         <v>44743</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7678,7 +7678,7 @@
         <v>44827</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7756,7 +7756,7 @@
         <v>44538</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7829,7 +7829,7 @@
         <v>44469</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7902,7 +7902,7 @@
         <v>44531</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7975,7 +7975,7 @@
         <v>45748</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8048,7 +8048,7 @@
         <v>45414</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8121,7 +8121,7 @@
         <v>44874</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8194,7 +8194,7 @@
         <v>45371</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8267,7 +8267,7 @@
         <v>45419</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8340,7 +8340,7 @@
         <v>45216</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8413,7 +8413,7 @@
         <v>45216</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8486,7 +8486,7 @@
         <v>44796</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8559,7 +8559,7 @@
         <v>44916</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8632,7 +8632,7 @@
         <v>45796</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8705,7 +8705,7 @@
         <v>46013</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8778,7 +8778,7 @@
         <v>46013</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8851,7 +8851,7 @@
         <v>46013</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8924,7 +8924,7 @@
         <v>45474</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8997,7 +8997,7 @@
         <v>46021</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9070,7 +9070,7 @@
         <v>45796</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9143,7 +9143,7 @@
         <v>45273</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9216,7 +9216,7 @@
         <v>44476</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9294,7 +9294,7 @@
         <v>45726</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9367,7 +9367,7 @@
         <v>45889</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9440,7 +9440,7 @@
         <v>44844</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9513,7 +9513,7 @@
         <v>46036</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9586,7 +9586,7 @@
         <v>45891</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9659,7 +9659,7 @@
         <v>44491</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9737,7 +9737,7 @@
         <v>46044</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9815,7 +9815,7 @@
         <v>45898</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9888,7 +9888,7 @@
         <v>45647</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9961,7 +9961,7 @@
         <v>45649</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10034,7 +10034,7 @@
         <v>46045</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10112,7 +10112,7 @@
         <v>46045</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10190,7 +10190,7 @@
         <v>45475</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10263,7 +10263,7 @@
         <v>45218</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10336,7 +10336,7 @@
         <v>45909</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10414,7 +10414,7 @@
         <v>45909</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10492,7 +10492,7 @@
         <v>45910</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10565,7 +10565,7 @@
         <v>46055</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10638,7 +10638,7 @@
         <v>45355</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10711,7 +10711,7 @@
         <v>45558</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10784,7 +10784,7 @@
         <v>44908</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10857,7 +10857,7 @@
         <v>44908</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10930,7 +10930,7 @@
         <v>46058</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11003,7 +11003,7 @@
         <v>45916</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11076,7 +11076,7 @@
         <v>44624</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11149,7 +11149,7 @@
         <v>45916</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11227,7 +11227,7 @@
         <v>45916</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11305,7 +11305,7 @@
         <v>46062</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11383,7 +11383,7 @@
         <v>45916</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11461,7 +11461,7 @@
         <v>46062</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11539,7 +11539,7 @@
         <v>45510</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11612,7 +11612,7 @@
         <v>44966</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11685,7 +11685,7 @@
         <v>45355</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11758,7 +11758,7 @@
         <v>45922</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11831,7 +11831,7 @@
         <v>45924</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11909,7 +11909,7 @@
         <v>45924</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11982,7 +11982,7 @@
         <v>46069</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12055,7 +12055,7 @@
         <v>46069</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12133,7 +12133,7 @@
         <v>45099</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12206,7 +12206,7 @@
         <v>46071</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12284,7 +12284,7 @@
         <v>46076</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12362,7 +12362,7 @@
         <v>45931</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12435,7 +12435,7 @@
         <v>45931</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12508,7 +12508,7 @@
         <v>45932</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12581,7 +12581,7 @@
         <v>45239</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12654,7 +12654,7 @@
         <v>45940</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12732,7 +12732,7 @@
         <v>45938</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12810,7 +12810,7 @@
         <v>45940</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12888,7 +12888,7 @@
         <v>46029</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12961,7 +12961,7 @@
         <v>44490</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13034,7 +13034,7 @@
         <v>46097</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13107,7 +13107,7 @@
         <v>46099</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13180,7 +13180,7 @@
         <v>45000</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13253,7 +13253,7 @@
         <v>46101</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13326,7 +13326,7 @@
         <v>46101</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13399,7 +13399,7 @@
         <v>44651</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13472,7 +13472,7 @@
         <v>44994</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13545,7 +13545,7 @@
         <v>44994</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13618,7 +13618,7 @@
         <v>44994</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13691,7 +13691,7 @@
         <v>45575</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13764,7 +13764,7 @@
         <v>45600</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13842,7 +13842,7 @@
         <v>46106</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13915,7 +13915,7 @@
         <v>45954</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13993,7 +13993,7 @@
         <v>45954</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14071,7 +14071,7 @@
         <v>46116</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14144,7 +14144,7 @@
         <v>45273</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14217,7 +14217,7 @@
         <v>46119</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14290,7 +14290,7 @@
         <v>46119</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14363,7 +14363,7 @@
         <v>46121</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14436,7 +14436,7 @@
         <v>45964</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14514,7 +14514,7 @@
         <v>45964</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14592,7 +14592,7 @@
         <v>45964</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14670,7 +14670,7 @@
         <v>45965</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14748,7 +14748,7 @@
         <v>45965</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14826,7 +14826,7 @@
         <v>46125</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14899,7 +14899,7 @@
         <v>45965</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14972,7 +14972,7 @@
         <v>46125</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15045,7 +15045,7 @@
         <v>45965</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15118,7 +15118,7 @@
         <v>45965</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15196,7 +15196,7 @@
         <v>45965</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15274,7 +15274,7 @@
         <v>45965</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15352,7 +15352,7 @@
         <v>45965</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15425,7 +15425,7 @@
         <v>45965</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15498,7 +15498,7 @@
         <v>46126</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15571,7 +15571,7 @@
         <v>45666</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15644,7 +15644,7 @@
         <v>45119</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15722,7 +15722,7 @@
         <v>45664</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15795,7 +15795,7 @@
         <v>44966</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15868,7 +15868,7 @@
         <v>45246</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15946,7 +15946,7 @@
         <v>45841</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16019,7 +16019,7 @@
         <v>45965</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16092,7 +16092,7 @@
         <v>45575</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16165,7 +16165,7 @@
         <v>45096</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16238,7 +16238,7 @@
         <v>45871</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16311,7 +16311,7 @@
         <v>45831</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16384,7 +16384,7 @@
         <v>45596</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16457,7 +16457,7 @@
         <v>45016</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16535,7 +16535,7 @@
         <v>45831</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16608,7 +16608,7 @@
         <v>45793</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16681,7 +16681,7 @@
         <v>45917</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16754,7 +16754,7 @@
         <v>45634</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16827,7 +16827,7 @@
         <v>45649</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16900,7 +16900,7 @@
         <v>45994</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16973,7 +16973,7 @@
         <v>45736</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17051,7 +17051,7 @@
         <v>45831</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17124,7 +17124,7 @@
         <v>45994</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17197,7 +17197,7 @@
         <v>45994</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17270,7 +17270,7 @@
         <v>45994</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17343,7 +17343,7 @@
         <v>45666</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17416,7 +17416,7 @@
         <v>44816</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17489,7 +17489,7 @@
         <v>45916</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17562,7 +17562,7 @@
         <v>45170</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17635,7 +17635,7 @@
         <v>45692</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17708,7 +17708,7 @@
         <v>44562</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17781,7 +17781,7 @@
         <v>46001</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17859,7 +17859,7 @@
         <v>46006</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17932,7 +17932,7 @@
         <v>45091</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18010,7 +18010,7 @@
         <v>44502</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18083,7 +18083,7 @@
         <v>46006</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18156,7 +18156,7 @@
         <v>46007</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18229,7 +18229,7 @@
         <v>46007</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18302,7 +18302,7 @@
         <v>45707</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18375,7 +18375,7 @@
         <v>46007</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18448,7 +18448,7 @@
         <v>46007</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18521,7 +18521,7 @@
         <v>46010</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18594,7 +18594,7 @@
         <v>46010</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18667,7 +18667,7 @@
         <v>44894</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18740,7 +18740,7 @@
         <v>45821</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18818,7 +18818,7 @@
         <v>44980</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18891,7 +18891,7 @@
         <v>45616</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18964,7 +18964,7 @@
         <v>45910</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19037,7 +19037,7 @@
         <v>45334</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19110,7 +19110,7 @@
         <v>45701</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19183,7 +19183,7 @@
         <v>46146</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19256,7 +19256,7 @@
         <v>45831</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19329,7 +19329,7 @@
         <v>46146</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19402,7 +19402,7 @@
         <v>46146</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19475,7 +19475,7 @@
         <v>46146</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19548,7 +19548,7 @@
         <v>45831</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19621,7 +19621,7 @@
         <v>44908</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19694,7 +19694,7 @@
         <v>46146</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19767,7 +19767,7 @@
         <v>45831</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19840,7 +19840,7 @@
         <v>44480</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19918,7 +19918,7 @@
         <v>46146</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19991,7 +19991,7 @@
         <v>45831</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20064,7 +20064,7 @@
         <v>45831</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20137,7 +20137,7 @@
         <v>44868</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20215,7 +20215,7 @@
         <v>45264</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20288,7 +20288,7 @@
         <v>45831</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20361,7 +20361,7 @@
         <v>45831</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20434,7 +20434,7 @@
         <v>45153</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20507,7 +20507,7 @@
         <v>45272</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20585,7 +20585,7 @@
         <v>46154</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20663,7 +20663,7 @@
         <v>46153</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20741,7 +20741,7 @@
         <v>45737</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20814,7 +20814,7 @@
         <v>45580</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20887,7 +20887,7 @@
         <v>45701</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20960,7 +20960,7 @@
         <v>45090</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -21038,7 +21038,7 @@
         <v>44994</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21111,7 +21111,7 @@
         <v>45838</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21189,7 +21189,7 @@
         <v>44483</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21262,7 +21262,7 @@
         <v>45790</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21335,7 +21335,7 @@
         <v>45810</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21408,7 +21408,7 @@
         <v>45701</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21481,7 +21481,7 @@
         <v>44572</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21554,7 +21554,7 @@
         <v>46038</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21632,7 +21632,7 @@
         <v>44987</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21705,7 +21705,7 @@
         <v>44831</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21778,7 +21778,7 @@
         <v>45587</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21856,7 +21856,7 @@
         <v>45965</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21934,7 +21934,7 @@
         <v>45769</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -22007,7 +22007,7 @@
         <v>46171</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -22085,7 +22085,7 @@
         <v>44530</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -22158,7 +22158,7 @@
         <v>45335</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22231,7 +22231,7 @@
         <v>46177</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22309,7 +22309,7 @@
         <v>45398</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22382,7 +22382,7 @@
         <v>45110</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22455,7 +22455,7 @@
         <v>45138</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22528,7 +22528,7 @@
         <v>46183</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22606,7 +22606,7 @@
         <v>44504</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22679,7 +22679,7 @@
         <v>45159</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22752,7 +22752,7 @@
         <v>44651</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22825,7 +22825,7 @@
         <v>44503</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22903,7 +22903,7 @@
         <v>45583</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22976,7 +22976,7 @@
         <v>46191</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -23049,7 +23049,7 @@
         <v>46190</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -23122,7 +23122,7 @@
         <v>45436</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -23195,7 +23195,7 @@
         <v>44606</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23268,7 +23268,7 @@
         <v>45170</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23341,7 +23341,7 @@
         <v>45104</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23414,7 +23414,7 @@
         <v>45054</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23487,7 +23487,7 @@
         <v>46202</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23560,7 +23560,7 @@
         <v>46202</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23633,7 +23633,7 @@
         <v>46202</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23706,7 +23706,7 @@
         <v>46202</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23779,7 +23779,7 @@
         <v>46202</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23852,7 +23852,7 @@
         <v>45755</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23925,7 +23925,7 @@
         <v>45105</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23998,7 +23998,7 @@
         <v>45194</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -24071,7 +24071,7 @@
         <v>44655</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -24144,7 +24144,7 @@
         <v>45762</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -24217,7 +24217,7 @@
         <v>44789</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24295,7 +24295,7 @@
         <v>44576</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24368,7 +24368,7 @@
         <v>45758</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24441,7 +24441,7 @@
         <v>45434</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24514,7 +24514,7 @@
         <v>46258</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24587,7 +24587,7 @@
         <v>45701</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24660,7 +24660,7 @@
         <v>45460</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24733,7 +24733,7 @@
         <v>44743</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24806,7 +24806,7 @@
         <v>45831</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24879,7 +24879,7 @@
         <v>45159</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24952,7 +24952,7 @@
         <v>44749</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -25025,7 +25025,7 @@
         <v>45414</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -25098,7 +25098,7 @@
         <v>45714</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -25171,7 +25171,7 @@
         <v>45278</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25244,7 +25244,7 @@
         <v>44711</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25322,7 +25322,7 @@
         <v>46269</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25395,7 +25395,7 @@
         <v>46269</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25468,7 +25468,7 @@
         <v>44670</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25541,7 +25541,7 @@
         <v>45302</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25614,7 +25614,7 @@
         <v>45310</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25687,7 +25687,7 @@
         <v>46273</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25760,7 +25760,7 @@
         <v>45231</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25833,7 +25833,7 @@
         <v>46273</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25906,7 +25906,7 @@
         <v>45261</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -25979,7 +25979,7 @@
         <v>46273</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -26052,7 +26052,7 @@
         <v>45261</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -26125,7 +26125,7 @@
         <v>46275</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -26198,7 +26198,7 @@
         <v>44939</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -26271,7 +26271,7 @@
         <v>45537</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -26344,7 +26344,7 @@
         <v>46280</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -26417,7 +26417,7 @@
         <v>45194</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -26490,7 +26490,7 @@
         <v>44538</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -26563,7 +26563,7 @@
         <v>46282</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26636,7 +26636,7 @@
         <v>44987</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26709,7 +26709,7 @@
         <v>46282</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26782,7 +26782,7 @@
         <v>46282</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -26855,7 +26855,7 @@
         <v>46282</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -26928,7 +26928,7 @@
         <v>46282</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -27001,7 +27001,7 @@
         <v>46282</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -27074,7 +27074,7 @@
         <v>45634</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -27147,7 +27147,7 @@
         <v>45671</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -27220,7 +27220,7 @@
         <v>46240</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -27293,7 +27293,7 @@
         <v>44980</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -27366,7 +27366,7 @@
         <v>45406</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -27439,7 +27439,7 @@
         <v>46283</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -27517,7 +27517,7 @@
         <v>46283</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -27595,7 +27595,7 @@
         <v>44965</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -27668,7 +27668,7 @@
         <v>46286</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -27746,7 +27746,7 @@
         <v>46286</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -27824,7 +27824,7 @@
         <v>46240</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -27897,7 +27897,7 @@
         <v>46283</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -27975,7 +27975,7 @@
         <v>46283</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -28053,7 +28053,7 @@
         <v>46076</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -28131,7 +28131,7 @@
         <v>44908</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -28204,7 +28204,7 @@
         <v>46283</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -28282,7 +28282,7 @@
         <v>45194</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -28355,7 +28355,7 @@
         <v>45335</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -28428,7 +28428,7 @@
         <v>45257</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -28501,7 +28501,7 @@
         <v>44592</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -28574,7 +28574,7 @@
         <v>44953</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -28647,7 +28647,7 @@
         <v>44903</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -28720,7 +28720,7 @@
         <v>45348</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -28793,7 +28793,7 @@
         <v>44600</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -28866,7 +28866,7 @@
         <v>45428</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -28939,7 +28939,7 @@
         <v>46290</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -29012,7 +29012,7 @@
         <v>46290</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -29085,7 +29085,7 @@
         <v>44480</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -29183,7 +29183,7 @@
         <v>44501</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -29256,7 +29256,7 @@
         <v>44536</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -29329,7 +29329,7 @@
         <v>45096</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -29402,7 +29402,7 @@
         <v>44953</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -29475,7 +29475,7 @@
         <v>44980</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -29548,7 +29548,7 @@
         <v>45145</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -29621,7 +29621,7 @@
         <v>45077</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -29694,7 +29694,7 @@
         <v>45665</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -29767,7 +29767,7 @@
         <v>45365</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -29840,7 +29840,7 @@
         <v>45208</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -29913,7 +29913,7 @@
         <v>45595</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -29986,7 +29986,7 @@
         <v>45698</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -30059,7 +30059,7 @@
         <v>45355</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -30132,7 +30132,7 @@
         <v>44480</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -30205,7 +30205,7 @@
         <v>45664</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -30278,7 +30278,7 @@
         <v>45596</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -30351,7 +30351,7 @@
         <v>45085</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -30424,7 +30424,7 @@
         <v>45460</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -30497,7 +30497,7 @@
         <v>45414</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -30570,7 +30570,7 @@
         <v>45666</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -30643,7 +30643,7 @@
         <v>44994</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -30716,7 +30716,7 @@
         <v>44635</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -30789,7 +30789,7 @@
         <v>45665</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -30862,7 +30862,7 @@
         <v>45110</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -30935,7 +30935,7 @@
         <v>45218</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -31008,7 +31008,7 @@
         <v>45236</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -31081,7 +31081,7 @@
         <v>45714</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -31154,7 +31154,7 @@
         <v>45597</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -31227,7 +31227,7 @@
         <v>45054</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -31300,7 +31300,7 @@
         <v>45170</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -31373,7 +31373,7 @@
         <v>45677</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -31446,7 +31446,7 @@
         <v>45707</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -31519,7 +31519,7 @@
         <v>45432</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -31592,7 +31592,7 @@
         <v>45638</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -31665,7 +31665,7 @@
         <v>45414</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -31738,7 +31738,7 @@
         <v>45414</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -31811,7 +31811,7 @@
         <v>45110</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -31884,7 +31884,7 @@
         <v>45468</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -31957,7 +31957,7 @@
         <v>45492</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -32030,7 +32030,7 @@
         <v>45666</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -32103,7 +32103,7 @@
         <v>45475</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -32176,7 +32176,7 @@
         <v>45714</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -32249,7 +32249,7 @@
         <v>45544</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -32322,7 +32322,7 @@
         <v>45719</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -32400,7 +32400,7 @@
         <v>45365</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -32473,7 +32473,7 @@
         <v>44585</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -32546,7 +32546,7 @@
         <v>45839</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -32624,7 +32624,7 @@
         <v>45916</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -32702,7 +32702,7 @@
         <v>45964</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -32775,7 +32775,7 @@
         <v>46066</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -32848,7 +32848,7 @@
         <v>46287</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>

--- a/Översikt YDRE.xlsx
+++ b/Översikt YDRE.xlsx
@@ -601,7 +601,7 @@
         <v>44503</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -729,7 +729,7 @@
         <v>45153</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -848,7 +848,7 @@
         <v>44621</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -957,7 +957,7 @@
         <v>46282</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>45378</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1184,7 +1184,7 @@
         <v>45954</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1301,7 +1301,7 @@
         <v>45198</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1412,7 +1412,7 @@
         <v>45709</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1519,7 +1519,7 @@
         <v>46189</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1626,7 +1626,7 @@
         <v>45883</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1738,7 +1738,7 @@
         <v>44509</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1844,7 +1844,7 @@
         <v>44789</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1955,7 +1955,7 @@
         <v>44874</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2061,7 +2061,7 @@
         <v>45251</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2171,7 +2171,7 @@
         <v>45415</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2277,7 +2277,7 @@
         <v>45973</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2388,7 +2388,7 @@
         <v>45792</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2494,7 +2494,7 @@
         <v>45348</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2600,7 +2600,7 @@
         <v>45611</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2715,7 +2715,7 @@
         <v>45091</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2826,7 +2826,7 @@
         <v>44732</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2937,7 +2937,7 @@
         <v>45614</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3048,7 +3048,7 @@
         <v>45846</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3159,7 +3159,7 @@
         <v>44468</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3269,7 +3269,7 @@
         <v>44515</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3374,7 +3374,7 @@
         <v>45371</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3479,7 +3479,7 @@
         <v>46045</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3593,7 +3593,7 @@
         <v>45916</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3698,7 +3698,7 @@
         <v>45922</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3803,7 +3803,7 @@
         <v>46069</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3908,7 +3908,7 @@
         <v>46069</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4018,7 +4018,7 @@
         <v>45964</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4128,7 +4128,7 @@
         <v>45965</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4237,7 +4237,7 @@
         <v>45192</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4342,7 +4342,7 @@
         <v>45769</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4447,7 +4447,7 @@
         <v>45922</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4552,7 +4552,7 @@
         <v>45727</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4657,7 +4657,7 @@
         <v>45754</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4762,7 +4762,7 @@
         <v>44858</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4872,7 +4872,7 @@
         <v>46202</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4977,7 +4977,7 @@
         <v>45733</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5082,7 +5082,7 @@
         <v>45611</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5192,7 +5192,7 @@
         <v>45561</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5297,7 +5297,7 @@
         <v>45777</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5402,7 +5402,7 @@
         <v>46075</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5511,7 +5511,7 @@
         <v>44508</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5584,7 +5584,7 @@
         <v>44693</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5657,7 +5657,7 @@
         <v>44827</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5735,7 +5735,7 @@
         <v>44582</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5808,7 +5808,7 @@
         <v>44476</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5886,7 +5886,7 @@
         <v>44491</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5964,7 +5964,7 @@
         <v>44585</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6037,7 +6037,7 @@
         <v>44502</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6110,7 +6110,7 @@
         <v>44820</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6183,7 +6183,7 @@
         <v>44827</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6261,7 +6261,7 @@
         <v>44687</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6339,7 +6339,7 @@
         <v>44503</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6417,7 +6417,7 @@
         <v>44868</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6490,7 +6490,7 @@
         <v>44879</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6568,7 +6568,7 @@
         <v>44879</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6641,7 +6641,7 @@
         <v>44879</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6714,7 +6714,7 @@
         <v>44468</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6792,7 +6792,7 @@
         <v>44789</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6870,7 +6870,7 @@
         <v>44474</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6943,7 +6943,7 @@
         <v>44477</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7016,7 +7016,7 @@
         <v>44516</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7089,7 +7089,7 @@
         <v>44816</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7162,7 +7162,7 @@
         <v>44483</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7235,7 +7235,7 @@
         <v>44538</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7308,7 +7308,7 @@
         <v>44728</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7381,7 +7381,7 @@
         <v>44593</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7459,7 +7459,7 @@
         <v>44698</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7532,7 +7532,7 @@
         <v>44650</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7605,7 +7605,7 @@
         <v>44743</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7678,7 +7678,7 @@
         <v>44827</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7756,7 +7756,7 @@
         <v>44538</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7829,7 +7829,7 @@
         <v>44469</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7902,7 +7902,7 @@
         <v>44531</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7975,7 +7975,7 @@
         <v>45748</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8048,7 +8048,7 @@
         <v>45414</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8121,7 +8121,7 @@
         <v>44874</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8194,7 +8194,7 @@
         <v>45371</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8267,7 +8267,7 @@
         <v>45419</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8340,7 +8340,7 @@
         <v>45216</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8413,7 +8413,7 @@
         <v>45216</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8486,7 +8486,7 @@
         <v>44796</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8559,7 +8559,7 @@
         <v>44916</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8632,7 +8632,7 @@
         <v>45796</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8705,7 +8705,7 @@
         <v>46013</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8778,7 +8778,7 @@
         <v>46013</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8851,7 +8851,7 @@
         <v>46013</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8924,7 +8924,7 @@
         <v>45474</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8997,7 +8997,7 @@
         <v>46021</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9070,7 +9070,7 @@
         <v>45796</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9143,7 +9143,7 @@
         <v>45273</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9216,7 +9216,7 @@
         <v>44476</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9294,7 +9294,7 @@
         <v>45726</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9367,7 +9367,7 @@
         <v>45889</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9440,7 +9440,7 @@
         <v>44844</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9513,7 +9513,7 @@
         <v>46036</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9586,7 +9586,7 @@
         <v>45891</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9659,7 +9659,7 @@
         <v>44491</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9737,7 +9737,7 @@
         <v>46044</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9815,7 +9815,7 @@
         <v>45898</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9888,7 +9888,7 @@
         <v>45647</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9961,7 +9961,7 @@
         <v>45649</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10034,7 +10034,7 @@
         <v>46045</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10112,7 +10112,7 @@
         <v>46045</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10190,7 +10190,7 @@
         <v>45475</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10263,7 +10263,7 @@
         <v>45218</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10336,7 +10336,7 @@
         <v>45909</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10414,7 +10414,7 @@
         <v>45909</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10492,7 +10492,7 @@
         <v>45910</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10565,7 +10565,7 @@
         <v>46055</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10638,7 +10638,7 @@
         <v>45355</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10711,7 +10711,7 @@
         <v>45558</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10784,7 +10784,7 @@
         <v>44908</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10857,7 +10857,7 @@
         <v>44908</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10930,7 +10930,7 @@
         <v>46058</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11003,7 +11003,7 @@
         <v>45916</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11076,7 +11076,7 @@
         <v>44624</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11149,7 +11149,7 @@
         <v>45916</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11227,7 +11227,7 @@
         <v>45916</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11305,7 +11305,7 @@
         <v>46062</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11383,7 +11383,7 @@
         <v>45916</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11461,7 +11461,7 @@
         <v>46062</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11539,7 +11539,7 @@
         <v>45510</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11612,7 +11612,7 @@
         <v>44966</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11685,7 +11685,7 @@
         <v>45355</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11758,7 +11758,7 @@
         <v>45922</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11831,7 +11831,7 @@
         <v>45924</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11909,7 +11909,7 @@
         <v>45924</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11982,7 +11982,7 @@
         <v>46069</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12055,7 +12055,7 @@
         <v>46069</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12133,7 +12133,7 @@
         <v>45099</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12206,7 +12206,7 @@
         <v>46071</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12284,7 +12284,7 @@
         <v>46076</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12362,7 +12362,7 @@
         <v>45931</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12435,7 +12435,7 @@
         <v>45931</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12508,7 +12508,7 @@
         <v>45932</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12581,7 +12581,7 @@
         <v>45239</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12654,7 +12654,7 @@
         <v>45940</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12732,7 +12732,7 @@
         <v>45938</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12810,7 +12810,7 @@
         <v>45940</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12888,7 +12888,7 @@
         <v>46029</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12961,7 +12961,7 @@
         <v>44490</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13034,7 +13034,7 @@
         <v>46097</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13107,7 +13107,7 @@
         <v>46099</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13180,7 +13180,7 @@
         <v>45000</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13253,7 +13253,7 @@
         <v>46101</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13326,7 +13326,7 @@
         <v>46101</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13399,7 +13399,7 @@
         <v>44651</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13472,7 +13472,7 @@
         <v>44994</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13545,7 +13545,7 @@
         <v>44994</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13618,7 +13618,7 @@
         <v>44994</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13691,7 +13691,7 @@
         <v>45575</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13764,7 +13764,7 @@
         <v>45600</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13842,7 +13842,7 @@
         <v>46106</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13915,7 +13915,7 @@
         <v>45954</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13993,7 +13993,7 @@
         <v>45954</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14071,7 +14071,7 @@
         <v>46116</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14144,7 +14144,7 @@
         <v>45273</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14217,7 +14217,7 @@
         <v>46119</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14290,7 +14290,7 @@
         <v>46119</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14363,7 +14363,7 @@
         <v>46121</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14436,7 +14436,7 @@
         <v>45964</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14514,7 +14514,7 @@
         <v>45964</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14592,7 +14592,7 @@
         <v>45964</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14670,7 +14670,7 @@
         <v>45965</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14748,7 +14748,7 @@
         <v>45965</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14826,7 +14826,7 @@
         <v>46125</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14899,7 +14899,7 @@
         <v>45965</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14972,7 +14972,7 @@
         <v>46125</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15045,7 +15045,7 @@
         <v>45965</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15118,7 +15118,7 @@
         <v>45965</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15196,7 +15196,7 @@
         <v>45965</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15274,7 +15274,7 @@
         <v>45965</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15352,7 +15352,7 @@
         <v>45965</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15425,7 +15425,7 @@
         <v>45965</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15498,7 +15498,7 @@
         <v>46126</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15571,7 +15571,7 @@
         <v>45666</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15644,7 +15644,7 @@
         <v>45119</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15722,7 +15722,7 @@
         <v>45664</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15795,7 +15795,7 @@
         <v>44966</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15868,7 +15868,7 @@
         <v>45246</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15946,7 +15946,7 @@
         <v>45841</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16019,7 +16019,7 @@
         <v>45965</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16092,7 +16092,7 @@
         <v>45575</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16165,7 +16165,7 @@
         <v>45096</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16238,7 +16238,7 @@
         <v>45871</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16311,7 +16311,7 @@
         <v>45831</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16384,7 +16384,7 @@
         <v>45596</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16457,7 +16457,7 @@
         <v>45016</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16535,7 +16535,7 @@
         <v>45831</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16608,7 +16608,7 @@
         <v>45793</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16681,7 +16681,7 @@
         <v>45917</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16754,7 +16754,7 @@
         <v>45634</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16827,7 +16827,7 @@
         <v>45649</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16900,7 +16900,7 @@
         <v>45994</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16973,7 +16973,7 @@
         <v>45736</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17051,7 +17051,7 @@
         <v>45831</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17124,7 +17124,7 @@
         <v>45994</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17197,7 +17197,7 @@
         <v>45994</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17270,7 +17270,7 @@
         <v>45994</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17343,7 +17343,7 @@
         <v>45666</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17416,7 +17416,7 @@
         <v>44816</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17489,7 +17489,7 @@
         <v>45916</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17562,7 +17562,7 @@
         <v>45170</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17635,7 +17635,7 @@
         <v>45692</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17708,7 +17708,7 @@
         <v>44562</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17781,7 +17781,7 @@
         <v>46001</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17859,7 +17859,7 @@
         <v>46006</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17932,7 +17932,7 @@
         <v>45091</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18010,7 +18010,7 @@
         <v>44502</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18083,7 +18083,7 @@
         <v>46006</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18156,7 +18156,7 @@
         <v>46007</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18229,7 +18229,7 @@
         <v>46007</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18302,7 +18302,7 @@
         <v>45707</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18375,7 +18375,7 @@
         <v>46007</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18448,7 +18448,7 @@
         <v>46007</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18521,7 +18521,7 @@
         <v>46010</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18594,7 +18594,7 @@
         <v>46010</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18667,7 +18667,7 @@
         <v>44894</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18740,7 +18740,7 @@
         <v>45821</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18818,7 +18818,7 @@
         <v>44980</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18891,7 +18891,7 @@
         <v>45616</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18964,7 +18964,7 @@
         <v>45910</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19037,7 +19037,7 @@
         <v>45334</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19110,7 +19110,7 @@
         <v>45701</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19183,7 +19183,7 @@
         <v>46146</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19256,7 +19256,7 @@
         <v>45831</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19329,7 +19329,7 @@
         <v>46146</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19402,7 +19402,7 @@
         <v>46146</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19475,7 +19475,7 @@
         <v>46146</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19548,7 +19548,7 @@
         <v>45831</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19621,7 +19621,7 @@
         <v>44908</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19694,7 +19694,7 @@
         <v>46146</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19767,7 +19767,7 @@
         <v>45831</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19840,7 +19840,7 @@
         <v>44480</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19918,7 +19918,7 @@
         <v>46146</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19991,7 +19991,7 @@
         <v>45831</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20064,7 +20064,7 @@
         <v>45831</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20137,7 +20137,7 @@
         <v>44868</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20215,7 +20215,7 @@
         <v>45264</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20288,7 +20288,7 @@
         <v>45831</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20361,7 +20361,7 @@
         <v>45831</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20434,7 +20434,7 @@
         <v>45153</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20507,7 +20507,7 @@
         <v>45272</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20585,7 +20585,7 @@
         <v>46154</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20663,7 +20663,7 @@
         <v>46153</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20741,7 +20741,7 @@
         <v>45737</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20814,7 +20814,7 @@
         <v>45580</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20887,7 +20887,7 @@
         <v>45701</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20960,7 +20960,7 @@
         <v>45090</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -21038,7 +21038,7 @@
         <v>44994</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21111,7 +21111,7 @@
         <v>45838</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21189,7 +21189,7 @@
         <v>44483</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21262,7 +21262,7 @@
         <v>45790</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21335,7 +21335,7 @@
         <v>45810</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21408,7 +21408,7 @@
         <v>45701</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21481,7 +21481,7 @@
         <v>44572</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21554,7 +21554,7 @@
         <v>46038</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21632,7 +21632,7 @@
         <v>44987</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21705,7 +21705,7 @@
         <v>44831</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21778,7 +21778,7 @@
         <v>45587</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21856,7 +21856,7 @@
         <v>45965</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21934,7 +21934,7 @@
         <v>45769</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -22007,7 +22007,7 @@
         <v>46171</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -22085,7 +22085,7 @@
         <v>44530</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -22158,7 +22158,7 @@
         <v>45335</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22231,7 +22231,7 @@
         <v>46177</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22309,7 +22309,7 @@
         <v>45398</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22382,7 +22382,7 @@
         <v>45110</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22455,7 +22455,7 @@
         <v>45138</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22528,7 +22528,7 @@
         <v>46183</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22606,7 +22606,7 @@
         <v>44504</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22679,7 +22679,7 @@
         <v>45159</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22752,7 +22752,7 @@
         <v>44651</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22825,7 +22825,7 @@
         <v>44503</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22903,7 +22903,7 @@
         <v>45583</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22976,7 +22976,7 @@
         <v>46191</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -23049,7 +23049,7 @@
         <v>46190</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -23122,7 +23122,7 @@
         <v>45436</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -23195,7 +23195,7 @@
         <v>44606</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23268,7 +23268,7 @@
         <v>45170</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23341,7 +23341,7 @@
         <v>45104</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23414,7 +23414,7 @@
         <v>45054</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23487,7 +23487,7 @@
         <v>46202</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23560,7 +23560,7 @@
         <v>46202</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23633,7 +23633,7 @@
         <v>46202</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23706,7 +23706,7 @@
         <v>46202</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23779,7 +23779,7 @@
         <v>46202</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23852,7 +23852,7 @@
         <v>45755</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23925,7 +23925,7 @@
         <v>45105</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23998,7 +23998,7 @@
         <v>45194</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -24071,7 +24071,7 @@
         <v>44655</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -24144,7 +24144,7 @@
         <v>45762</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -24217,7 +24217,7 @@
         <v>44789</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24295,7 +24295,7 @@
         <v>44576</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24368,7 +24368,7 @@
         <v>45758</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24441,7 +24441,7 @@
         <v>45434</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24514,7 +24514,7 @@
         <v>46258</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24587,7 +24587,7 @@
         <v>45701</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24660,7 +24660,7 @@
         <v>45460</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24733,7 +24733,7 @@
         <v>44743</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24806,7 +24806,7 @@
         <v>45831</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24879,7 +24879,7 @@
         <v>45159</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24952,7 +24952,7 @@
         <v>44749</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -25025,7 +25025,7 @@
         <v>45414</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -25098,7 +25098,7 @@
         <v>45714</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -25171,7 +25171,7 @@
         <v>45278</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25244,7 +25244,7 @@
         <v>44711</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25322,7 +25322,7 @@
         <v>46269</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25395,7 +25395,7 @@
         <v>46269</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25468,7 +25468,7 @@
         <v>44670</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25541,7 +25541,7 @@
         <v>45302</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25614,7 +25614,7 @@
         <v>45310</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25687,7 +25687,7 @@
         <v>46273</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25760,7 +25760,7 @@
         <v>45231</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25833,7 +25833,7 @@
         <v>46273</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25906,7 +25906,7 @@
         <v>45261</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -25979,7 +25979,7 @@
         <v>46273</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -26052,7 +26052,7 @@
         <v>45261</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -26125,7 +26125,7 @@
         <v>46275</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -26198,7 +26198,7 @@
         <v>44939</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -26271,7 +26271,7 @@
         <v>45537</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -26344,7 +26344,7 @@
         <v>46280</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -26417,7 +26417,7 @@
         <v>45194</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -26490,7 +26490,7 @@
         <v>44538</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -26563,7 +26563,7 @@
         <v>46282</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26636,7 +26636,7 @@
         <v>44987</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26709,7 +26709,7 @@
         <v>46282</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26782,7 +26782,7 @@
         <v>46282</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -26855,7 +26855,7 @@
         <v>46282</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -26928,7 +26928,7 @@
         <v>46282</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -27001,7 +27001,7 @@
         <v>46282</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -27074,7 +27074,7 @@
         <v>45634</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -27147,7 +27147,7 @@
         <v>45671</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -27220,7 +27220,7 @@
         <v>46240</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -27293,7 +27293,7 @@
         <v>44980</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -27366,7 +27366,7 @@
         <v>45406</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -27439,7 +27439,7 @@
         <v>46283</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -27517,7 +27517,7 @@
         <v>46283</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -27595,7 +27595,7 @@
         <v>44965</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -27668,7 +27668,7 @@
         <v>46286</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -27746,7 +27746,7 @@
         <v>46286</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -27824,7 +27824,7 @@
         <v>46240</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -27897,7 +27897,7 @@
         <v>46283</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -27975,7 +27975,7 @@
         <v>46283</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -28053,7 +28053,7 @@
         <v>46076</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -28131,7 +28131,7 @@
         <v>44908</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -28204,7 +28204,7 @@
         <v>46283</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -28282,7 +28282,7 @@
         <v>45194</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -28355,7 +28355,7 @@
         <v>45335</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -28428,7 +28428,7 @@
         <v>45257</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -28501,7 +28501,7 @@
         <v>44592</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -28574,7 +28574,7 @@
         <v>44953</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -28647,7 +28647,7 @@
         <v>44903</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -28720,7 +28720,7 @@
         <v>45348</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -28793,7 +28793,7 @@
         <v>44600</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -28866,7 +28866,7 @@
         <v>45428</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -28939,7 +28939,7 @@
         <v>46290</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -29012,7 +29012,7 @@
         <v>46290</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -29085,7 +29085,7 @@
         <v>44480</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -29183,7 +29183,7 @@
         <v>44501</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -29256,7 +29256,7 @@
         <v>44536</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -29329,7 +29329,7 @@
         <v>45096</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -29402,7 +29402,7 @@
         <v>44953</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -29475,7 +29475,7 @@
         <v>44980</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -29548,7 +29548,7 @@
         <v>45145</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -29621,7 +29621,7 @@
         <v>45077</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -29694,7 +29694,7 @@
         <v>45665</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -29767,7 +29767,7 @@
         <v>45365</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -29840,7 +29840,7 @@
         <v>45208</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -29913,7 +29913,7 @@
         <v>45595</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -29986,7 +29986,7 @@
         <v>45698</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -30059,7 +30059,7 @@
         <v>45355</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -30132,7 +30132,7 @@
         <v>44480</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -30205,7 +30205,7 @@
         <v>45664</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -30278,7 +30278,7 @@
         <v>45596</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -30351,7 +30351,7 @@
         <v>45085</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -30424,7 +30424,7 @@
         <v>45460</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -30497,7 +30497,7 @@
         <v>45414</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -30570,7 +30570,7 @@
         <v>45666</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -30643,7 +30643,7 @@
         <v>44994</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -30716,7 +30716,7 @@
         <v>44635</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -30789,7 +30789,7 @@
         <v>45665</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -30862,7 +30862,7 @@
         <v>45110</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -30935,7 +30935,7 @@
         <v>45218</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -31008,7 +31008,7 @@
         <v>45236</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -31081,7 +31081,7 @@
         <v>45714</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -31154,7 +31154,7 @@
         <v>45597</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -31227,7 +31227,7 @@
         <v>45054</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -31300,7 +31300,7 @@
         <v>45170</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -31373,7 +31373,7 @@
         <v>45677</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -31446,7 +31446,7 @@
         <v>45707</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -31519,7 +31519,7 @@
         <v>45432</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -31592,7 +31592,7 @@
         <v>45638</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -31665,7 +31665,7 @@
         <v>45414</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -31738,7 +31738,7 @@
         <v>45414</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -31811,7 +31811,7 @@
         <v>45110</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -31884,7 +31884,7 @@
         <v>45468</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -31957,7 +31957,7 @@
         <v>45492</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -32030,7 +32030,7 @@
         <v>45666</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -32103,7 +32103,7 @@
         <v>45475</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -32176,7 +32176,7 @@
         <v>45714</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -32249,7 +32249,7 @@
         <v>45544</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -32322,7 +32322,7 @@
         <v>45719</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -32400,7 +32400,7 @@
         <v>45365</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -32473,7 +32473,7 @@
         <v>44585</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -32546,7 +32546,7 @@
         <v>45839</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -32624,7 +32624,7 @@
         <v>45916</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -32702,7 +32702,7 @@
         <v>45964</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -32775,7 +32775,7 @@
         <v>46066</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -32848,7 +32848,7 @@
         <v>46287</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>

--- a/Översikt YDRE.xlsx
+++ b/Översikt YDRE.xlsx
@@ -601,7 +601,7 @@
         <v>44503</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -729,7 +729,7 @@
         <v>45153</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -848,7 +848,7 @@
         <v>44621</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -957,7 +957,7 @@
         <v>46282</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>45378</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1184,7 +1184,7 @@
         <v>45954</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1301,7 +1301,7 @@
         <v>45198</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1412,7 +1412,7 @@
         <v>45709</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1519,7 +1519,7 @@
         <v>46189</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1626,7 +1626,7 @@
         <v>45883</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1738,7 +1738,7 @@
         <v>44509</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1844,7 +1844,7 @@
         <v>45091</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1955,7 +1955,7 @@
         <v>44789</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2066,7 +2066,7 @@
         <v>45973</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2177,7 +2177,7 @@
         <v>45792</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2283,7 +2283,7 @@
         <v>45415</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2389,7 +2389,7 @@
         <v>45348</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2495,7 +2495,7 @@
         <v>45611</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2610,7 +2610,7 @@
         <v>45251</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2720,7 +2720,7 @@
         <v>44874</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2826,7 +2826,7 @@
         <v>44732</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2937,7 +2937,7 @@
         <v>45614</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3048,7 +3048,7 @@
         <v>45846</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3159,7 +3159,7 @@
         <v>44515</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3264,7 +3264,7 @@
         <v>44858</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3374,7 +3374,7 @@
         <v>46045</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3488,7 +3488,7 @@
         <v>45916</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3593,7 +3593,7 @@
         <v>45922</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3698,7 +3698,7 @@
         <v>46069</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3803,7 +3803,7 @@
         <v>46069</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3913,7 +3913,7 @@
         <v>45965</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4022,7 +4022,7 @@
         <v>45964</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4132,7 +4132,7 @@
         <v>45769</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4237,7 +4237,7 @@
         <v>45727</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4342,7 +4342,7 @@
         <v>45611</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4452,7 +4452,7 @@
         <v>45371</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4557,7 +4557,7 @@
         <v>45922</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4662,7 +4662,7 @@
         <v>45561</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4767,7 +4767,7 @@
         <v>45754</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4872,7 +4872,7 @@
         <v>46202</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4977,7 +4977,7 @@
         <v>45733</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5082,7 +5082,7 @@
         <v>45192</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5187,7 +5187,7 @@
         <v>45777</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5292,7 +5292,7 @@
         <v>46075</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5401,7 +5401,7 @@
         <v>44508</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5474,7 +5474,7 @@
         <v>44693</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5547,7 +5547,7 @@
         <v>44827</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5625,7 +5625,7 @@
         <v>44476</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5703,7 +5703,7 @@
         <v>44491</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5781,7 +5781,7 @@
         <v>44585</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5854,7 +5854,7 @@
         <v>44502</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5927,7 +5927,7 @@
         <v>44582</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6000,7 +6000,7 @@
         <v>44820</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6073,7 +6073,7 @@
         <v>44827</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6151,7 +6151,7 @@
         <v>44503</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6229,7 +6229,7 @@
         <v>44687</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6307,7 +6307,7 @@
         <v>44868</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6380,7 +6380,7 @@
         <v>44879</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6458,7 +6458,7 @@
         <v>44879</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6531,7 +6531,7 @@
         <v>44879</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6604,7 +6604,7 @@
         <v>44789</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6682,7 +6682,7 @@
         <v>44474</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6755,7 +6755,7 @@
         <v>44477</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6828,7 +6828,7 @@
         <v>44516</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6901,7 +6901,7 @@
         <v>44816</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6974,7 +6974,7 @@
         <v>44483</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7047,7 +7047,7 @@
         <v>44538</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7120,7 +7120,7 @@
         <v>44728</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7193,7 +7193,7 @@
         <v>44593</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7271,7 +7271,7 @@
         <v>44698</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7344,7 +7344,7 @@
         <v>44650</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7417,7 +7417,7 @@
         <v>44827</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7495,7 +7495,7 @@
         <v>44743</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7568,7 +7568,7 @@
         <v>44538</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7641,7 +7641,7 @@
         <v>44531</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7714,7 +7714,7 @@
         <v>45432</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7787,7 +7787,7 @@
         <v>45597</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7860,7 +7860,7 @@
         <v>44476</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7938,7 +7938,7 @@
         <v>45110</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8011,7 +8011,7 @@
         <v>45664</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8084,7 +8084,7 @@
         <v>44538</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8157,7 +8157,7 @@
         <v>44606</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8230,7 +8230,7 @@
         <v>45110</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8303,7 +8303,7 @@
         <v>45544</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8376,7 +8376,7 @@
         <v>45714</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8449,7 +8449,7 @@
         <v>45666</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8522,7 +8522,7 @@
         <v>45719</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8600,7 +8600,7 @@
         <v>45475</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8673,7 +8673,7 @@
         <v>45714</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8746,7 +8746,7 @@
         <v>46007</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8819,7 +8819,7 @@
         <v>46006</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8892,7 +8892,7 @@
         <v>46007</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8965,7 +8965,7 @@
         <v>46007</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9038,7 +9038,7 @@
         <v>46007</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9111,7 +9111,7 @@
         <v>46006</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9184,7 +9184,7 @@
         <v>45596</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9257,7 +9257,7 @@
         <v>46013</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9330,7 +9330,7 @@
         <v>46010</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9403,7 +9403,7 @@
         <v>45138</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9476,7 +9476,7 @@
         <v>46013</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9549,7 +9549,7 @@
         <v>46013</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9622,7 +9622,7 @@
         <v>46010</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9695,7 +9695,7 @@
         <v>45665</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9768,7 +9768,7 @@
         <v>46021</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9841,7 +9841,7 @@
         <v>45889</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9914,7 +9914,7 @@
         <v>45707</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9987,7 +9987,7 @@
         <v>45355</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10060,7 +10060,7 @@
         <v>45355</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10133,7 +10133,7 @@
         <v>44796</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10206,7 +10206,7 @@
         <v>45891</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10279,7 +10279,7 @@
         <v>45665</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10352,7 +10352,7 @@
         <v>45666</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10425,7 +10425,7 @@
         <v>44903</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10498,7 +10498,7 @@
         <v>45365</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10571,7 +10571,7 @@
         <v>45231</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10644,7 +10644,7 @@
         <v>45208</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10717,7 +10717,7 @@
         <v>45898</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10790,7 +10790,7 @@
         <v>44592</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10863,7 +10863,7 @@
         <v>45701</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10936,7 +10936,7 @@
         <v>46036</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11009,7 +11009,7 @@
         <v>45909</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11087,7 +11087,7 @@
         <v>45596</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11160,7 +11160,7 @@
         <v>45909</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11238,7 +11238,7 @@
         <v>45335</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11311,7 +11311,7 @@
         <v>46044</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11389,7 +11389,7 @@
         <v>45261</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11462,7 +11462,7 @@
         <v>45910</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11535,7 +11535,7 @@
         <v>45796</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11608,7 +11608,7 @@
         <v>45796</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11681,7 +11681,7 @@
         <v>46045</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11759,7 +11759,7 @@
         <v>46045</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11837,7 +11837,7 @@
         <v>45726</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11910,7 +11910,7 @@
         <v>45916</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11988,7 +11988,7 @@
         <v>45916</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12066,7 +12066,7 @@
         <v>45916</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12139,7 +12139,7 @@
         <v>45916</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12217,7 +12217,7 @@
         <v>45922</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12290,7 +12290,7 @@
         <v>46055</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12363,7 +12363,7 @@
         <v>45419</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12436,7 +12436,7 @@
         <v>45924</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12509,7 +12509,7 @@
         <v>45924</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12587,7 +12587,7 @@
         <v>46058</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12660,7 +12660,7 @@
         <v>45475</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12733,7 +12733,7 @@
         <v>45278</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12806,7 +12806,7 @@
         <v>45931</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12879,7 +12879,7 @@
         <v>45931</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12952,7 +12952,7 @@
         <v>46062</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13030,7 +13030,7 @@
         <v>45932</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13103,7 +13103,7 @@
         <v>45236</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13176,7 +13176,7 @@
         <v>46069</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13254,7 +13254,7 @@
         <v>46069</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13327,7 +13327,7 @@
         <v>45938</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13405,7 +13405,7 @@
         <v>46071</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13483,7 +13483,7 @@
         <v>45105</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13556,7 +13556,7 @@
         <v>45940</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13634,7 +13634,7 @@
         <v>44504</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13707,7 +13707,7 @@
         <v>45940</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13785,7 +13785,7 @@
         <v>45000</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13858,7 +13858,7 @@
         <v>45355</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13931,7 +13931,7 @@
         <v>45414</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14004,7 +14004,7 @@
         <v>46076</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14082,7 +14082,7 @@
         <v>45239</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14155,7 +14155,7 @@
         <v>45170</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14228,7 +14228,7 @@
         <v>45170</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14301,7 +14301,7 @@
         <v>45954</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14379,7 +14379,7 @@
         <v>45954</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14457,7 +14457,7 @@
         <v>44503</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14535,7 +14535,7 @@
         <v>44980</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14608,7 +14608,7 @@
         <v>45965</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14686,7 +14686,7 @@
         <v>45965</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14764,7 +14764,7 @@
         <v>45965</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14842,7 +14842,7 @@
         <v>45965</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14915,7 +14915,7 @@
         <v>45965</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14993,7 +14993,7 @@
         <v>45965</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15066,7 +15066,7 @@
         <v>45965</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15144,7 +15144,7 @@
         <v>45965</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15217,7 +15217,7 @@
         <v>45964</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15295,7 +15295,7 @@
         <v>44831</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15368,7 +15368,7 @@
         <v>45964</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15446,7 +15446,7 @@
         <v>45964</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15524,7 +15524,7 @@
         <v>44743</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15597,7 +15597,7 @@
         <v>44749</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15670,7 +15670,7 @@
         <v>46029</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15743,7 +15743,7 @@
         <v>46097</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15816,7 +15816,7 @@
         <v>45434</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15889,7 +15889,7 @@
         <v>45218</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15962,7 +15962,7 @@
         <v>45510</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16035,7 +16035,7 @@
         <v>46099</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16108,7 +16108,7 @@
         <v>45216</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16181,7 +16181,7 @@
         <v>45216</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16254,7 +16254,7 @@
         <v>46101</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16327,7 +16327,7 @@
         <v>46101</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16400,7 +16400,7 @@
         <v>45194</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16473,7 +16473,7 @@
         <v>45666</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16546,7 +16546,7 @@
         <v>46106</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16619,7 +16619,7 @@
         <v>45119</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16697,7 +16697,7 @@
         <v>44966</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16770,7 +16770,7 @@
         <v>44480</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16848,7 +16848,7 @@
         <v>45821</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16926,7 +16926,7 @@
         <v>46116</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16999,7 +16999,7 @@
         <v>46119</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17072,7 +17072,7 @@
         <v>46119</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17145,7 +17145,7 @@
         <v>44939</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17218,7 +17218,7 @@
         <v>46121</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17291,7 +17291,7 @@
         <v>46125</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17364,7 +17364,7 @@
         <v>45994</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17437,7 +17437,7 @@
         <v>45994</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17510,7 +17510,7 @@
         <v>46125</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17583,7 +17583,7 @@
         <v>46126</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17656,7 +17656,7 @@
         <v>45994</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17729,7 +17729,7 @@
         <v>44994</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17802,7 +17802,7 @@
         <v>45965</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17875,7 +17875,7 @@
         <v>44980</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17948,7 +17948,7 @@
         <v>45831</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18021,7 +18021,7 @@
         <v>45831</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18094,7 +18094,7 @@
         <v>45831</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18167,7 +18167,7 @@
         <v>45831</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18240,7 +18240,7 @@
         <v>45831</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18313,7 +18313,7 @@
         <v>45091</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18391,7 +18391,7 @@
         <v>44480</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18464,7 +18464,7 @@
         <v>44576</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18537,7 +18537,7 @@
         <v>44994</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18610,7 +18610,7 @@
         <v>44994</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18683,7 +18683,7 @@
         <v>44635</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18756,7 +18756,7 @@
         <v>45575</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18829,7 +18829,7 @@
         <v>44789</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18907,7 +18907,7 @@
         <v>45831</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18980,7 +18980,7 @@
         <v>45838</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19058,7 +19058,7 @@
         <v>45365</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19131,7 +19131,7 @@
         <v>44908</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19204,7 +19204,7 @@
         <v>45153</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19277,7 +19277,7 @@
         <v>45474</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19350,7 +19350,7 @@
         <v>45916</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19423,7 +19423,7 @@
         <v>45077</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19496,7 +19496,7 @@
         <v>45831</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19569,7 +19569,7 @@
         <v>45790</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19642,7 +19642,7 @@
         <v>45810</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19715,7 +19715,7 @@
         <v>45917</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19788,7 +19788,7 @@
         <v>45616</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19861,7 +19861,7 @@
         <v>45647</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19934,7 +19934,7 @@
         <v>45634</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20007,7 +20007,7 @@
         <v>45910</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20080,7 +20080,7 @@
         <v>45406</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20153,7 +20153,7 @@
         <v>45965</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20226,7 +20226,7 @@
         <v>45871</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20299,7 +20299,7 @@
         <v>45460</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20372,7 +20372,7 @@
         <v>45096</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20445,7 +20445,7 @@
         <v>45831</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20518,7 +20518,7 @@
         <v>45793</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20591,7 +20591,7 @@
         <v>45246</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20669,7 +20669,7 @@
         <v>45841</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20742,7 +20742,7 @@
         <v>45273</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20815,7 +20815,7 @@
         <v>44953</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20888,7 +20888,7 @@
         <v>44600</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20961,7 +20961,7 @@
         <v>44894</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21034,7 +21034,7 @@
         <v>44480</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21132,7 +21132,7 @@
         <v>45145</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21205,7 +21205,7 @@
         <v>45666</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21278,7 +21278,7 @@
         <v>45701</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21351,7 +21351,7 @@
         <v>45769</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21424,7 +21424,7 @@
         <v>45714</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21497,7 +21497,7 @@
         <v>45054</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21570,7 +21570,7 @@
         <v>44502</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21643,7 +21643,7 @@
         <v>44965</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21716,7 +21716,7 @@
         <v>46146</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21789,7 +21789,7 @@
         <v>46146</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21862,7 +21862,7 @@
         <v>46146</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21935,7 +21935,7 @@
         <v>46146</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -22008,7 +22008,7 @@
         <v>46146</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -22081,7 +22081,7 @@
         <v>46146</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22154,7 +22154,7 @@
         <v>45310</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22227,7 +22227,7 @@
         <v>45428</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22300,7 +22300,7 @@
         <v>45737</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22373,7 +22373,7 @@
         <v>46153</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22451,7 +22451,7 @@
         <v>46154</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22529,7 +22529,7 @@
         <v>45194</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22602,7 +22602,7 @@
         <v>45587</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22680,7 +22680,7 @@
         <v>45194</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22753,7 +22753,7 @@
         <v>44916</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22826,7 +22826,7 @@
         <v>44562</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22899,7 +22899,7 @@
         <v>45272</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22977,7 +22977,7 @@
         <v>45414</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -23050,7 +23050,7 @@
         <v>44536</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -23123,7 +23123,7 @@
         <v>45701</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23196,7 +23196,7 @@
         <v>46038</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23274,7 +23274,7 @@
         <v>45965</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23352,7 +23352,7 @@
         <v>46171</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23430,7 +23430,7 @@
         <v>45090</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23508,7 +23508,7 @@
         <v>44908</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23581,7 +23581,7 @@
         <v>44908</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23654,7 +23654,7 @@
         <v>44624</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23727,7 +23727,7 @@
         <v>46177</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23805,7 +23805,7 @@
         <v>46183</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23883,7 +23883,7 @@
         <v>46190</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23956,7 +23956,7 @@
         <v>45302</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -24029,7 +24029,7 @@
         <v>44994</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -24102,7 +24102,7 @@
         <v>46191</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -24175,7 +24175,7 @@
         <v>45371</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24248,7 +24248,7 @@
         <v>45537</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24321,7 +24321,7 @@
         <v>46202</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24394,7 +24394,7 @@
         <v>46202</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24467,7 +24467,7 @@
         <v>46202</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24540,7 +24540,7 @@
         <v>46202</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24613,7 +24613,7 @@
         <v>46202</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24686,7 +24686,7 @@
         <v>44868</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24764,7 +24764,7 @@
         <v>45110</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24837,7 +24837,7 @@
         <v>45755</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24910,7 +24910,7 @@
         <v>45583</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -24983,7 +24983,7 @@
         <v>45099</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -25056,7 +25056,7 @@
         <v>45595</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -25129,7 +25129,7 @@
         <v>46258</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25202,7 +25202,7 @@
         <v>44966</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25275,7 +25275,7 @@
         <v>44572</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25348,7 +25348,7 @@
         <v>44491</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25426,7 +25426,7 @@
         <v>45831</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25499,7 +25499,7 @@
         <v>44501</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25572,7 +25572,7 @@
         <v>45701</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25645,7 +25645,7 @@
         <v>45335</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25718,7 +25718,7 @@
         <v>45575</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25791,7 +25791,7 @@
         <v>46269</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25864,7 +25864,7 @@
         <v>46269</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -25937,7 +25937,7 @@
         <v>44874</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -26010,7 +26010,7 @@
         <v>46273</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -26083,7 +26083,7 @@
         <v>46273</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -26156,7 +26156,7 @@
         <v>46273</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -26229,7 +26229,7 @@
         <v>44711</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -26307,7 +26307,7 @@
         <v>46275</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -26380,7 +26380,7 @@
         <v>46280</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -26453,7 +26453,7 @@
         <v>46283</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -26531,7 +26531,7 @@
         <v>46282</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26604,7 +26604,7 @@
         <v>45649</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26677,7 +26677,7 @@
         <v>46282</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26750,7 +26750,7 @@
         <v>46282</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -26823,7 +26823,7 @@
         <v>46240</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -26896,7 +26896,7 @@
         <v>46283</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -26974,7 +26974,7 @@
         <v>46283</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -27052,7 +27052,7 @@
         <v>46283</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -27130,7 +27130,7 @@
         <v>46282</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -27203,7 +27203,7 @@
         <v>46240</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -27276,7 +27276,7 @@
         <v>46282</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -27349,7 +27349,7 @@
         <v>46282</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -27422,7 +27422,7 @@
         <v>46283</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -27500,7 +27500,7 @@
         <v>45460</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -27573,7 +27573,7 @@
         <v>45580</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -27646,7 +27646,7 @@
         <v>45170</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -27719,7 +27719,7 @@
         <v>45707</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -27792,7 +27792,7 @@
         <v>46076</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -27870,7 +27870,7 @@
         <v>45664</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -27943,7 +27943,7 @@
         <v>46286</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -28021,7 +28021,7 @@
         <v>46286</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -28099,7 +28099,7 @@
         <v>45436</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -28172,7 +28172,7 @@
         <v>44530</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -28245,7 +28245,7 @@
         <v>45261</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -28318,7 +28318,7 @@
         <v>45649</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -28391,7 +28391,7 @@
         <v>46290</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -28464,7 +28464,7 @@
         <v>45398</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -28537,7 +28537,7 @@
         <v>44987</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -28610,7 +28610,7 @@
         <v>45762</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -28683,7 +28683,7 @@
         <v>45831</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -28756,7 +28756,7 @@
         <v>45758</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -28829,7 +28829,7 @@
         <v>45104</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -28902,7 +28902,7 @@
         <v>45600</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -28980,7 +28980,7 @@
         <v>45638</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -29053,7 +29053,7 @@
         <v>46290</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -29126,7 +29126,7 @@
         <v>45414</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -29199,7 +29199,7 @@
         <v>45334</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -29272,7 +29272,7 @@
         <v>44816</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -29345,7 +29345,7 @@
         <v>45016</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -29423,7 +29423,7 @@
         <v>44655</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -29496,7 +29496,7 @@
         <v>45348</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -29569,7 +29569,7 @@
         <v>45085</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -29642,7 +29642,7 @@
         <v>45414</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -29715,7 +29715,7 @@
         <v>44987</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -29788,7 +29788,7 @@
         <v>44980</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -29861,7 +29861,7 @@
         <v>44908</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -29934,7 +29934,7 @@
         <v>45634</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -30007,7 +30007,7 @@
         <v>45218</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -30080,7 +30080,7 @@
         <v>45414</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -30153,7 +30153,7 @@
         <v>44651</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -30226,7 +30226,7 @@
         <v>44844</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -30299,7 +30299,7 @@
         <v>45257</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -30372,7 +30372,7 @@
         <v>45698</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -30445,7 +30445,7 @@
         <v>45159</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -30518,7 +30518,7 @@
         <v>45558</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -30591,7 +30591,7 @@
         <v>45054</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -30664,7 +30664,7 @@
         <v>44994</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -30737,7 +30737,7 @@
         <v>45273</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -30810,7 +30810,7 @@
         <v>45692</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -30883,7 +30883,7 @@
         <v>44670</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -30956,7 +30956,7 @@
         <v>44953</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -31029,7 +31029,7 @@
         <v>44651</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -31102,7 +31102,7 @@
         <v>45671</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -31175,7 +31175,7 @@
         <v>44490</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -31248,7 +31248,7 @@
         <v>45159</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -31321,7 +31321,7 @@
         <v>45096</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -31394,7 +31394,7 @@
         <v>45677</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -31467,7 +31467,7 @@
         <v>45736</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -31545,7 +31545,7 @@
         <v>45748</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -31618,7 +31618,7 @@
         <v>45264</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -31691,7 +31691,7 @@
         <v>44483</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -31764,7 +31764,7 @@
         <v>45492</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -31837,7 +31837,7 @@
         <v>45468</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -31910,7 +31910,7 @@
         <v>44585</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -31983,7 +31983,7 @@
         <v>45839</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -32061,7 +32061,7 @@
         <v>45916</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -32139,7 +32139,7 @@
         <v>45964</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -32212,7 +32212,7 @@
         <v>46066</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -32285,7 +32285,7 @@
         <v>46287</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>

--- a/Översikt YDRE.xlsx
+++ b/Översikt YDRE.xlsx
@@ -601,7 +601,7 @@
         <v>44503</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -729,7 +729,7 @@
         <v>45153</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -848,7 +848,7 @@
         <v>44621</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -957,7 +957,7 @@
         <v>46282</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>45378</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1184,7 +1184,7 @@
         <v>45954</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1301,7 +1301,7 @@
         <v>45198</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1412,7 +1412,7 @@
         <v>45709</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1519,7 +1519,7 @@
         <v>46189</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1626,7 +1626,7 @@
         <v>45883</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1738,7 +1738,7 @@
         <v>44509</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1844,7 +1844,7 @@
         <v>45091</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1955,7 +1955,7 @@
         <v>44789</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2066,7 +2066,7 @@
         <v>45973</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2177,7 +2177,7 @@
         <v>45792</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2283,7 +2283,7 @@
         <v>45415</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2389,7 +2389,7 @@
         <v>45348</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2495,7 +2495,7 @@
         <v>45611</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2610,7 +2610,7 @@
         <v>45251</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2720,7 +2720,7 @@
         <v>44874</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2826,7 +2826,7 @@
         <v>44732</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2937,7 +2937,7 @@
         <v>45614</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3048,7 +3048,7 @@
         <v>45846</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3159,7 +3159,7 @@
         <v>44515</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3264,7 +3264,7 @@
         <v>44858</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3374,7 +3374,7 @@
         <v>46045</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3488,7 +3488,7 @@
         <v>45916</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3593,7 +3593,7 @@
         <v>45922</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3698,7 +3698,7 @@
         <v>46069</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3803,7 +3803,7 @@
         <v>46069</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3913,7 +3913,7 @@
         <v>45965</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4022,7 +4022,7 @@
         <v>45964</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4132,7 +4132,7 @@
         <v>45769</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4237,7 +4237,7 @@
         <v>45727</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4342,7 +4342,7 @@
         <v>45611</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4452,7 +4452,7 @@
         <v>45371</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4557,7 +4557,7 @@
         <v>45922</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4662,7 +4662,7 @@
         <v>45561</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4767,7 +4767,7 @@
         <v>45754</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4872,7 +4872,7 @@
         <v>46202</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4977,7 +4977,7 @@
         <v>45733</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5082,7 +5082,7 @@
         <v>45192</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5187,7 +5187,7 @@
         <v>45777</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5292,7 +5292,7 @@
         <v>46075</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5401,7 +5401,7 @@
         <v>44508</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5474,7 +5474,7 @@
         <v>44693</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5547,7 +5547,7 @@
         <v>44827</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5625,7 +5625,7 @@
         <v>44476</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5703,7 +5703,7 @@
         <v>44491</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5781,7 +5781,7 @@
         <v>44585</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5854,7 +5854,7 @@
         <v>44502</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5927,7 +5927,7 @@
         <v>44582</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6000,7 +6000,7 @@
         <v>44820</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6073,7 +6073,7 @@
         <v>44827</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6151,7 +6151,7 @@
         <v>44503</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6229,7 +6229,7 @@
         <v>44687</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6307,7 +6307,7 @@
         <v>44868</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6380,7 +6380,7 @@
         <v>44879</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6458,7 +6458,7 @@
         <v>44879</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6531,7 +6531,7 @@
         <v>44879</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6604,7 +6604,7 @@
         <v>44789</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6682,7 +6682,7 @@
         <v>44474</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6755,7 +6755,7 @@
         <v>44477</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6828,7 +6828,7 @@
         <v>44516</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6901,7 +6901,7 @@
         <v>44816</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6974,7 +6974,7 @@
         <v>44483</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7047,7 +7047,7 @@
         <v>44538</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7120,7 +7120,7 @@
         <v>44728</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7193,7 +7193,7 @@
         <v>44593</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7271,7 +7271,7 @@
         <v>44698</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7344,7 +7344,7 @@
         <v>44650</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7417,7 +7417,7 @@
         <v>44827</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7495,7 +7495,7 @@
         <v>44743</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7568,7 +7568,7 @@
         <v>44538</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7641,7 +7641,7 @@
         <v>44531</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7714,7 +7714,7 @@
         <v>45432</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7787,7 +7787,7 @@
         <v>45597</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7860,7 +7860,7 @@
         <v>44476</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7938,7 +7938,7 @@
         <v>45110</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8011,7 +8011,7 @@
         <v>45664</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8084,7 +8084,7 @@
         <v>44538</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8157,7 +8157,7 @@
         <v>44606</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8230,7 +8230,7 @@
         <v>45110</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8303,7 +8303,7 @@
         <v>45544</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8376,7 +8376,7 @@
         <v>45714</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8449,7 +8449,7 @@
         <v>45666</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8522,7 +8522,7 @@
         <v>45719</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8600,7 +8600,7 @@
         <v>45475</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8673,7 +8673,7 @@
         <v>45714</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8746,7 +8746,7 @@
         <v>46007</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8819,7 +8819,7 @@
         <v>46006</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8892,7 +8892,7 @@
         <v>46007</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8965,7 +8965,7 @@
         <v>46007</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9038,7 +9038,7 @@
         <v>46007</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9111,7 +9111,7 @@
         <v>46006</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9184,7 +9184,7 @@
         <v>45596</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9257,7 +9257,7 @@
         <v>46013</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9330,7 +9330,7 @@
         <v>46010</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9403,7 +9403,7 @@
         <v>45138</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9476,7 +9476,7 @@
         <v>46013</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9549,7 +9549,7 @@
         <v>46013</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9622,7 +9622,7 @@
         <v>46010</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9695,7 +9695,7 @@
         <v>45665</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9768,7 +9768,7 @@
         <v>46021</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9841,7 +9841,7 @@
         <v>45889</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9914,7 +9914,7 @@
         <v>45707</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9987,7 +9987,7 @@
         <v>45355</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10060,7 +10060,7 @@
         <v>45355</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10133,7 +10133,7 @@
         <v>44796</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10206,7 +10206,7 @@
         <v>45891</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10279,7 +10279,7 @@
         <v>45665</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10352,7 +10352,7 @@
         <v>45666</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10425,7 +10425,7 @@
         <v>44903</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10498,7 +10498,7 @@
         <v>45365</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10571,7 +10571,7 @@
         <v>45231</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10644,7 +10644,7 @@
         <v>45208</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10717,7 +10717,7 @@
         <v>45898</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10790,7 +10790,7 @@
         <v>44592</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10863,7 +10863,7 @@
         <v>45701</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10936,7 +10936,7 @@
         <v>46036</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11009,7 +11009,7 @@
         <v>45909</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11087,7 +11087,7 @@
         <v>45596</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11160,7 +11160,7 @@
         <v>45909</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11238,7 +11238,7 @@
         <v>45335</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11311,7 +11311,7 @@
         <v>46044</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11389,7 +11389,7 @@
         <v>45261</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11462,7 +11462,7 @@
         <v>45910</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11535,7 +11535,7 @@
         <v>45796</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11608,7 +11608,7 @@
         <v>45796</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11681,7 +11681,7 @@
         <v>46045</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11759,7 +11759,7 @@
         <v>46045</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11837,7 +11837,7 @@
         <v>45726</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11910,7 +11910,7 @@
         <v>45916</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11988,7 +11988,7 @@
         <v>45916</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12066,7 +12066,7 @@
         <v>45916</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12139,7 +12139,7 @@
         <v>45916</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12217,7 +12217,7 @@
         <v>45922</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12290,7 +12290,7 @@
         <v>46055</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12363,7 +12363,7 @@
         <v>45419</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12436,7 +12436,7 @@
         <v>45924</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12509,7 +12509,7 @@
         <v>45924</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12587,7 +12587,7 @@
         <v>46058</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12660,7 +12660,7 @@
         <v>45475</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12733,7 +12733,7 @@
         <v>45278</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12806,7 +12806,7 @@
         <v>45931</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12879,7 +12879,7 @@
         <v>45931</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12952,7 +12952,7 @@
         <v>46062</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13030,7 +13030,7 @@
         <v>45932</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13103,7 +13103,7 @@
         <v>45236</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13176,7 +13176,7 @@
         <v>46069</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13254,7 +13254,7 @@
         <v>46069</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13327,7 +13327,7 @@
         <v>45938</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13405,7 +13405,7 @@
         <v>46071</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13483,7 +13483,7 @@
         <v>45105</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13556,7 +13556,7 @@
         <v>45940</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13634,7 +13634,7 @@
         <v>44504</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13707,7 +13707,7 @@
         <v>45940</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13785,7 +13785,7 @@
         <v>45000</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13858,7 +13858,7 @@
         <v>45355</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13931,7 +13931,7 @@
         <v>45414</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14004,7 +14004,7 @@
         <v>46076</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14082,7 +14082,7 @@
         <v>45239</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14155,7 +14155,7 @@
         <v>45170</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14228,7 +14228,7 @@
         <v>45170</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14301,7 +14301,7 @@
         <v>45954</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14379,7 +14379,7 @@
         <v>45954</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14457,7 +14457,7 @@
         <v>44503</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14535,7 +14535,7 @@
         <v>44980</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14608,7 +14608,7 @@
         <v>45965</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14686,7 +14686,7 @@
         <v>45965</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14764,7 +14764,7 @@
         <v>45965</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14842,7 +14842,7 @@
         <v>45965</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14915,7 +14915,7 @@
         <v>45965</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14993,7 +14993,7 @@
         <v>45965</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15066,7 +15066,7 @@
         <v>45965</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15144,7 +15144,7 @@
         <v>45965</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15217,7 +15217,7 @@
         <v>45964</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15295,7 +15295,7 @@
         <v>44831</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15368,7 +15368,7 @@
         <v>45964</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15446,7 +15446,7 @@
         <v>45964</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15524,7 +15524,7 @@
         <v>44743</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15597,7 +15597,7 @@
         <v>44749</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15670,7 +15670,7 @@
         <v>46029</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15743,7 +15743,7 @@
         <v>46097</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15816,7 +15816,7 @@
         <v>45434</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15889,7 +15889,7 @@
         <v>45218</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15962,7 +15962,7 @@
         <v>45510</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16035,7 +16035,7 @@
         <v>46099</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16108,7 +16108,7 @@
         <v>45216</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16181,7 +16181,7 @@
         <v>45216</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16254,7 +16254,7 @@
         <v>46101</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16327,7 +16327,7 @@
         <v>46101</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16400,7 +16400,7 @@
         <v>45194</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16473,7 +16473,7 @@
         <v>45666</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16546,7 +16546,7 @@
         <v>46106</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16619,7 +16619,7 @@
         <v>45119</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16697,7 +16697,7 @@
         <v>44966</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16770,7 +16770,7 @@
         <v>44480</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16848,7 +16848,7 @@
         <v>45821</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16926,7 +16926,7 @@
         <v>46116</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16999,7 +16999,7 @@
         <v>46119</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17072,7 +17072,7 @@
         <v>46119</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17145,7 +17145,7 @@
         <v>44939</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17218,7 +17218,7 @@
         <v>46121</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17291,7 +17291,7 @@
         <v>46125</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17364,7 +17364,7 @@
         <v>45994</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17437,7 +17437,7 @@
         <v>45994</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17510,7 +17510,7 @@
         <v>46125</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17583,7 +17583,7 @@
         <v>46126</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17656,7 +17656,7 @@
         <v>45994</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17729,7 +17729,7 @@
         <v>44994</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17802,7 +17802,7 @@
         <v>45965</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17875,7 +17875,7 @@
         <v>44980</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17948,7 +17948,7 @@
         <v>45831</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18021,7 +18021,7 @@
         <v>45831</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18094,7 +18094,7 @@
         <v>45831</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18167,7 +18167,7 @@
         <v>45831</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18240,7 +18240,7 @@
         <v>45831</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18313,7 +18313,7 @@
         <v>45091</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18391,7 +18391,7 @@
         <v>44480</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18464,7 +18464,7 @@
         <v>44576</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18537,7 +18537,7 @@
         <v>44994</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18610,7 +18610,7 @@
         <v>44994</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18683,7 +18683,7 @@
         <v>44635</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18756,7 +18756,7 @@
         <v>45575</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18829,7 +18829,7 @@
         <v>44789</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18907,7 +18907,7 @@
         <v>45831</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18980,7 +18980,7 @@
         <v>45838</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19058,7 +19058,7 @@
         <v>45365</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19131,7 +19131,7 @@
         <v>44908</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19204,7 +19204,7 @@
         <v>45153</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19277,7 +19277,7 @@
         <v>45474</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19350,7 +19350,7 @@
         <v>45916</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19423,7 +19423,7 @@
         <v>45077</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19496,7 +19496,7 @@
         <v>45831</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19569,7 +19569,7 @@
         <v>45790</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19642,7 +19642,7 @@
         <v>45810</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19715,7 +19715,7 @@
         <v>45917</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19788,7 +19788,7 @@
         <v>45616</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19861,7 +19861,7 @@
         <v>45647</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19934,7 +19934,7 @@
         <v>45634</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20007,7 +20007,7 @@
         <v>45910</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20080,7 +20080,7 @@
         <v>45406</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20153,7 +20153,7 @@
         <v>45965</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20226,7 +20226,7 @@
         <v>45871</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20299,7 +20299,7 @@
         <v>45460</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20372,7 +20372,7 @@
         <v>45096</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20445,7 +20445,7 @@
         <v>45831</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20518,7 +20518,7 @@
         <v>45793</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20591,7 +20591,7 @@
         <v>45246</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20669,7 +20669,7 @@
         <v>45841</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20742,7 +20742,7 @@
         <v>45273</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20815,7 +20815,7 @@
         <v>44953</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20888,7 +20888,7 @@
         <v>44600</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20961,7 +20961,7 @@
         <v>44894</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21034,7 +21034,7 @@
         <v>44480</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21132,7 +21132,7 @@
         <v>45145</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21205,7 +21205,7 @@
         <v>45666</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21278,7 +21278,7 @@
         <v>45701</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21351,7 +21351,7 @@
         <v>45769</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21424,7 +21424,7 @@
         <v>45714</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21497,7 +21497,7 @@
         <v>45054</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21570,7 +21570,7 @@
         <v>44502</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21643,7 +21643,7 @@
         <v>44965</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21716,7 +21716,7 @@
         <v>46146</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21789,7 +21789,7 @@
         <v>46146</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21862,7 +21862,7 @@
         <v>46146</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21935,7 +21935,7 @@
         <v>46146</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -22008,7 +22008,7 @@
         <v>46146</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -22081,7 +22081,7 @@
         <v>46146</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22154,7 +22154,7 @@
         <v>45310</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22227,7 +22227,7 @@
         <v>45428</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22300,7 +22300,7 @@
         <v>45737</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22373,7 +22373,7 @@
         <v>46153</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22451,7 +22451,7 @@
         <v>46154</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22529,7 +22529,7 @@
         <v>45194</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22602,7 +22602,7 @@
         <v>45587</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22680,7 +22680,7 @@
         <v>45194</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22753,7 +22753,7 @@
         <v>44916</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22826,7 +22826,7 @@
         <v>44562</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22899,7 +22899,7 @@
         <v>45272</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22977,7 +22977,7 @@
         <v>45414</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -23050,7 +23050,7 @@
         <v>44536</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -23123,7 +23123,7 @@
         <v>45701</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23196,7 +23196,7 @@
         <v>46038</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23274,7 +23274,7 @@
         <v>45965</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23352,7 +23352,7 @@
         <v>46171</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23430,7 +23430,7 @@
         <v>45090</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23508,7 +23508,7 @@
         <v>44908</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23581,7 +23581,7 @@
         <v>44908</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23654,7 +23654,7 @@
         <v>44624</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23727,7 +23727,7 @@
         <v>46177</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23805,7 +23805,7 @@
         <v>46183</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23883,7 +23883,7 @@
         <v>46190</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23956,7 +23956,7 @@
         <v>45302</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -24029,7 +24029,7 @@
         <v>44994</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -24102,7 +24102,7 @@
         <v>46191</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -24175,7 +24175,7 @@
         <v>45371</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24248,7 +24248,7 @@
         <v>45537</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24321,7 +24321,7 @@
         <v>46202</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24394,7 +24394,7 @@
         <v>46202</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24467,7 +24467,7 @@
         <v>46202</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24540,7 +24540,7 @@
         <v>46202</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24613,7 +24613,7 @@
         <v>46202</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24686,7 +24686,7 @@
         <v>44868</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24764,7 +24764,7 @@
         <v>45110</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24837,7 +24837,7 @@
         <v>45755</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24910,7 +24910,7 @@
         <v>45583</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -24983,7 +24983,7 @@
         <v>45099</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -25056,7 +25056,7 @@
         <v>45595</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -25129,7 +25129,7 @@
         <v>46258</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25202,7 +25202,7 @@
         <v>44966</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25275,7 +25275,7 @@
         <v>44572</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25348,7 +25348,7 @@
         <v>44491</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25426,7 +25426,7 @@
         <v>45831</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25499,7 +25499,7 @@
         <v>44501</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25572,7 +25572,7 @@
         <v>45701</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25645,7 +25645,7 @@
         <v>45335</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25718,7 +25718,7 @@
         <v>45575</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25791,7 +25791,7 @@
         <v>46269</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25864,7 +25864,7 @@
         <v>46269</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -25937,7 +25937,7 @@
         <v>44874</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -26010,7 +26010,7 @@
         <v>46273</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -26083,7 +26083,7 @@
         <v>46273</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -26156,7 +26156,7 @@
         <v>46273</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -26229,7 +26229,7 @@
         <v>44711</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -26307,7 +26307,7 @@
         <v>46275</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -26380,7 +26380,7 @@
         <v>46280</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -26453,7 +26453,7 @@
         <v>46283</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -26531,7 +26531,7 @@
         <v>46282</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26604,7 +26604,7 @@
         <v>45649</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26677,7 +26677,7 @@
         <v>46282</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26750,7 +26750,7 @@
         <v>46282</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -26823,7 +26823,7 @@
         <v>46240</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -26896,7 +26896,7 @@
         <v>46283</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -26974,7 +26974,7 @@
         <v>46283</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -27052,7 +27052,7 @@
         <v>46283</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -27130,7 +27130,7 @@
         <v>46282</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -27203,7 +27203,7 @@
         <v>46240</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -27276,7 +27276,7 @@
         <v>46282</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -27349,7 +27349,7 @@
         <v>46282</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -27422,7 +27422,7 @@
         <v>46283</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -27500,7 +27500,7 @@
         <v>45460</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -27573,7 +27573,7 @@
         <v>45580</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -27646,7 +27646,7 @@
         <v>45170</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -27719,7 +27719,7 @@
         <v>45707</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -27792,7 +27792,7 @@
         <v>46076</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -27870,7 +27870,7 @@
         <v>45664</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -27943,7 +27943,7 @@
         <v>46286</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -28021,7 +28021,7 @@
         <v>46286</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -28099,7 +28099,7 @@
         <v>45436</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -28172,7 +28172,7 @@
         <v>44530</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -28245,7 +28245,7 @@
         <v>45261</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -28318,7 +28318,7 @@
         <v>45649</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -28391,7 +28391,7 @@
         <v>46290</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -28464,7 +28464,7 @@
         <v>45398</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -28537,7 +28537,7 @@
         <v>44987</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -28610,7 +28610,7 @@
         <v>45762</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -28683,7 +28683,7 @@
         <v>45831</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -28756,7 +28756,7 @@
         <v>45758</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -28829,7 +28829,7 @@
         <v>45104</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -28902,7 +28902,7 @@
         <v>45600</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -28980,7 +28980,7 @@
         <v>45638</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -29053,7 +29053,7 @@
         <v>46290</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -29126,7 +29126,7 @@
         <v>45414</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -29199,7 +29199,7 @@
         <v>45334</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -29272,7 +29272,7 @@
         <v>44816</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -29345,7 +29345,7 @@
         <v>45016</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -29423,7 +29423,7 @@
         <v>44655</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -29496,7 +29496,7 @@
         <v>45348</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -29569,7 +29569,7 @@
         <v>45085</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -29642,7 +29642,7 @@
         <v>45414</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -29715,7 +29715,7 @@
         <v>44987</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -29788,7 +29788,7 @@
         <v>44980</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -29861,7 +29861,7 @@
         <v>44908</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -29934,7 +29934,7 @@
         <v>45634</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -30007,7 +30007,7 @@
         <v>45218</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -30080,7 +30080,7 @@
         <v>45414</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -30153,7 +30153,7 @@
         <v>44651</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -30226,7 +30226,7 @@
         <v>44844</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -30299,7 +30299,7 @@
         <v>45257</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -30372,7 +30372,7 @@
         <v>45698</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -30445,7 +30445,7 @@
         <v>45159</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -30518,7 +30518,7 @@
         <v>45558</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -30591,7 +30591,7 @@
         <v>45054</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -30664,7 +30664,7 @@
         <v>44994</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -30737,7 +30737,7 @@
         <v>45273</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -30810,7 +30810,7 @@
         <v>45692</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -30883,7 +30883,7 @@
         <v>44670</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -30956,7 +30956,7 @@
         <v>44953</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -31029,7 +31029,7 @@
         <v>44651</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -31102,7 +31102,7 @@
         <v>45671</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -31175,7 +31175,7 @@
         <v>44490</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -31248,7 +31248,7 @@
         <v>45159</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -31321,7 +31321,7 @@
         <v>45096</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -31394,7 +31394,7 @@
         <v>45677</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -31467,7 +31467,7 @@
         <v>45736</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -31545,7 +31545,7 @@
         <v>45748</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -31618,7 +31618,7 @@
         <v>45264</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -31691,7 +31691,7 @@
         <v>44483</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -31764,7 +31764,7 @@
         <v>45492</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -31837,7 +31837,7 @@
         <v>45468</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -31910,7 +31910,7 @@
         <v>44585</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -31983,7 +31983,7 @@
         <v>45839</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -32061,7 +32061,7 @@
         <v>45916</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -32139,7 +32139,7 @@
         <v>45964</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -32212,7 +32212,7 @@
         <v>46066</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -32285,7 +32285,7 @@
         <v>46287</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>

--- a/Översikt YDRE.xlsx
+++ b/Översikt YDRE.xlsx
@@ -601,7 +601,7 @@
         <v>44503</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -729,7 +729,7 @@
         <v>45153</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -848,7 +848,7 @@
         <v>44621</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -957,7 +957,7 @@
         <v>46282</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>45378</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1184,7 +1184,7 @@
         <v>45954</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1301,7 +1301,7 @@
         <v>45198</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1412,7 +1412,7 @@
         <v>45709</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1519,7 +1519,7 @@
         <v>46189</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1626,7 +1626,7 @@
         <v>45883</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1738,7 +1738,7 @@
         <v>44509</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1844,7 +1844,7 @@
         <v>44789</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1955,7 +1955,7 @@
         <v>44874</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2061,7 +2061,7 @@
         <v>45348</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2167,7 +2167,7 @@
         <v>44732</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2278,7 +2278,7 @@
         <v>45611</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2393,7 +2393,7 @@
         <v>45091</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2504,7 +2504,7 @@
         <v>45251</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2614,7 +2614,7 @@
         <v>45415</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2720,7 +2720,7 @@
         <v>45792</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2826,7 +2826,7 @@
         <v>45973</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2937,7 +2937,7 @@
         <v>45614</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3048,7 +3048,7 @@
         <v>45846</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3159,7 +3159,7 @@
         <v>44515</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3264,7 +3264,7 @@
         <v>44858</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3374,7 +3374,7 @@
         <v>45371</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3479,7 +3479,7 @@
         <v>45611</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3589,7 +3589,7 @@
         <v>45561</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3694,7 +3694,7 @@
         <v>45916</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3799,7 +3799,7 @@
         <v>45922</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3904,7 +3904,7 @@
         <v>45964</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4014,7 +4014,7 @@
         <v>45192</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4119,7 +4119,7 @@
         <v>45965</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4228,7 +4228,7 @@
         <v>45769</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4333,7 +4333,7 @@
         <v>45733</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4438,7 +4438,7 @@
         <v>45754</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4543,7 +4543,7 @@
         <v>45922</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4648,7 +4648,7 @@
         <v>45727</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4753,7 +4753,7 @@
         <v>46045</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4867,7 +4867,7 @@
         <v>46069</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4972,7 +4972,7 @@
         <v>46069</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5082,7 +5082,7 @@
         <v>46202</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5187,7 +5187,7 @@
         <v>45777</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5292,7 +5292,7 @@
         <v>46075</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5401,7 +5401,7 @@
         <v>44582</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5474,7 +5474,7 @@
         <v>44508</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5547,7 +5547,7 @@
         <v>44693</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5620,7 +5620,7 @@
         <v>44827</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5698,7 +5698,7 @@
         <v>44491</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5776,7 +5776,7 @@
         <v>44585</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5849,7 +5849,7 @@
         <v>44502</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5922,7 +5922,7 @@
         <v>44820</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5995,7 +5995,7 @@
         <v>44827</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6073,7 +6073,7 @@
         <v>44503</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6151,7 +6151,7 @@
         <v>44687</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6229,7 +6229,7 @@
         <v>44868</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6302,7 +6302,7 @@
         <v>44879</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6380,7 +6380,7 @@
         <v>44879</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6453,7 +6453,7 @@
         <v>44879</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6526,7 +6526,7 @@
         <v>44483</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6599,7 +6599,7 @@
         <v>44789</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6677,7 +6677,7 @@
         <v>44593</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6755,7 +6755,7 @@
         <v>44698</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6828,7 +6828,7 @@
         <v>44538</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6901,7 +6901,7 @@
         <v>44650</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6974,7 +6974,7 @@
         <v>44827</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7052,7 +7052,7 @@
         <v>44728</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7125,7 +7125,7 @@
         <v>44743</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7198,7 +7198,7 @@
         <v>44516</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7271,7 +7271,7 @@
         <v>44816</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7344,7 +7344,7 @@
         <v>44538</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7417,7 +7417,7 @@
         <v>44874</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7490,7 +7490,7 @@
         <v>44531</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7563,7 +7563,7 @@
         <v>45371</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7636,7 +7636,7 @@
         <v>45145</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7709,7 +7709,7 @@
         <v>44868</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7787,7 +7787,7 @@
         <v>45264</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7860,7 +7860,7 @@
         <v>45153</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7933,7 +7933,7 @@
         <v>45419</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8006,7 +8006,7 @@
         <v>45272</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8084,7 +8084,7 @@
         <v>45077</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8157,7 +8157,7 @@
         <v>45737</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8230,7 +8230,7 @@
         <v>45580</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8303,7 +8303,7 @@
         <v>45701</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8376,7 +8376,7 @@
         <v>45665</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8449,7 +8449,7 @@
         <v>45748</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8522,7 +8522,7 @@
         <v>45365</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8595,7 +8595,7 @@
         <v>45090</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8673,7 +8673,7 @@
         <v>44994</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8746,7 +8746,7 @@
         <v>45208</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8819,7 +8819,7 @@
         <v>44796</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8892,7 +8892,7 @@
         <v>45216</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8965,7 +8965,7 @@
         <v>45216</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9038,7 +9038,7 @@
         <v>45595</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9111,7 +9111,7 @@
         <v>44483</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9184,7 +9184,7 @@
         <v>45698</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9257,7 +9257,7 @@
         <v>45701</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9330,7 +9330,7 @@
         <v>45414</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9403,7 +9403,7 @@
         <v>45355</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9476,7 +9476,7 @@
         <v>44480</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9549,7 +9549,7 @@
         <v>45664</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9622,7 +9622,7 @@
         <v>44916</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9695,7 +9695,7 @@
         <v>44572</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9768,7 +9768,7 @@
         <v>44987</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9841,7 +9841,7 @@
         <v>45596</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9914,7 +9914,7 @@
         <v>45085</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9987,7 +9987,7 @@
         <v>45474</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10060,7 +10060,7 @@
         <v>45460</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10133,7 +10133,7 @@
         <v>45414</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10206,7 +10206,7 @@
         <v>45666</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10279,7 +10279,7 @@
         <v>44994</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10352,7 +10352,7 @@
         <v>44831</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10425,7 +10425,7 @@
         <v>44635</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10498,7 +10498,7 @@
         <v>45587</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10576,7 +10576,7 @@
         <v>45273</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10649,7 +10649,7 @@
         <v>45665</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10722,7 +10722,7 @@
         <v>44530</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10795,7 +10795,7 @@
         <v>45335</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10868,7 +10868,7 @@
         <v>45110</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10941,7 +10941,7 @@
         <v>45218</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11014,7 +11014,7 @@
         <v>45889</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11087,7 +11087,7 @@
         <v>45236</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11160,7 +11160,7 @@
         <v>45891</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11233,7 +11233,7 @@
         <v>45898</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11306,7 +11306,7 @@
         <v>45714</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11379,7 +11379,7 @@
         <v>45597</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11452,7 +11452,7 @@
         <v>45054</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11525,7 +11525,7 @@
         <v>45170</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11598,7 +11598,7 @@
         <v>44844</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11671,7 +11671,7 @@
         <v>45677</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11744,7 +11744,7 @@
         <v>45707</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11817,7 +11817,7 @@
         <v>45432</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11890,7 +11890,7 @@
         <v>45638</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11963,7 +11963,7 @@
         <v>45414</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12036,7 +12036,7 @@
         <v>45414</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12109,7 +12109,7 @@
         <v>44491</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12187,7 +12187,7 @@
         <v>45110</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12260,7 +12260,7 @@
         <v>45398</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12333,7 +12333,7 @@
         <v>45647</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12406,7 +12406,7 @@
         <v>45909</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12484,7 +12484,7 @@
         <v>45649</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12557,7 +12557,7 @@
         <v>45909</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12635,7 +12635,7 @@
         <v>45475</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12708,7 +12708,7 @@
         <v>45110</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12781,7 +12781,7 @@
         <v>45910</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12854,7 +12854,7 @@
         <v>45468</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12927,7 +12927,7 @@
         <v>45492</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13000,7 +13000,7 @@
         <v>45138</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13073,7 +13073,7 @@
         <v>45916</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13146,7 +13146,7 @@
         <v>45916</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13224,7 +13224,7 @@
         <v>45218</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13297,7 +13297,7 @@
         <v>44504</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13370,7 +13370,7 @@
         <v>45666</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13443,7 +13443,7 @@
         <v>45916</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13521,7 +13521,7 @@
         <v>45355</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13594,7 +13594,7 @@
         <v>45916</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13672,7 +13672,7 @@
         <v>45159</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13745,7 +13745,7 @@
         <v>45558</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13818,7 +13818,7 @@
         <v>44908</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13891,7 +13891,7 @@
         <v>44908</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13964,7 +13964,7 @@
         <v>44651</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14037,7 +14037,7 @@
         <v>44503</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14115,7 +14115,7 @@
         <v>45583</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14188,7 +14188,7 @@
         <v>44624</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14261,7 +14261,7 @@
         <v>45475</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14334,7 +14334,7 @@
         <v>45922</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14407,7 +14407,7 @@
         <v>45510</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14480,7 +14480,7 @@
         <v>45714</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14553,7 +14553,7 @@
         <v>44966</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14626,7 +14626,7 @@
         <v>45355</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14699,7 +14699,7 @@
         <v>45924</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14777,7 +14777,7 @@
         <v>45924</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14850,7 +14850,7 @@
         <v>45544</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14923,7 +14923,7 @@
         <v>45719</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15001,7 +15001,7 @@
         <v>45436</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15074,7 +15074,7 @@
         <v>45099</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15147,7 +15147,7 @@
         <v>44606</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15220,7 +15220,7 @@
         <v>45365</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15293,7 +15293,7 @@
         <v>45170</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15366,7 +15366,7 @@
         <v>45796</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15439,7 +15439,7 @@
         <v>45104</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15512,7 +15512,7 @@
         <v>45796</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15585,7 +15585,7 @@
         <v>45931</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15658,7 +15658,7 @@
         <v>45054</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15731,7 +15731,7 @@
         <v>45931</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15804,7 +15804,7 @@
         <v>45726</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15877,7 +15877,7 @@
         <v>45932</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15950,7 +15950,7 @@
         <v>44490</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16023,7 +16023,7 @@
         <v>45105</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16096,7 +16096,7 @@
         <v>45000</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16169,7 +16169,7 @@
         <v>45194</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16242,7 +16242,7 @@
         <v>44651</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16315,7 +16315,7 @@
         <v>45239</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16388,7 +16388,7 @@
         <v>44655</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16461,7 +16461,7 @@
         <v>44994</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16534,7 +16534,7 @@
         <v>44994</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16607,7 +16607,7 @@
         <v>45762</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16680,7 +16680,7 @@
         <v>45940</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16758,7 +16758,7 @@
         <v>45938</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16836,7 +16836,7 @@
         <v>45940</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16914,7 +16914,7 @@
         <v>44994</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16987,7 +16987,7 @@
         <v>45575</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17060,7 +17060,7 @@
         <v>45600</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17138,7 +17138,7 @@
         <v>44789</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17216,7 +17216,7 @@
         <v>44576</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17289,7 +17289,7 @@
         <v>45758</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17362,7 +17362,7 @@
         <v>45434</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17435,7 +17435,7 @@
         <v>45273</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17508,7 +17508,7 @@
         <v>45821</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17586,7 +17586,7 @@
         <v>45701</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17659,7 +17659,7 @@
         <v>45460</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17732,7 +17732,7 @@
         <v>45831</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17805,7 +17805,7 @@
         <v>45831</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17878,7 +17878,7 @@
         <v>45831</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17951,7 +17951,7 @@
         <v>44743</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18024,7 +18024,7 @@
         <v>45831</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18097,7 +18097,7 @@
         <v>45954</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18175,7 +18175,7 @@
         <v>45954</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18253,7 +18253,7 @@
         <v>45666</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18326,7 +18326,7 @@
         <v>45119</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18404,7 +18404,7 @@
         <v>45964</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18482,7 +18482,7 @@
         <v>45664</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18555,7 +18555,7 @@
         <v>45964</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18633,7 +18633,7 @@
         <v>45964</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18711,7 +18711,7 @@
         <v>45965</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18789,7 +18789,7 @@
         <v>45965</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18867,7 +18867,7 @@
         <v>45159</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18940,7 +18940,7 @@
         <v>44966</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19013,7 +19013,7 @@
         <v>45965</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19086,7 +19086,7 @@
         <v>45965</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19159,7 +19159,7 @@
         <v>45965</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19237,7 +19237,7 @@
         <v>45965</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19315,7 +19315,7 @@
         <v>45965</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19393,7 +19393,7 @@
         <v>45965</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19466,7 +19466,7 @@
         <v>45838</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19544,7 +19544,7 @@
         <v>44749</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19617,7 +19617,7 @@
         <v>45414</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19690,7 +19690,7 @@
         <v>45714</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19763,7 +19763,7 @@
         <v>45575</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19836,7 +19836,7 @@
         <v>45790</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19909,7 +19909,7 @@
         <v>45096</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19982,7 +19982,7 @@
         <v>45810</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20055,7 +20055,7 @@
         <v>45596</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20128,7 +20128,7 @@
         <v>45016</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20206,7 +20206,7 @@
         <v>45278</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20279,7 +20279,7 @@
         <v>45634</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20352,7 +20352,7 @@
         <v>45649</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20425,7 +20425,7 @@
         <v>45736</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20503,7 +20503,7 @@
         <v>45666</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20576,7 +20576,7 @@
         <v>44816</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20649,7 +20649,7 @@
         <v>45769</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20722,7 +20722,7 @@
         <v>45170</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20795,7 +20795,7 @@
         <v>45692</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20868,7 +20868,7 @@
         <v>44711</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20946,7 +20946,7 @@
         <v>44562</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21019,7 +21019,7 @@
         <v>44670</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21092,7 +21092,7 @@
         <v>45091</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21170,7 +21170,7 @@
         <v>44502</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21243,7 +21243,7 @@
         <v>45302</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21316,7 +21316,7 @@
         <v>45310</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21389,7 +21389,7 @@
         <v>45707</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21462,7 +21462,7 @@
         <v>45231</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21535,7 +21535,7 @@
         <v>45261</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21608,7 +21608,7 @@
         <v>45261</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21681,7 +21681,7 @@
         <v>44894</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21754,7 +21754,7 @@
         <v>44980</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21827,7 +21827,7 @@
         <v>44939</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21900,7 +21900,7 @@
         <v>45537</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21973,7 +21973,7 @@
         <v>45334</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -22046,7 +22046,7 @@
         <v>46099</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22119,7 +22119,7 @@
         <v>46101</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22192,7 +22192,7 @@
         <v>46101</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22265,7 +22265,7 @@
         <v>45194</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22338,7 +22338,7 @@
         <v>44538</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22411,7 +22411,7 @@
         <v>44987</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22484,7 +22484,7 @@
         <v>46106</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22557,7 +22557,7 @@
         <v>45634</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22630,7 +22630,7 @@
         <v>45671</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22703,7 +22703,7 @@
         <v>44980</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22776,7 +22776,7 @@
         <v>45406</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22849,7 +22849,7 @@
         <v>44965</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22922,7 +22922,7 @@
         <v>44908</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -22995,7 +22995,7 @@
         <v>44480</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -23073,7 +23073,7 @@
         <v>46116</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23146,7 +23146,7 @@
         <v>45994</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23219,7 +23219,7 @@
         <v>46119</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23292,7 +23292,7 @@
         <v>46119</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23365,7 +23365,7 @@
         <v>46121</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23438,7 +23438,7 @@
         <v>44908</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23511,7 +23511,7 @@
         <v>45994</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23584,7 +23584,7 @@
         <v>46125</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23657,7 +23657,7 @@
         <v>46125</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23730,7 +23730,7 @@
         <v>45965</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23803,7 +23803,7 @@
         <v>46126</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23876,7 +23876,7 @@
         <v>45194</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -23949,7 +23949,7 @@
         <v>45335</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -24022,7 +24022,7 @@
         <v>45257</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -24095,7 +24095,7 @@
         <v>44592</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24168,7 +24168,7 @@
         <v>46006</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24241,7 +24241,7 @@
         <v>44953</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24314,7 +24314,7 @@
         <v>45246</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24392,7 +24392,7 @@
         <v>46006</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24465,7 +24465,7 @@
         <v>44903</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24538,7 +24538,7 @@
         <v>45841</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24611,7 +24611,7 @@
         <v>46007</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24684,7 +24684,7 @@
         <v>46007</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24757,7 +24757,7 @@
         <v>45965</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24830,7 +24830,7 @@
         <v>46007</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -24903,7 +24903,7 @@
         <v>46007</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -24976,7 +24976,7 @@
         <v>45871</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -25049,7 +25049,7 @@
         <v>46010</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25122,7 +25122,7 @@
         <v>45348</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25195,7 +25195,7 @@
         <v>45831</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25268,7 +25268,7 @@
         <v>44600</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25341,7 +25341,7 @@
         <v>45428</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25414,7 +25414,7 @@
         <v>45831</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25487,7 +25487,7 @@
         <v>45793</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25560,7 +25560,7 @@
         <v>45917</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25633,7 +25633,7 @@
         <v>45831</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25706,7 +25706,7 @@
         <v>46013</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25779,7 +25779,7 @@
         <v>46013</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -25852,7 +25852,7 @@
         <v>46013</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -25925,7 +25925,7 @@
         <v>46021</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -25998,7 +25998,7 @@
         <v>44480</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -26096,7 +26096,7 @@
         <v>45916</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -26169,7 +26169,7 @@
         <v>44501</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -26242,7 +26242,7 @@
         <v>44536</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -26315,7 +26315,7 @@
         <v>46036</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -26388,7 +26388,7 @@
         <v>45096</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -26461,7 +26461,7 @@
         <v>45616</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26534,7 +26534,7 @@
         <v>46044</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26612,7 +26612,7 @@
         <v>44953</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26685,7 +26685,7 @@
         <v>44980</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -26758,7 +26758,7 @@
         <v>46045</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -26836,7 +26836,7 @@
         <v>46045</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -26914,7 +26914,7 @@
         <v>45910</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -26987,7 +26987,7 @@
         <v>45701</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -27060,7 +27060,7 @@
         <v>46055</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -27133,7 +27133,7 @@
         <v>46058</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -27206,7 +27206,7 @@
         <v>46062</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -27284,7 +27284,7 @@
         <v>46146</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -27357,7 +27357,7 @@
         <v>46146</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -27430,7 +27430,7 @@
         <v>46146</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -27503,7 +27503,7 @@
         <v>46146</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -27576,7 +27576,7 @@
         <v>46146</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -27649,7 +27649,7 @@
         <v>46146</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -27722,7 +27722,7 @@
         <v>46069</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -27795,7 +27795,7 @@
         <v>46069</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -27873,7 +27873,7 @@
         <v>46071</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -27951,7 +27951,7 @@
         <v>46154</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -28029,7 +28029,7 @@
         <v>46153</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -28107,7 +28107,7 @@
         <v>46029</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -28180,7 +28180,7 @@
         <v>46038</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -28258,7 +28258,7 @@
         <v>45965</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -28336,7 +28336,7 @@
         <v>46171</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -28414,7 +28414,7 @@
         <v>46177</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -28492,7 +28492,7 @@
         <v>46183</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -28570,7 +28570,7 @@
         <v>46191</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -28643,7 +28643,7 @@
         <v>46190</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -28716,7 +28716,7 @@
         <v>46202</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -28789,7 +28789,7 @@
         <v>46202</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -28862,7 +28862,7 @@
         <v>46202</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -28935,7 +28935,7 @@
         <v>46202</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -29008,7 +29008,7 @@
         <v>46202</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -29081,7 +29081,7 @@
         <v>45755</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -29154,7 +29154,7 @@
         <v>45831</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -29227,7 +29227,7 @@
         <v>46269</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -29300,7 +29300,7 @@
         <v>46269</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -29373,7 +29373,7 @@
         <v>46273</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -29446,7 +29446,7 @@
         <v>46273</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -29519,7 +29519,7 @@
         <v>46273</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -29592,7 +29592,7 @@
         <v>46275</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -29665,7 +29665,7 @@
         <v>46280</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -29738,7 +29738,7 @@
         <v>46282</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -29811,7 +29811,7 @@
         <v>46282</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -29884,7 +29884,7 @@
         <v>46282</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -29957,7 +29957,7 @@
         <v>46282</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -30030,7 +30030,7 @@
         <v>46282</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -30103,7 +30103,7 @@
         <v>46282</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -30176,7 +30176,7 @@
         <v>46240</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -30249,7 +30249,7 @@
         <v>46283</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -30327,7 +30327,7 @@
         <v>46283</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -30405,7 +30405,7 @@
         <v>46286</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -30483,7 +30483,7 @@
         <v>46286</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -30561,7 +30561,7 @@
         <v>46240</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -30634,7 +30634,7 @@
         <v>46283</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -30712,7 +30712,7 @@
         <v>46283</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -30790,7 +30790,7 @@
         <v>46283</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -30868,7 +30868,7 @@
         <v>46290</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -30941,7 +30941,7 @@
         <v>46290</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -31014,7 +31014,7 @@
         <v>45831</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -31087,7 +31087,7 @@
         <v>46258</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -31160,7 +31160,7 @@
         <v>46097</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -31233,7 +31233,7 @@
         <v>45831</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -31306,7 +31306,7 @@
         <v>46303</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -31379,7 +31379,7 @@
         <v>46303</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -31452,7 +31452,7 @@
         <v>46304</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -31525,7 +31525,7 @@
         <v>46304</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -31598,7 +31598,7 @@
         <v>45994</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -31671,7 +31671,7 @@
         <v>44585</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -31744,7 +31744,7 @@
         <v>45839</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -31822,7 +31822,7 @@
         <v>45916</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -31900,7 +31900,7 @@
         <v>45964</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -31973,7 +31973,7 @@
         <v>46066</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -32046,7 +32046,7 @@
         <v>46287</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>

--- a/Översikt YDRE.xlsx
+++ b/Översikt YDRE.xlsx
@@ -601,7 +601,7 @@
         <v>44503</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -729,7 +729,7 @@
         <v>45153</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -848,7 +848,7 @@
         <v>44621</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -957,7 +957,7 @@
         <v>46282</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>45378</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1184,7 +1184,7 @@
         <v>45954</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1301,7 +1301,7 @@
         <v>45198</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1412,7 +1412,7 @@
         <v>45709</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1519,7 +1519,7 @@
         <v>46189</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1626,7 +1626,7 @@
         <v>45883</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1738,7 +1738,7 @@
         <v>44509</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1844,7 +1844,7 @@
         <v>44789</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1955,7 +1955,7 @@
         <v>44874</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2061,7 +2061,7 @@
         <v>45348</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2167,7 +2167,7 @@
         <v>44732</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2278,7 +2278,7 @@
         <v>45611</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2393,7 +2393,7 @@
         <v>45091</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2504,7 +2504,7 @@
         <v>45251</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2614,7 +2614,7 @@
         <v>45415</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2720,7 +2720,7 @@
         <v>45792</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2826,7 +2826,7 @@
         <v>45973</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2937,7 +2937,7 @@
         <v>45614</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3048,7 +3048,7 @@
         <v>45846</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3159,7 +3159,7 @@
         <v>44515</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3264,7 +3264,7 @@
         <v>44858</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3374,7 +3374,7 @@
         <v>45371</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3479,7 +3479,7 @@
         <v>45611</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3589,7 +3589,7 @@
         <v>45561</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3694,7 +3694,7 @@
         <v>45916</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3799,7 +3799,7 @@
         <v>45922</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3904,7 +3904,7 @@
         <v>45964</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4014,7 +4014,7 @@
         <v>45192</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4119,7 +4119,7 @@
         <v>45965</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4228,7 +4228,7 @@
         <v>45769</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4333,7 +4333,7 @@
         <v>45733</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4438,7 +4438,7 @@
         <v>45754</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4543,7 +4543,7 @@
         <v>45922</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4648,7 +4648,7 @@
         <v>45727</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4753,7 +4753,7 @@
         <v>46045</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4867,7 +4867,7 @@
         <v>46069</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4972,7 +4972,7 @@
         <v>46069</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5082,7 +5082,7 @@
         <v>46202</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5187,7 +5187,7 @@
         <v>45777</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5292,7 +5292,7 @@
         <v>46075</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5401,7 +5401,7 @@
         <v>44582</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5474,7 +5474,7 @@
         <v>44508</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5547,7 +5547,7 @@
         <v>44693</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5620,7 +5620,7 @@
         <v>44827</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5698,7 +5698,7 @@
         <v>44491</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5776,7 +5776,7 @@
         <v>44585</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5849,7 +5849,7 @@
         <v>44502</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5922,7 +5922,7 @@
         <v>44820</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5995,7 +5995,7 @@
         <v>44827</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6073,7 +6073,7 @@
         <v>44503</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6151,7 +6151,7 @@
         <v>44687</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6229,7 +6229,7 @@
         <v>44868</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6302,7 +6302,7 @@
         <v>44879</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6380,7 +6380,7 @@
         <v>44879</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6453,7 +6453,7 @@
         <v>44879</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6526,7 +6526,7 @@
         <v>44483</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6599,7 +6599,7 @@
         <v>44789</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6677,7 +6677,7 @@
         <v>44593</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6755,7 +6755,7 @@
         <v>44698</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6828,7 +6828,7 @@
         <v>44538</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6901,7 +6901,7 @@
         <v>44650</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6974,7 +6974,7 @@
         <v>44827</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7052,7 +7052,7 @@
         <v>44728</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7125,7 +7125,7 @@
         <v>44743</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7198,7 +7198,7 @@
         <v>44516</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7271,7 +7271,7 @@
         <v>44816</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7344,7 +7344,7 @@
         <v>44538</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7417,7 +7417,7 @@
         <v>44874</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7490,7 +7490,7 @@
         <v>44531</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7563,7 +7563,7 @@
         <v>45371</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7636,7 +7636,7 @@
         <v>45145</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7709,7 +7709,7 @@
         <v>44868</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7787,7 +7787,7 @@
         <v>45264</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7860,7 +7860,7 @@
         <v>45153</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7933,7 +7933,7 @@
         <v>45419</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8006,7 +8006,7 @@
         <v>45272</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8084,7 +8084,7 @@
         <v>45077</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8157,7 +8157,7 @@
         <v>45737</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8230,7 +8230,7 @@
         <v>45580</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8303,7 +8303,7 @@
         <v>45701</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8376,7 +8376,7 @@
         <v>45665</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8449,7 +8449,7 @@
         <v>45748</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8522,7 +8522,7 @@
         <v>45365</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8595,7 +8595,7 @@
         <v>45090</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8673,7 +8673,7 @@
         <v>44994</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8746,7 +8746,7 @@
         <v>45208</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8819,7 +8819,7 @@
         <v>44796</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8892,7 +8892,7 @@
         <v>45216</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8965,7 +8965,7 @@
         <v>45216</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9038,7 +9038,7 @@
         <v>45595</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9111,7 +9111,7 @@
         <v>44483</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9184,7 +9184,7 @@
         <v>45698</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9257,7 +9257,7 @@
         <v>45701</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9330,7 +9330,7 @@
         <v>45414</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9403,7 +9403,7 @@
         <v>45355</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9476,7 +9476,7 @@
         <v>44480</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9549,7 +9549,7 @@
         <v>45664</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9622,7 +9622,7 @@
         <v>44916</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9695,7 +9695,7 @@
         <v>44572</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9768,7 +9768,7 @@
         <v>44987</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9841,7 +9841,7 @@
         <v>45596</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9914,7 +9914,7 @@
         <v>45085</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9987,7 +9987,7 @@
         <v>45474</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10060,7 +10060,7 @@
         <v>45460</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10133,7 +10133,7 @@
         <v>45414</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10206,7 +10206,7 @@
         <v>45666</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10279,7 +10279,7 @@
         <v>44994</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10352,7 +10352,7 @@
         <v>44831</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10425,7 +10425,7 @@
         <v>44635</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10498,7 +10498,7 @@
         <v>45587</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10576,7 +10576,7 @@
         <v>45273</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10649,7 +10649,7 @@
         <v>45665</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10722,7 +10722,7 @@
         <v>44530</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10795,7 +10795,7 @@
         <v>45335</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10868,7 +10868,7 @@
         <v>45110</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10941,7 +10941,7 @@
         <v>45218</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11014,7 +11014,7 @@
         <v>45889</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11087,7 +11087,7 @@
         <v>45236</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11160,7 +11160,7 @@
         <v>45891</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11233,7 +11233,7 @@
         <v>45898</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11306,7 +11306,7 @@
         <v>45714</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11379,7 +11379,7 @@
         <v>45597</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11452,7 +11452,7 @@
         <v>45054</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11525,7 +11525,7 @@
         <v>45170</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11598,7 +11598,7 @@
         <v>44844</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11671,7 +11671,7 @@
         <v>45677</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11744,7 +11744,7 @@
         <v>45707</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11817,7 +11817,7 @@
         <v>45432</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11890,7 +11890,7 @@
         <v>45638</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11963,7 +11963,7 @@
         <v>45414</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12036,7 +12036,7 @@
         <v>45414</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12109,7 +12109,7 @@
         <v>44491</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12187,7 +12187,7 @@
         <v>45110</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12260,7 +12260,7 @@
         <v>45398</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12333,7 +12333,7 @@
         <v>45647</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12406,7 +12406,7 @@
         <v>45909</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12484,7 +12484,7 @@
         <v>45649</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12557,7 +12557,7 @@
         <v>45909</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12635,7 +12635,7 @@
         <v>45475</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12708,7 +12708,7 @@
         <v>45110</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12781,7 +12781,7 @@
         <v>45910</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12854,7 +12854,7 @@
         <v>45468</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12927,7 +12927,7 @@
         <v>45492</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13000,7 +13000,7 @@
         <v>45138</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13073,7 +13073,7 @@
         <v>45916</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13146,7 +13146,7 @@
         <v>45916</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13224,7 +13224,7 @@
         <v>45218</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13297,7 +13297,7 @@
         <v>44504</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13370,7 +13370,7 @@
         <v>45666</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13443,7 +13443,7 @@
         <v>45916</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13521,7 +13521,7 @@
         <v>45355</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13594,7 +13594,7 @@
         <v>45916</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13672,7 +13672,7 @@
         <v>45159</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13745,7 +13745,7 @@
         <v>45558</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13818,7 +13818,7 @@
         <v>44908</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13891,7 +13891,7 @@
         <v>44908</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13964,7 +13964,7 @@
         <v>44651</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14037,7 +14037,7 @@
         <v>44503</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14115,7 +14115,7 @@
         <v>45583</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14188,7 +14188,7 @@
         <v>44624</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14261,7 +14261,7 @@
         <v>45475</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14334,7 +14334,7 @@
         <v>45922</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14407,7 +14407,7 @@
         <v>45510</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14480,7 +14480,7 @@
         <v>45714</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14553,7 +14553,7 @@
         <v>44966</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14626,7 +14626,7 @@
         <v>45355</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14699,7 +14699,7 @@
         <v>45924</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14777,7 +14777,7 @@
         <v>45924</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14850,7 +14850,7 @@
         <v>45544</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14923,7 +14923,7 @@
         <v>45719</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15001,7 +15001,7 @@
         <v>45436</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15074,7 +15074,7 @@
         <v>45099</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15147,7 +15147,7 @@
         <v>44606</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15220,7 +15220,7 @@
         <v>45365</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15293,7 +15293,7 @@
         <v>45170</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15366,7 +15366,7 @@
         <v>45796</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15439,7 +15439,7 @@
         <v>45104</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15512,7 +15512,7 @@
         <v>45796</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15585,7 +15585,7 @@
         <v>45931</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15658,7 +15658,7 @@
         <v>45054</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15731,7 +15731,7 @@
         <v>45931</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15804,7 +15804,7 @@
         <v>45726</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15877,7 +15877,7 @@
         <v>45932</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15950,7 +15950,7 @@
         <v>44490</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16023,7 +16023,7 @@
         <v>45105</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16096,7 +16096,7 @@
         <v>45000</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16169,7 +16169,7 @@
         <v>45194</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16242,7 +16242,7 @@
         <v>44651</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16315,7 +16315,7 @@
         <v>45239</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16388,7 +16388,7 @@
         <v>44655</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16461,7 +16461,7 @@
         <v>44994</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16534,7 +16534,7 @@
         <v>44994</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16607,7 +16607,7 @@
         <v>45762</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16680,7 +16680,7 @@
         <v>45940</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16758,7 +16758,7 @@
         <v>45938</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16836,7 +16836,7 @@
         <v>45940</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16914,7 +16914,7 @@
         <v>44994</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16987,7 +16987,7 @@
         <v>45575</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17060,7 +17060,7 @@
         <v>45600</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17138,7 +17138,7 @@
         <v>44789</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17216,7 +17216,7 @@
         <v>44576</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17289,7 +17289,7 @@
         <v>45758</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17362,7 +17362,7 @@
         <v>45434</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17435,7 +17435,7 @@
         <v>45273</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17508,7 +17508,7 @@
         <v>45821</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17586,7 +17586,7 @@
         <v>45701</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17659,7 +17659,7 @@
         <v>45460</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17732,7 +17732,7 @@
         <v>45831</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17805,7 +17805,7 @@
         <v>45831</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17878,7 +17878,7 @@
         <v>45831</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17951,7 +17951,7 @@
         <v>44743</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18024,7 +18024,7 @@
         <v>45831</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18097,7 +18097,7 @@
         <v>45954</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18175,7 +18175,7 @@
         <v>45954</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18253,7 +18253,7 @@
         <v>45666</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18326,7 +18326,7 @@
         <v>45119</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18404,7 +18404,7 @@
         <v>45964</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18482,7 +18482,7 @@
         <v>45664</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18555,7 +18555,7 @@
         <v>45964</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18633,7 +18633,7 @@
         <v>45964</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18711,7 +18711,7 @@
         <v>45965</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18789,7 +18789,7 @@
         <v>45965</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18867,7 +18867,7 @@
         <v>45159</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18940,7 +18940,7 @@
         <v>44966</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19013,7 +19013,7 @@
         <v>45965</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19086,7 +19086,7 @@
         <v>45965</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19159,7 +19159,7 @@
         <v>45965</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19237,7 +19237,7 @@
         <v>45965</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19315,7 +19315,7 @@
         <v>45965</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19393,7 +19393,7 @@
         <v>45965</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19466,7 +19466,7 @@
         <v>45838</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19544,7 +19544,7 @@
         <v>44749</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19617,7 +19617,7 @@
         <v>45414</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19690,7 +19690,7 @@
         <v>45714</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19763,7 +19763,7 @@
         <v>45575</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19836,7 +19836,7 @@
         <v>45790</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19909,7 +19909,7 @@
         <v>45096</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19982,7 +19982,7 @@
         <v>45810</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20055,7 +20055,7 @@
         <v>45596</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20128,7 +20128,7 @@
         <v>45016</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20206,7 +20206,7 @@
         <v>45278</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20279,7 +20279,7 @@
         <v>45634</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20352,7 +20352,7 @@
         <v>45649</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20425,7 +20425,7 @@
         <v>45736</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20503,7 +20503,7 @@
         <v>45666</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20576,7 +20576,7 @@
         <v>44816</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20649,7 +20649,7 @@
         <v>45769</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20722,7 +20722,7 @@
         <v>45170</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20795,7 +20795,7 @@
         <v>45692</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20868,7 +20868,7 @@
         <v>44711</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20946,7 +20946,7 @@
         <v>44562</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21019,7 +21019,7 @@
         <v>44670</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21092,7 +21092,7 @@
         <v>45091</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21170,7 +21170,7 @@
         <v>44502</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21243,7 +21243,7 @@
         <v>45302</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21316,7 +21316,7 @@
         <v>45310</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21389,7 +21389,7 @@
         <v>45707</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21462,7 +21462,7 @@
         <v>45231</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21535,7 +21535,7 @@
         <v>45261</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21608,7 +21608,7 @@
         <v>45261</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21681,7 +21681,7 @@
         <v>44894</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21754,7 +21754,7 @@
         <v>44980</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21827,7 +21827,7 @@
         <v>44939</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21900,7 +21900,7 @@
         <v>45537</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21973,7 +21973,7 @@
         <v>45334</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -22046,7 +22046,7 @@
         <v>46099</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22119,7 +22119,7 @@
         <v>46101</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22192,7 +22192,7 @@
         <v>46101</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22265,7 +22265,7 @@
         <v>45194</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22338,7 +22338,7 @@
         <v>44538</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22411,7 +22411,7 @@
         <v>44987</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22484,7 +22484,7 @@
         <v>46106</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22557,7 +22557,7 @@
         <v>45634</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22630,7 +22630,7 @@
         <v>45671</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22703,7 +22703,7 @@
         <v>44980</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22776,7 +22776,7 @@
         <v>45406</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22849,7 +22849,7 @@
         <v>44965</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22922,7 +22922,7 @@
         <v>44908</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -22995,7 +22995,7 @@
         <v>44480</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -23073,7 +23073,7 @@
         <v>46116</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23146,7 +23146,7 @@
         <v>45994</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23219,7 +23219,7 @@
         <v>46119</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23292,7 +23292,7 @@
         <v>46119</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23365,7 +23365,7 @@
         <v>46121</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23438,7 +23438,7 @@
         <v>44908</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23511,7 +23511,7 @@
         <v>45994</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23584,7 +23584,7 @@
         <v>46125</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23657,7 +23657,7 @@
         <v>46125</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23730,7 +23730,7 @@
         <v>45965</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23803,7 +23803,7 @@
         <v>46126</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23876,7 +23876,7 @@
         <v>45194</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -23949,7 +23949,7 @@
         <v>45335</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -24022,7 +24022,7 @@
         <v>45257</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -24095,7 +24095,7 @@
         <v>44592</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24168,7 +24168,7 @@
         <v>46006</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24241,7 +24241,7 @@
         <v>44953</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24314,7 +24314,7 @@
         <v>45246</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24392,7 +24392,7 @@
         <v>46006</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24465,7 +24465,7 @@
         <v>44903</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24538,7 +24538,7 @@
         <v>45841</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24611,7 +24611,7 @@
         <v>46007</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24684,7 +24684,7 @@
         <v>46007</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24757,7 +24757,7 @@
         <v>45965</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24830,7 +24830,7 @@
         <v>46007</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -24903,7 +24903,7 @@
         <v>46007</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -24976,7 +24976,7 @@
         <v>45871</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -25049,7 +25049,7 @@
         <v>46010</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25122,7 +25122,7 @@
         <v>45348</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25195,7 +25195,7 @@
         <v>45831</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25268,7 +25268,7 @@
         <v>44600</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25341,7 +25341,7 @@
         <v>45428</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25414,7 +25414,7 @@
         <v>45831</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25487,7 +25487,7 @@
         <v>45793</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25560,7 +25560,7 @@
         <v>45917</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25633,7 +25633,7 @@
         <v>45831</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25706,7 +25706,7 @@
         <v>46013</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25779,7 +25779,7 @@
         <v>46013</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -25852,7 +25852,7 @@
         <v>46013</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -25925,7 +25925,7 @@
         <v>46021</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -25998,7 +25998,7 @@
         <v>44480</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -26096,7 +26096,7 @@
         <v>45916</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -26169,7 +26169,7 @@
         <v>44501</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -26242,7 +26242,7 @@
         <v>44536</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -26315,7 +26315,7 @@
         <v>46036</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -26388,7 +26388,7 @@
         <v>45096</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -26461,7 +26461,7 @@
         <v>45616</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26534,7 +26534,7 @@
         <v>46044</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26612,7 +26612,7 @@
         <v>44953</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26685,7 +26685,7 @@
         <v>44980</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -26758,7 +26758,7 @@
         <v>46045</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -26836,7 +26836,7 @@
         <v>46045</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -26914,7 +26914,7 @@
         <v>45910</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -26987,7 +26987,7 @@
         <v>45701</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -27060,7 +27060,7 @@
         <v>46055</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -27133,7 +27133,7 @@
         <v>46058</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -27206,7 +27206,7 @@
         <v>46062</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -27284,7 +27284,7 @@
         <v>46146</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -27357,7 +27357,7 @@
         <v>46146</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -27430,7 +27430,7 @@
         <v>46146</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -27503,7 +27503,7 @@
         <v>46146</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -27576,7 +27576,7 @@
         <v>46146</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -27649,7 +27649,7 @@
         <v>46146</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -27722,7 +27722,7 @@
         <v>46069</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -27795,7 +27795,7 @@
         <v>46069</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -27873,7 +27873,7 @@
         <v>46071</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -27951,7 +27951,7 @@
         <v>46154</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -28029,7 +28029,7 @@
         <v>46153</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -28107,7 +28107,7 @@
         <v>46029</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -28180,7 +28180,7 @@
         <v>46038</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -28258,7 +28258,7 @@
         <v>45965</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -28336,7 +28336,7 @@
         <v>46171</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -28414,7 +28414,7 @@
         <v>46177</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -28492,7 +28492,7 @@
         <v>46183</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -28570,7 +28570,7 @@
         <v>46191</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -28643,7 +28643,7 @@
         <v>46190</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -28716,7 +28716,7 @@
         <v>46202</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -28789,7 +28789,7 @@
         <v>46202</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -28862,7 +28862,7 @@
         <v>46202</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -28935,7 +28935,7 @@
         <v>46202</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -29008,7 +29008,7 @@
         <v>46202</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -29081,7 +29081,7 @@
         <v>45755</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -29154,7 +29154,7 @@
         <v>45831</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -29227,7 +29227,7 @@
         <v>46269</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -29300,7 +29300,7 @@
         <v>46269</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -29373,7 +29373,7 @@
         <v>46273</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -29446,7 +29446,7 @@
         <v>46273</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -29519,7 +29519,7 @@
         <v>46273</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -29592,7 +29592,7 @@
         <v>46275</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -29665,7 +29665,7 @@
         <v>46280</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -29738,7 +29738,7 @@
         <v>46282</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -29811,7 +29811,7 @@
         <v>46282</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -29884,7 +29884,7 @@
         <v>46282</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -29957,7 +29957,7 @@
         <v>46282</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -30030,7 +30030,7 @@
         <v>46282</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -30103,7 +30103,7 @@
         <v>46282</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -30176,7 +30176,7 @@
         <v>46240</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -30249,7 +30249,7 @@
         <v>46283</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -30327,7 +30327,7 @@
         <v>46283</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -30405,7 +30405,7 @@
         <v>46286</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -30483,7 +30483,7 @@
         <v>46286</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -30561,7 +30561,7 @@
         <v>46240</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -30634,7 +30634,7 @@
         <v>46283</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -30712,7 +30712,7 @@
         <v>46283</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -30790,7 +30790,7 @@
         <v>46283</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -30868,7 +30868,7 @@
         <v>46290</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -30941,7 +30941,7 @@
         <v>46290</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -31014,7 +31014,7 @@
         <v>45831</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -31087,7 +31087,7 @@
         <v>46258</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -31160,7 +31160,7 @@
         <v>46097</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -31233,7 +31233,7 @@
         <v>45831</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -31306,7 +31306,7 @@
         <v>46303</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -31379,7 +31379,7 @@
         <v>46303</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -31452,7 +31452,7 @@
         <v>46304</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -31525,7 +31525,7 @@
         <v>46304</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -31598,7 +31598,7 @@
         <v>45994</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -31671,7 +31671,7 @@
         <v>44585</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -31744,7 +31744,7 @@
         <v>45839</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -31822,7 +31822,7 @@
         <v>45916</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -31900,7 +31900,7 @@
         <v>45964</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -31973,7 +31973,7 @@
         <v>46066</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -32046,7 +32046,7 @@
         <v>46287</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>

--- a/Översikt YDRE.xlsx
+++ b/Översikt YDRE.xlsx
@@ -601,7 +601,7 @@
         <v>44503</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -729,7 +729,7 @@
         <v>45153</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -848,7 +848,7 @@
         <v>44621</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -957,7 +957,7 @@
         <v>46282</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>45378</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1184,7 +1184,7 @@
         <v>45954</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1301,7 +1301,7 @@
         <v>45709</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1408,7 +1408,7 @@
         <v>45198</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1519,7 +1519,7 @@
         <v>46189</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1626,7 +1626,7 @@
         <v>45883</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1738,7 +1738,7 @@
         <v>44509</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1844,7 +1844,7 @@
         <v>45091</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1955,7 +1955,7 @@
         <v>44789</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2066,7 +2066,7 @@
         <v>45973</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2177,7 +2177,7 @@
         <v>45415</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2283,7 +2283,7 @@
         <v>45348</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2389,7 +2389,7 @@
         <v>45611</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2504,7 +2504,7 @@
         <v>45251</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2614,7 +2614,7 @@
         <v>44874</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2720,7 +2720,7 @@
         <v>44732</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2831,7 +2831,7 @@
         <v>45792</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2937,7 +2937,7 @@
         <v>45614</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3048,7 +3048,7 @@
         <v>45846</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3159,7 +3159,7 @@
         <v>44515</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3264,7 +3264,7 @@
         <v>44858</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3374,7 +3374,7 @@
         <v>45727</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3479,7 +3479,7 @@
         <v>45922</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3584,7 +3584,7 @@
         <v>45769</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3689,7 +3689,7 @@
         <v>45916</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3794,7 +3794,7 @@
         <v>45922</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3899,7 +3899,7 @@
         <v>45611</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4009,7 +4009,7 @@
         <v>45371</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4114,7 +4114,7 @@
         <v>45965</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4223,7 +4223,7 @@
         <v>45964</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4333,7 +4333,7 @@
         <v>45561</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4438,7 +4438,7 @@
         <v>45754</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4543,7 +4543,7 @@
         <v>46045</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4657,7 +4657,7 @@
         <v>46069</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4762,7 +4762,7 @@
         <v>46069</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4872,7 +4872,7 @@
         <v>45733</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4977,7 +4977,7 @@
         <v>46202</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5082,7 +5082,7 @@
         <v>45192</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5187,7 +5187,7 @@
         <v>45777</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5292,7 +5292,7 @@
         <v>46075</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5401,7 +5401,7 @@
         <v>44582</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5474,7 +5474,7 @@
         <v>44508</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5547,7 +5547,7 @@
         <v>44693</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5620,7 +5620,7 @@
         <v>44827</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5698,7 +5698,7 @@
         <v>44491</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5776,7 +5776,7 @@
         <v>44585</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5849,7 +5849,7 @@
         <v>44502</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5922,7 +5922,7 @@
         <v>44820</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5995,7 +5995,7 @@
         <v>44827</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6073,7 +6073,7 @@
         <v>44687</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6151,7 +6151,7 @@
         <v>44503</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6229,7 +6229,7 @@
         <v>44868</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6302,7 +6302,7 @@
         <v>44879</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6380,7 +6380,7 @@
         <v>44879</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6453,7 +6453,7 @@
         <v>44879</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6526,7 +6526,7 @@
         <v>44789</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6604,7 +6604,7 @@
         <v>44516</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6677,7 +6677,7 @@
         <v>44816</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6750,7 +6750,7 @@
         <v>44538</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6823,7 +6823,7 @@
         <v>44728</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6896,7 +6896,7 @@
         <v>44593</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6974,7 +6974,7 @@
         <v>44698</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7047,7 +7047,7 @@
         <v>44650</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7120,7 +7120,7 @@
         <v>44827</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7198,7 +7198,7 @@
         <v>44743</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7271,7 +7271,7 @@
         <v>44538</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7344,7 +7344,7 @@
         <v>44531</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7417,7 +7417,7 @@
         <v>45432</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7490,7 +7490,7 @@
         <v>45597</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7563,7 +7563,7 @@
         <v>45110</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7636,7 +7636,7 @@
         <v>45664</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7709,7 +7709,7 @@
         <v>44606</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7782,7 +7782,7 @@
         <v>44538</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7855,7 +7855,7 @@
         <v>45110</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7928,7 +7928,7 @@
         <v>45714</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8001,7 +8001,7 @@
         <v>45596</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8074,7 +8074,7 @@
         <v>45665</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8147,7 +8147,7 @@
         <v>45138</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8220,7 +8220,7 @@
         <v>45665</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8293,7 +8293,7 @@
         <v>45666</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8366,7 +8366,7 @@
         <v>45707</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8439,7 +8439,7 @@
         <v>45355</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8512,7 +8512,7 @@
         <v>45355</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8585,7 +8585,7 @@
         <v>44903</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8658,7 +8658,7 @@
         <v>44796</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8731,7 +8731,7 @@
         <v>45231</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8804,7 +8804,7 @@
         <v>45208</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8877,7 +8877,7 @@
         <v>44592</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8950,7 +8950,7 @@
         <v>45701</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9023,7 +9023,7 @@
         <v>45335</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9096,7 +9096,7 @@
         <v>45596</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9169,7 +9169,7 @@
         <v>45261</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9242,7 +9242,7 @@
         <v>45419</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9315,7 +9315,7 @@
         <v>45236</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9388,7 +9388,7 @@
         <v>45000</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9461,7 +9461,7 @@
         <v>45355</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9534,7 +9534,7 @@
         <v>45414</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9607,7 +9607,7 @@
         <v>45475</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9680,7 +9680,7 @@
         <v>45105</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9753,7 +9753,7 @@
         <v>45170</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9826,7 +9826,7 @@
         <v>45170</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9899,7 +9899,7 @@
         <v>44504</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9972,7 +9972,7 @@
         <v>45278</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10045,7 +10045,7 @@
         <v>44503</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10123,7 +10123,7 @@
         <v>44980</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10196,7 +10196,7 @@
         <v>44831</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10269,7 +10269,7 @@
         <v>44743</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10342,7 +10342,7 @@
         <v>44749</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10415,7 +10415,7 @@
         <v>45434</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10488,7 +10488,7 @@
         <v>45218</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10561,7 +10561,7 @@
         <v>45510</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10634,7 +10634,7 @@
         <v>45194</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10707,7 +10707,7 @@
         <v>45216</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10780,7 +10780,7 @@
         <v>45216</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10853,7 +10853,7 @@
         <v>45666</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10926,7 +10926,7 @@
         <v>45119</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11004,7 +11004,7 @@
         <v>44966</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11077,7 +11077,7 @@
         <v>45831</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11150,7 +11150,7 @@
         <v>45917</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11223,7 +11223,7 @@
         <v>45616</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11296,7 +11296,7 @@
         <v>44939</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11369,7 +11369,7 @@
         <v>45910</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11442,7 +11442,7 @@
         <v>45889</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11515,7 +11515,7 @@
         <v>44994</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11588,7 +11588,7 @@
         <v>45965</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11661,7 +11661,7 @@
         <v>45891</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11734,7 +11734,7 @@
         <v>45871</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11807,7 +11807,7 @@
         <v>44980</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11880,7 +11880,7 @@
         <v>45091</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11958,7 +11958,7 @@
         <v>45831</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12031,7 +12031,7 @@
         <v>45793</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12104,7 +12104,7 @@
         <v>45246</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12182,7 +12182,7 @@
         <v>45841</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12255,7 +12255,7 @@
         <v>45898</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12328,7 +12328,7 @@
         <v>44576</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12401,7 +12401,7 @@
         <v>44994</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12474,7 +12474,7 @@
         <v>44994</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12547,7 +12547,7 @@
         <v>44635</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12620,7 +12620,7 @@
         <v>45701</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12693,7 +12693,7 @@
         <v>45575</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12766,7 +12766,7 @@
         <v>44789</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12844,7 +12844,7 @@
         <v>45909</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12922,7 +12922,7 @@
         <v>45909</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13000,7 +13000,7 @@
         <v>45365</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13073,7 +13073,7 @@
         <v>44908</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13146,7 +13146,7 @@
         <v>45910</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13219,7 +13219,7 @@
         <v>45153</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13292,7 +13292,7 @@
         <v>45474</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13365,7 +13365,7 @@
         <v>45916</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13443,7 +13443,7 @@
         <v>45916</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13521,7 +13521,7 @@
         <v>45916</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13594,7 +13594,7 @@
         <v>45916</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13672,7 +13672,7 @@
         <v>45077</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13745,7 +13745,7 @@
         <v>46146</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13818,7 +13818,7 @@
         <v>46146</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13891,7 +13891,7 @@
         <v>46146</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13964,7 +13964,7 @@
         <v>46146</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14037,7 +14037,7 @@
         <v>46146</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14110,7 +14110,7 @@
         <v>45922</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14183,7 +14183,7 @@
         <v>46146</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14256,7 +14256,7 @@
         <v>45924</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14334,7 +14334,7 @@
         <v>45647</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14407,7 +14407,7 @@
         <v>45931</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14480,7 +14480,7 @@
         <v>45931</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14553,7 +14553,7 @@
         <v>45932</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14626,7 +14626,7 @@
         <v>46153</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14704,7 +14704,7 @@
         <v>45634</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14777,7 +14777,7 @@
         <v>45406</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14850,7 +14850,7 @@
         <v>45938</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14928,7 +14928,7 @@
         <v>45460</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15001,7 +15001,7 @@
         <v>45096</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15074,7 +15074,7 @@
         <v>45940</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15152,7 +15152,7 @@
         <v>45940</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15230,7 +15230,7 @@
         <v>45273</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15303,7 +15303,7 @@
         <v>44953</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15376,7 +15376,7 @@
         <v>46154</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15454,7 +15454,7 @@
         <v>44600</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15527,7 +15527,7 @@
         <v>44894</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15600,7 +15600,7 @@
         <v>45145</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15673,7 +15673,7 @@
         <v>45666</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15746,7 +15746,7 @@
         <v>45954</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15824,7 +15824,7 @@
         <v>45954</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15902,7 +15902,7 @@
         <v>45714</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15975,7 +15975,7 @@
         <v>45965</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16053,7 +16053,7 @@
         <v>45965</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16131,7 +16131,7 @@
         <v>45965</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16209,7 +16209,7 @@
         <v>45965</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16282,7 +16282,7 @@
         <v>45965</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16360,7 +16360,7 @@
         <v>45965</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16433,7 +16433,7 @@
         <v>45965</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16511,7 +16511,7 @@
         <v>45965</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16584,7 +16584,7 @@
         <v>45964</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16662,7 +16662,7 @@
         <v>45964</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16740,7 +16740,7 @@
         <v>45964</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16818,7 +16818,7 @@
         <v>45054</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16891,7 +16891,7 @@
         <v>44502</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16964,7 +16964,7 @@
         <v>44965</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17037,7 +17037,7 @@
         <v>45310</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17110,7 +17110,7 @@
         <v>45428</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17183,7 +17183,7 @@
         <v>45737</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17256,7 +17256,7 @@
         <v>45194</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17329,7 +17329,7 @@
         <v>45587</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17407,7 +17407,7 @@
         <v>45194</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17480,7 +17480,7 @@
         <v>44916</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17553,7 +17553,7 @@
         <v>44562</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17626,7 +17626,7 @@
         <v>45272</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17704,7 +17704,7 @@
         <v>46038</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17782,7 +17782,7 @@
         <v>45994</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17855,7 +17855,7 @@
         <v>45994</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17928,7 +17928,7 @@
         <v>45414</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18001,7 +18001,7 @@
         <v>44536</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18074,7 +18074,7 @@
         <v>45701</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18147,7 +18147,7 @@
         <v>45965</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18225,7 +18225,7 @@
         <v>46007</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18298,7 +18298,7 @@
         <v>46006</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18371,7 +18371,7 @@
         <v>46171</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18449,7 +18449,7 @@
         <v>46007</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18522,7 +18522,7 @@
         <v>46007</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18595,7 +18595,7 @@
         <v>46007</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18668,7 +18668,7 @@
         <v>46006</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18741,7 +18741,7 @@
         <v>45090</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18819,7 +18819,7 @@
         <v>44908</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18892,7 +18892,7 @@
         <v>44908</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18965,7 +18965,7 @@
         <v>46013</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19038,7 +19038,7 @@
         <v>46013</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19111,7 +19111,7 @@
         <v>46013</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19184,7 +19184,7 @@
         <v>46010</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19257,7 +19257,7 @@
         <v>44624</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19330,7 +19330,7 @@
         <v>46021</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19403,7 +19403,7 @@
         <v>46036</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19476,7 +19476,7 @@
         <v>46177</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19554,7 +19554,7 @@
         <v>46044</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19632,7 +19632,7 @@
         <v>45302</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19705,7 +19705,7 @@
         <v>46045</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19783,7 +19783,7 @@
         <v>46045</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19861,7 +19861,7 @@
         <v>44994</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19934,7 +19934,7 @@
         <v>45371</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20007,7 +20007,7 @@
         <v>46055</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20080,7 +20080,7 @@
         <v>46058</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20153,7 +20153,7 @@
         <v>46183</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20231,7 +20231,7 @@
         <v>45537</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20304,7 +20304,7 @@
         <v>46062</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20382,7 +20382,7 @@
         <v>46069</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20460,7 +20460,7 @@
         <v>46069</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20533,7 +20533,7 @@
         <v>46071</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20611,7 +20611,7 @@
         <v>44868</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20689,7 +20689,7 @@
         <v>45110</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20762,7 +20762,7 @@
         <v>46190</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20835,7 +20835,7 @@
         <v>45583</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20908,7 +20908,7 @@
         <v>45099</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20981,7 +20981,7 @@
         <v>45595</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21054,7 +21054,7 @@
         <v>46191</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21127,7 +21127,7 @@
         <v>46029</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21200,7 +21200,7 @@
         <v>44966</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21273,7 +21273,7 @@
         <v>46099</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21346,7 +21346,7 @@
         <v>44572</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21419,7 +21419,7 @@
         <v>46101</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21492,7 +21492,7 @@
         <v>44491</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21570,7 +21570,7 @@
         <v>46101</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21643,7 +21643,7 @@
         <v>46106</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21716,7 +21716,7 @@
         <v>44501</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21789,7 +21789,7 @@
         <v>46116</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21862,7 +21862,7 @@
         <v>46119</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21935,7 +21935,7 @@
         <v>46202</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -22008,7 +22008,7 @@
         <v>45701</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -22081,7 +22081,7 @@
         <v>46119</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22154,7 +22154,7 @@
         <v>45335</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22227,7 +22227,7 @@
         <v>45575</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22300,7 +22300,7 @@
         <v>46121</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22373,7 +22373,7 @@
         <v>46125</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22446,7 +22446,7 @@
         <v>46202</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22519,7 +22519,7 @@
         <v>46125</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22592,7 +22592,7 @@
         <v>46126</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22665,7 +22665,7 @@
         <v>46202</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22738,7 +22738,7 @@
         <v>46202</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22811,7 +22811,7 @@
         <v>45965</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22884,7 +22884,7 @@
         <v>44874</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22957,7 +22957,7 @@
         <v>46202</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -23030,7 +23030,7 @@
         <v>45755</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -23103,7 +23103,7 @@
         <v>44711</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23181,7 +23181,7 @@
         <v>45831</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23254,7 +23254,7 @@
         <v>45916</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23327,7 +23327,7 @@
         <v>45649</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23400,7 +23400,7 @@
         <v>45460</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23473,7 +23473,7 @@
         <v>45580</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23546,7 +23546,7 @@
         <v>45170</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23619,7 +23619,7 @@
         <v>45707</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23692,7 +23692,7 @@
         <v>45664</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23765,7 +23765,7 @@
         <v>45436</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23838,7 +23838,7 @@
         <v>45831</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23911,7 +23911,7 @@
         <v>44530</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -23984,7 +23984,7 @@
         <v>45261</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -24057,7 +24057,7 @@
         <v>46273</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -24130,7 +24130,7 @@
         <v>46273</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24203,7 +24203,7 @@
         <v>46273</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24276,7 +24276,7 @@
         <v>45649</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24349,7 +24349,7 @@
         <v>46275</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24422,7 +24422,7 @@
         <v>45398</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24495,7 +24495,7 @@
         <v>44987</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24568,7 +24568,7 @@
         <v>45762</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24641,7 +24641,7 @@
         <v>45758</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24714,7 +24714,7 @@
         <v>45104</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24787,7 +24787,7 @@
         <v>45600</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24865,7 +24865,7 @@
         <v>45638</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -24938,7 +24938,7 @@
         <v>45414</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -25011,7 +25011,7 @@
         <v>45334</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -25084,7 +25084,7 @@
         <v>44816</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25157,7 +25157,7 @@
         <v>45016</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25235,7 +25235,7 @@
         <v>46280</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25308,7 +25308,7 @@
         <v>44655</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25381,7 +25381,7 @@
         <v>46283</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25459,7 +25459,7 @@
         <v>46282</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25532,7 +25532,7 @@
         <v>46282</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25605,7 +25605,7 @@
         <v>46282</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25678,7 +25678,7 @@
         <v>45348</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25751,7 +25751,7 @@
         <v>46240</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25824,7 +25824,7 @@
         <v>46283</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -25902,7 +25902,7 @@
         <v>46283</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -25980,7 +25980,7 @@
         <v>46283</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -26058,7 +26058,7 @@
         <v>46282</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -26131,7 +26131,7 @@
         <v>46240</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -26204,7 +26204,7 @@
         <v>46282</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -26277,7 +26277,7 @@
         <v>46282</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -26350,7 +26350,7 @@
         <v>45085</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -26423,7 +26423,7 @@
         <v>45414</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -26496,7 +26496,7 @@
         <v>46283</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26574,7 +26574,7 @@
         <v>44987</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26647,7 +26647,7 @@
         <v>44980</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26720,7 +26720,7 @@
         <v>44908</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -26793,7 +26793,7 @@
         <v>45634</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -26866,7 +26866,7 @@
         <v>45218</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -26939,7 +26939,7 @@
         <v>46286</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -27017,7 +27017,7 @@
         <v>46286</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -27095,7 +27095,7 @@
         <v>45414</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -27168,7 +27168,7 @@
         <v>44651</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -27241,7 +27241,7 @@
         <v>44844</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -27314,7 +27314,7 @@
         <v>45257</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -27387,7 +27387,7 @@
         <v>45698</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -27460,7 +27460,7 @@
         <v>45159</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -27533,7 +27533,7 @@
         <v>45558</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -27606,7 +27606,7 @@
         <v>45054</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -27679,7 +27679,7 @@
         <v>46290</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -27752,7 +27752,7 @@
         <v>44994</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -27825,7 +27825,7 @@
         <v>45273</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -27898,7 +27898,7 @@
         <v>45692</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -27971,7 +27971,7 @@
         <v>44670</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -28044,7 +28044,7 @@
         <v>44953</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -28117,7 +28117,7 @@
         <v>44651</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -28190,7 +28190,7 @@
         <v>45671</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -28263,7 +28263,7 @@
         <v>44490</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -28336,7 +28336,7 @@
         <v>45831</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -28409,7 +28409,7 @@
         <v>46290</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -28482,7 +28482,7 @@
         <v>45159</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -28555,7 +28555,7 @@
         <v>45096</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -28628,7 +28628,7 @@
         <v>45677</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -28701,7 +28701,7 @@
         <v>45736</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -28779,7 +28779,7 @@
         <v>45748</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -28852,7 +28852,7 @@
         <v>45264</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -28925,7 +28925,7 @@
         <v>45492</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -28998,7 +28998,7 @@
         <v>45468</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -29071,7 +29071,7 @@
         <v>46258</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -29144,7 +29144,7 @@
         <v>46097</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -29217,7 +29217,7 @@
         <v>45544</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -29290,7 +29290,7 @@
         <v>45714</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -29363,7 +29363,7 @@
         <v>45666</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -29436,7 +29436,7 @@
         <v>45994</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -29509,7 +29509,7 @@
         <v>45719</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -29587,7 +29587,7 @@
         <v>46303</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -29660,7 +29660,7 @@
         <v>46303</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -29733,7 +29733,7 @@
         <v>45475</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -29806,7 +29806,7 @@
         <v>45831</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -29879,7 +29879,7 @@
         <v>45365</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -29952,7 +29952,7 @@
         <v>46304</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -30025,7 +30025,7 @@
         <v>45796</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -30098,7 +30098,7 @@
         <v>45796</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -30171,7 +30171,7 @@
         <v>45726</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -30244,7 +30244,7 @@
         <v>46304</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -30317,7 +30317,7 @@
         <v>46308</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -30390,7 +30390,7 @@
         <v>45239</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -30463,7 +30463,7 @@
         <v>46269</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -30536,7 +30536,7 @@
         <v>46310</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -30609,7 +30609,7 @@
         <v>45821</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -30687,7 +30687,7 @@
         <v>46269</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -30760,7 +30760,7 @@
         <v>45831</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -30833,7 +30833,7 @@
         <v>45831</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -30906,7 +30906,7 @@
         <v>45831</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -30979,7 +30979,7 @@
         <v>45831</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -31052,7 +31052,7 @@
         <v>45838</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -31130,7 +31130,7 @@
         <v>45790</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -31203,7 +31203,7 @@
         <v>45810</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -31276,7 +31276,7 @@
         <v>45769</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -31349,7 +31349,7 @@
         <v>44585</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -31422,7 +31422,7 @@
         <v>45839</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -31500,7 +31500,7 @@
         <v>45916</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -31578,7 +31578,7 @@
         <v>45964</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -31651,7 +31651,7 @@
         <v>46066</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -31724,7 +31724,7 @@
         <v>46287</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>

--- a/Översikt YDRE.xlsx
+++ b/Översikt YDRE.xlsx
@@ -601,7 +601,7 @@
         <v>44503</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -729,7 +729,7 @@
         <v>45153</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -848,7 +848,7 @@
         <v>44621</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -957,7 +957,7 @@
         <v>46282</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>45378</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1184,7 +1184,7 @@
         <v>45954</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1301,7 +1301,7 @@
         <v>45709</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1408,7 +1408,7 @@
         <v>45198</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1519,7 +1519,7 @@
         <v>46189</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1626,7 +1626,7 @@
         <v>45883</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1738,7 +1738,7 @@
         <v>44509</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1844,7 +1844,7 @@
         <v>45091</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1955,7 +1955,7 @@
         <v>44789</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2066,7 +2066,7 @@
         <v>45973</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2177,7 +2177,7 @@
         <v>45415</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2283,7 +2283,7 @@
         <v>45348</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2389,7 +2389,7 @@
         <v>45611</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2504,7 +2504,7 @@
         <v>45251</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2614,7 +2614,7 @@
         <v>44874</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2720,7 +2720,7 @@
         <v>44732</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2831,7 +2831,7 @@
         <v>45792</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2937,7 +2937,7 @@
         <v>45614</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3048,7 +3048,7 @@
         <v>45846</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3159,7 +3159,7 @@
         <v>44515</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3264,7 +3264,7 @@
         <v>44858</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3374,7 +3374,7 @@
         <v>45727</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3479,7 +3479,7 @@
         <v>45922</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3584,7 +3584,7 @@
         <v>45769</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3689,7 +3689,7 @@
         <v>45916</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3794,7 +3794,7 @@
         <v>45922</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3899,7 +3899,7 @@
         <v>45611</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4009,7 +4009,7 @@
         <v>45371</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4114,7 +4114,7 @@
         <v>45965</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4223,7 +4223,7 @@
         <v>45964</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4333,7 +4333,7 @@
         <v>45561</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4438,7 +4438,7 @@
         <v>45754</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4543,7 +4543,7 @@
         <v>46045</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4657,7 +4657,7 @@
         <v>46069</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4762,7 +4762,7 @@
         <v>46069</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4872,7 +4872,7 @@
         <v>45733</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4977,7 +4977,7 @@
         <v>46202</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5082,7 +5082,7 @@
         <v>45192</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5187,7 +5187,7 @@
         <v>45777</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5292,7 +5292,7 @@
         <v>46075</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5401,7 +5401,7 @@
         <v>44582</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5474,7 +5474,7 @@
         <v>44508</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5547,7 +5547,7 @@
         <v>44693</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5620,7 +5620,7 @@
         <v>44827</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5698,7 +5698,7 @@
         <v>44491</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5776,7 +5776,7 @@
         <v>44585</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5849,7 +5849,7 @@
         <v>44502</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5922,7 +5922,7 @@
         <v>44820</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5995,7 +5995,7 @@
         <v>44827</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6073,7 +6073,7 @@
         <v>44687</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6151,7 +6151,7 @@
         <v>44503</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6229,7 +6229,7 @@
         <v>44868</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6302,7 +6302,7 @@
         <v>44879</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6380,7 +6380,7 @@
         <v>44879</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6453,7 +6453,7 @@
         <v>44879</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6526,7 +6526,7 @@
         <v>44789</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6604,7 +6604,7 @@
         <v>44516</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6677,7 +6677,7 @@
         <v>44816</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6750,7 +6750,7 @@
         <v>44538</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6823,7 +6823,7 @@
         <v>44728</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6896,7 +6896,7 @@
         <v>44593</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6974,7 +6974,7 @@
         <v>44698</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7047,7 +7047,7 @@
         <v>44650</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7120,7 +7120,7 @@
         <v>44827</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7198,7 +7198,7 @@
         <v>44743</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7271,7 +7271,7 @@
         <v>44538</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7344,7 +7344,7 @@
         <v>44531</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7417,7 +7417,7 @@
         <v>45432</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7490,7 +7490,7 @@
         <v>45597</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7563,7 +7563,7 @@
         <v>45110</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7636,7 +7636,7 @@
         <v>45664</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7709,7 +7709,7 @@
         <v>44606</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7782,7 +7782,7 @@
         <v>44538</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7855,7 +7855,7 @@
         <v>45110</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7928,7 +7928,7 @@
         <v>45714</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8001,7 +8001,7 @@
         <v>45596</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8074,7 +8074,7 @@
         <v>45665</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8147,7 +8147,7 @@
         <v>45138</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8220,7 +8220,7 @@
         <v>45665</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8293,7 +8293,7 @@
         <v>45666</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8366,7 +8366,7 @@
         <v>45707</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8439,7 +8439,7 @@
         <v>45355</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8512,7 +8512,7 @@
         <v>45355</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8585,7 +8585,7 @@
         <v>44903</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8658,7 +8658,7 @@
         <v>44796</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8731,7 +8731,7 @@
         <v>45231</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8804,7 +8804,7 @@
         <v>45208</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8877,7 +8877,7 @@
         <v>44592</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8950,7 +8950,7 @@
         <v>45701</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9023,7 +9023,7 @@
         <v>45335</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9096,7 +9096,7 @@
         <v>45596</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9169,7 +9169,7 @@
         <v>45261</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9242,7 +9242,7 @@
         <v>45419</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9315,7 +9315,7 @@
         <v>45236</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9388,7 +9388,7 @@
         <v>45000</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9461,7 +9461,7 @@
         <v>45355</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9534,7 +9534,7 @@
         <v>45414</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9607,7 +9607,7 @@
         <v>45475</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9680,7 +9680,7 @@
         <v>45105</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9753,7 +9753,7 @@
         <v>45170</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9826,7 +9826,7 @@
         <v>45170</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9899,7 +9899,7 @@
         <v>44504</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9972,7 +9972,7 @@
         <v>45278</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10045,7 +10045,7 @@
         <v>44503</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10123,7 +10123,7 @@
         <v>44980</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10196,7 +10196,7 @@
         <v>44831</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10269,7 +10269,7 @@
         <v>44743</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10342,7 +10342,7 @@
         <v>44749</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10415,7 +10415,7 @@
         <v>45434</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10488,7 +10488,7 @@
         <v>45218</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10561,7 +10561,7 @@
         <v>45510</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10634,7 +10634,7 @@
         <v>45194</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10707,7 +10707,7 @@
         <v>45216</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10780,7 +10780,7 @@
         <v>45216</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10853,7 +10853,7 @@
         <v>45666</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10926,7 +10926,7 @@
         <v>45119</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11004,7 +11004,7 @@
         <v>44966</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11077,7 +11077,7 @@
         <v>45831</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11150,7 +11150,7 @@
         <v>45917</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11223,7 +11223,7 @@
         <v>45616</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11296,7 +11296,7 @@
         <v>44939</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11369,7 +11369,7 @@
         <v>45910</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11442,7 +11442,7 @@
         <v>45889</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11515,7 +11515,7 @@
         <v>44994</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11588,7 +11588,7 @@
         <v>45965</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11661,7 +11661,7 @@
         <v>45891</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11734,7 +11734,7 @@
         <v>45871</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11807,7 +11807,7 @@
         <v>44980</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11880,7 +11880,7 @@
         <v>45091</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11958,7 +11958,7 @@
         <v>45831</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12031,7 +12031,7 @@
         <v>45793</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12104,7 +12104,7 @@
         <v>45246</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12182,7 +12182,7 @@
         <v>45841</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12255,7 +12255,7 @@
         <v>45898</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12328,7 +12328,7 @@
         <v>44576</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12401,7 +12401,7 @@
         <v>44994</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12474,7 +12474,7 @@
         <v>44994</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12547,7 +12547,7 @@
         <v>44635</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12620,7 +12620,7 @@
         <v>45701</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12693,7 +12693,7 @@
         <v>45575</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12766,7 +12766,7 @@
         <v>44789</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12844,7 +12844,7 @@
         <v>45909</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12922,7 +12922,7 @@
         <v>45909</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13000,7 +13000,7 @@
         <v>45365</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13073,7 +13073,7 @@
         <v>44908</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13146,7 +13146,7 @@
         <v>45910</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13219,7 +13219,7 @@
         <v>45153</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13292,7 +13292,7 @@
         <v>45474</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13365,7 +13365,7 @@
         <v>45916</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13443,7 +13443,7 @@
         <v>45916</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13521,7 +13521,7 @@
         <v>45916</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13594,7 +13594,7 @@
         <v>45916</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13672,7 +13672,7 @@
         <v>45077</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13745,7 +13745,7 @@
         <v>46146</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13818,7 +13818,7 @@
         <v>46146</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13891,7 +13891,7 @@
         <v>46146</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13964,7 +13964,7 @@
         <v>46146</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14037,7 +14037,7 @@
         <v>46146</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14110,7 +14110,7 @@
         <v>45922</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14183,7 +14183,7 @@
         <v>46146</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14256,7 +14256,7 @@
         <v>45924</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14334,7 +14334,7 @@
         <v>45647</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14407,7 +14407,7 @@
         <v>45931</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14480,7 +14480,7 @@
         <v>45931</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14553,7 +14553,7 @@
         <v>45932</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14626,7 +14626,7 @@
         <v>46153</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14704,7 +14704,7 @@
         <v>45634</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14777,7 +14777,7 @@
         <v>45406</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14850,7 +14850,7 @@
         <v>45938</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14928,7 +14928,7 @@
         <v>45460</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15001,7 +15001,7 @@
         <v>45096</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15074,7 +15074,7 @@
         <v>45940</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15152,7 +15152,7 @@
         <v>45940</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15230,7 +15230,7 @@
         <v>45273</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15303,7 +15303,7 @@
         <v>44953</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15376,7 +15376,7 @@
         <v>46154</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15454,7 +15454,7 @@
         <v>44600</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15527,7 +15527,7 @@
         <v>44894</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15600,7 +15600,7 @@
         <v>45145</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15673,7 +15673,7 @@
         <v>45666</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15746,7 +15746,7 @@
         <v>45954</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15824,7 +15824,7 @@
         <v>45954</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15902,7 +15902,7 @@
         <v>45714</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15975,7 +15975,7 @@
         <v>45965</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16053,7 +16053,7 @@
         <v>45965</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16131,7 +16131,7 @@
         <v>45965</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16209,7 +16209,7 @@
         <v>45965</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16282,7 +16282,7 @@
         <v>45965</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16360,7 +16360,7 @@
         <v>45965</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16433,7 +16433,7 @@
         <v>45965</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16511,7 +16511,7 @@
         <v>45965</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16584,7 +16584,7 @@
         <v>45964</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16662,7 +16662,7 @@
         <v>45964</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16740,7 +16740,7 @@
         <v>45964</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16818,7 +16818,7 @@
         <v>45054</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16891,7 +16891,7 @@
         <v>44502</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16964,7 +16964,7 @@
         <v>44965</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17037,7 +17037,7 @@
         <v>45310</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17110,7 +17110,7 @@
         <v>45428</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17183,7 +17183,7 @@
         <v>45737</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17256,7 +17256,7 @@
         <v>45194</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17329,7 +17329,7 @@
         <v>45587</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17407,7 +17407,7 @@
         <v>45194</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17480,7 +17480,7 @@
         <v>44916</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17553,7 +17553,7 @@
         <v>44562</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17626,7 +17626,7 @@
         <v>45272</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17704,7 +17704,7 @@
         <v>46038</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17782,7 +17782,7 @@
         <v>45994</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17855,7 +17855,7 @@
         <v>45994</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17928,7 +17928,7 @@
         <v>45414</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18001,7 +18001,7 @@
         <v>44536</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18074,7 +18074,7 @@
         <v>45701</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18147,7 +18147,7 @@
         <v>45965</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18225,7 +18225,7 @@
         <v>46007</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18298,7 +18298,7 @@
         <v>46006</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18371,7 +18371,7 @@
         <v>46171</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18449,7 +18449,7 @@
         <v>46007</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18522,7 +18522,7 @@
         <v>46007</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18595,7 +18595,7 @@
         <v>46007</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18668,7 +18668,7 @@
         <v>46006</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18741,7 +18741,7 @@
         <v>45090</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18819,7 +18819,7 @@
         <v>44908</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18892,7 +18892,7 @@
         <v>44908</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18965,7 +18965,7 @@
         <v>46013</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19038,7 +19038,7 @@
         <v>46013</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19111,7 +19111,7 @@
         <v>46013</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19184,7 +19184,7 @@
         <v>46010</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19257,7 +19257,7 @@
         <v>44624</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19330,7 +19330,7 @@
         <v>46021</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19403,7 +19403,7 @@
         <v>46036</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19476,7 +19476,7 @@
         <v>46177</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19554,7 +19554,7 @@
         <v>46044</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19632,7 +19632,7 @@
         <v>45302</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19705,7 +19705,7 @@
         <v>46045</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19783,7 +19783,7 @@
         <v>46045</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19861,7 +19861,7 @@
         <v>44994</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19934,7 +19934,7 @@
         <v>45371</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20007,7 +20007,7 @@
         <v>46055</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20080,7 +20080,7 @@
         <v>46058</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20153,7 +20153,7 @@
         <v>46183</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20231,7 +20231,7 @@
         <v>45537</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20304,7 +20304,7 @@
         <v>46062</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20382,7 +20382,7 @@
         <v>46069</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20460,7 +20460,7 @@
         <v>46069</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20533,7 +20533,7 @@
         <v>46071</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20611,7 +20611,7 @@
         <v>44868</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20689,7 +20689,7 @@
         <v>45110</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20762,7 +20762,7 @@
         <v>46190</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20835,7 +20835,7 @@
         <v>45583</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20908,7 +20908,7 @@
         <v>45099</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20981,7 +20981,7 @@
         <v>45595</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21054,7 +21054,7 @@
         <v>46191</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21127,7 +21127,7 @@
         <v>46029</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21200,7 +21200,7 @@
         <v>44966</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21273,7 +21273,7 @@
         <v>46099</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21346,7 +21346,7 @@
         <v>44572</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21419,7 +21419,7 @@
         <v>46101</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21492,7 +21492,7 @@
         <v>44491</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21570,7 +21570,7 @@
         <v>46101</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21643,7 +21643,7 @@
         <v>46106</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21716,7 +21716,7 @@
         <v>44501</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21789,7 +21789,7 @@
         <v>46116</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21862,7 +21862,7 @@
         <v>46119</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21935,7 +21935,7 @@
         <v>46202</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -22008,7 +22008,7 @@
         <v>45701</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -22081,7 +22081,7 @@
         <v>46119</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22154,7 +22154,7 @@
         <v>45335</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22227,7 +22227,7 @@
         <v>45575</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22300,7 +22300,7 @@
         <v>46121</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22373,7 +22373,7 @@
         <v>46125</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22446,7 +22446,7 @@
         <v>46202</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22519,7 +22519,7 @@
         <v>46125</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22592,7 +22592,7 @@
         <v>46126</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22665,7 +22665,7 @@
         <v>46202</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22738,7 +22738,7 @@
         <v>46202</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22811,7 +22811,7 @@
         <v>45965</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22884,7 +22884,7 @@
         <v>44874</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22957,7 +22957,7 @@
         <v>46202</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -23030,7 +23030,7 @@
         <v>45755</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -23103,7 +23103,7 @@
         <v>44711</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23181,7 +23181,7 @@
         <v>45831</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23254,7 +23254,7 @@
         <v>45916</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23327,7 +23327,7 @@
         <v>45649</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23400,7 +23400,7 @@
         <v>45460</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23473,7 +23473,7 @@
         <v>45580</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23546,7 +23546,7 @@
         <v>45170</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23619,7 +23619,7 @@
         <v>45707</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23692,7 +23692,7 @@
         <v>45664</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23765,7 +23765,7 @@
         <v>45436</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23838,7 +23838,7 @@
         <v>45831</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23911,7 +23911,7 @@
         <v>44530</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -23984,7 +23984,7 @@
         <v>45261</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -24057,7 +24057,7 @@
         <v>46273</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -24130,7 +24130,7 @@
         <v>46273</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24203,7 +24203,7 @@
         <v>46273</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24276,7 +24276,7 @@
         <v>45649</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24349,7 +24349,7 @@
         <v>46275</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24422,7 +24422,7 @@
         <v>45398</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24495,7 +24495,7 @@
         <v>44987</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24568,7 +24568,7 @@
         <v>45762</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24641,7 +24641,7 @@
         <v>45758</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24714,7 +24714,7 @@
         <v>45104</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24787,7 +24787,7 @@
         <v>45600</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24865,7 +24865,7 @@
         <v>45638</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -24938,7 +24938,7 @@
         <v>45414</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -25011,7 +25011,7 @@
         <v>45334</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -25084,7 +25084,7 @@
         <v>44816</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25157,7 +25157,7 @@
         <v>45016</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25235,7 +25235,7 @@
         <v>46280</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25308,7 +25308,7 @@
         <v>44655</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25381,7 +25381,7 @@
         <v>46283</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25459,7 +25459,7 @@
         <v>46282</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25532,7 +25532,7 @@
         <v>46282</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25605,7 +25605,7 @@
         <v>46282</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25678,7 +25678,7 @@
         <v>45348</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25751,7 +25751,7 @@
         <v>46240</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25824,7 +25824,7 @@
         <v>46283</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -25902,7 +25902,7 @@
         <v>46283</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -25980,7 +25980,7 @@
         <v>46283</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -26058,7 +26058,7 @@
         <v>46282</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -26131,7 +26131,7 @@
         <v>46240</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -26204,7 +26204,7 @@
         <v>46282</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -26277,7 +26277,7 @@
         <v>46282</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -26350,7 +26350,7 @@
         <v>45085</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -26423,7 +26423,7 @@
         <v>45414</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -26496,7 +26496,7 @@
         <v>46283</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26574,7 +26574,7 @@
         <v>44987</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26647,7 +26647,7 @@
         <v>44980</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26720,7 +26720,7 @@
         <v>44908</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -26793,7 +26793,7 @@
         <v>45634</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -26866,7 +26866,7 @@
         <v>45218</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -26939,7 +26939,7 @@
         <v>46286</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -27017,7 +27017,7 @@
         <v>46286</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -27095,7 +27095,7 @@
         <v>45414</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -27168,7 +27168,7 @@
         <v>44651</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -27241,7 +27241,7 @@
         <v>44844</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -27314,7 +27314,7 @@
         <v>45257</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -27387,7 +27387,7 @@
         <v>45698</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -27460,7 +27460,7 @@
         <v>45159</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -27533,7 +27533,7 @@
         <v>45558</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -27606,7 +27606,7 @@
         <v>45054</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -27679,7 +27679,7 @@
         <v>46290</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -27752,7 +27752,7 @@
         <v>44994</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -27825,7 +27825,7 @@
         <v>45273</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -27898,7 +27898,7 @@
         <v>45692</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -27971,7 +27971,7 @@
         <v>44670</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -28044,7 +28044,7 @@
         <v>44953</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -28117,7 +28117,7 @@
         <v>44651</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -28190,7 +28190,7 @@
         <v>45671</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -28263,7 +28263,7 @@
         <v>44490</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -28336,7 +28336,7 @@
         <v>45831</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -28409,7 +28409,7 @@
         <v>46290</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -28482,7 +28482,7 @@
         <v>45159</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -28555,7 +28555,7 @@
         <v>45096</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -28628,7 +28628,7 @@
         <v>45677</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -28701,7 +28701,7 @@
         <v>45736</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -28779,7 +28779,7 @@
         <v>45748</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -28852,7 +28852,7 @@
         <v>45264</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -28925,7 +28925,7 @@
         <v>45492</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -28998,7 +28998,7 @@
         <v>45468</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -29071,7 +29071,7 @@
         <v>46258</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -29144,7 +29144,7 @@
         <v>46097</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -29217,7 +29217,7 @@
         <v>45544</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -29290,7 +29290,7 @@
         <v>45714</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -29363,7 +29363,7 @@
         <v>45666</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -29436,7 +29436,7 @@
         <v>45994</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -29509,7 +29509,7 @@
         <v>45719</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -29587,7 +29587,7 @@
         <v>46303</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -29660,7 +29660,7 @@
         <v>46303</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -29733,7 +29733,7 @@
         <v>45475</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -29806,7 +29806,7 @@
         <v>45831</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -29879,7 +29879,7 @@
         <v>45365</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -29952,7 +29952,7 @@
         <v>46304</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -30025,7 +30025,7 @@
         <v>45796</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -30098,7 +30098,7 @@
         <v>45796</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -30171,7 +30171,7 @@
         <v>45726</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -30244,7 +30244,7 @@
         <v>46304</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -30317,7 +30317,7 @@
         <v>46308</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -30390,7 +30390,7 @@
         <v>45239</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -30463,7 +30463,7 @@
         <v>46269</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -30536,7 +30536,7 @@
         <v>46310</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -30609,7 +30609,7 @@
         <v>45821</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -30687,7 +30687,7 @@
         <v>46269</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -30760,7 +30760,7 @@
         <v>45831</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -30833,7 +30833,7 @@
         <v>45831</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -30906,7 +30906,7 @@
         <v>45831</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -30979,7 +30979,7 @@
         <v>45831</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -31052,7 +31052,7 @@
         <v>45838</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -31130,7 +31130,7 @@
         <v>45790</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -31203,7 +31203,7 @@
         <v>45810</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -31276,7 +31276,7 @@
         <v>45769</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -31349,7 +31349,7 @@
         <v>44585</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -31422,7 +31422,7 @@
         <v>45839</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -31500,7 +31500,7 @@
         <v>45916</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -31578,7 +31578,7 @@
         <v>45964</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -31651,7 +31651,7 @@
         <v>46066</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -31724,7 +31724,7 @@
         <v>46287</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>

--- a/Översikt YDRE.xlsx
+++ b/Översikt YDRE.xlsx
@@ -601,7 +601,7 @@
         <v>44503</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -729,7 +729,7 @@
         <v>45153</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -848,7 +848,7 @@
         <v>44621</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -957,7 +957,7 @@
         <v>46282</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>45378</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1184,7 +1184,7 @@
         <v>45954</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1301,7 +1301,7 @@
         <v>46189</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1408,7 +1408,7 @@
         <v>45198</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1519,7 +1519,7 @@
         <v>45709</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1626,7 +1626,7 @@
         <v>45883</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1738,7 +1738,7 @@
         <v>44509</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1844,7 +1844,7 @@
         <v>44789</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1955,7 +1955,7 @@
         <v>45973</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2066,7 +2066,7 @@
         <v>44732</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2177,7 +2177,7 @@
         <v>45792</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2283,7 +2283,7 @@
         <v>44874</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2389,7 +2389,7 @@
         <v>45251</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2499,7 +2499,7 @@
         <v>45415</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2605,7 +2605,7 @@
         <v>45348</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2711,7 +2711,7 @@
         <v>45611</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2826,7 +2826,7 @@
         <v>45091</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2937,7 +2937,7 @@
         <v>45614</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3048,7 +3048,7 @@
         <v>45846</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3159,7 +3159,7 @@
         <v>44515</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3264,7 +3264,7 @@
         <v>45916</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3369,7 +3369,7 @@
         <v>45922</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3474,7 +3474,7 @@
         <v>45371</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3579,7 +3579,7 @@
         <v>45964</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3689,7 +3689,7 @@
         <v>45965</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3798,7 +3798,7 @@
         <v>46202</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3903,7 +3903,7 @@
         <v>45611</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4013,7 +4013,7 @@
         <v>45561</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4118,7 +4118,7 @@
         <v>46045</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4232,7 +4232,7 @@
         <v>46069</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4337,7 +4337,7 @@
         <v>46069</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4447,7 +4447,7 @@
         <v>45922</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4552,7 +4552,7 @@
         <v>45727</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4657,7 +4657,7 @@
         <v>45192</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4762,7 +4762,7 @@
         <v>45769</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4867,7 +4867,7 @@
         <v>45754</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4972,7 +4972,7 @@
         <v>44858</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5082,7 +5082,7 @@
         <v>45733</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5187,7 +5187,7 @@
         <v>45777</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5292,7 +5292,7 @@
         <v>46075</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5401,7 +5401,7 @@
         <v>44582</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5474,7 +5474,7 @@
         <v>44508</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5547,7 +5547,7 @@
         <v>44693</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5620,7 +5620,7 @@
         <v>44827</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5698,7 +5698,7 @@
         <v>44585</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5771,7 +5771,7 @@
         <v>44502</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5844,7 +5844,7 @@
         <v>44820</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5917,7 +5917,7 @@
         <v>44827</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5995,7 +5995,7 @@
         <v>44503</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6073,7 +6073,7 @@
         <v>44687</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6151,7 +6151,7 @@
         <v>44868</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6224,7 +6224,7 @@
         <v>44879</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6302,7 +6302,7 @@
         <v>44879</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6375,7 +6375,7 @@
         <v>44879</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6448,7 +6448,7 @@
         <v>44789</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6526,7 +6526,7 @@
         <v>44516</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6599,7 +6599,7 @@
         <v>44816</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6672,7 +6672,7 @@
         <v>44538</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6745,7 +6745,7 @@
         <v>44728</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6818,7 +6818,7 @@
         <v>44593</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6896,7 +6896,7 @@
         <v>44698</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6969,7 +6969,7 @@
         <v>44650</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7042,7 +7042,7 @@
         <v>44827</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7120,7 +7120,7 @@
         <v>44743</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7193,7 +7193,7 @@
         <v>44538</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7266,7 +7266,7 @@
         <v>44531</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7339,7 +7339,7 @@
         <v>44953</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7412,7 +7412,7 @@
         <v>44903</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7485,7 +7485,7 @@
         <v>45748</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7558,7 +7558,7 @@
         <v>45889</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7631,7 +7631,7 @@
         <v>45891</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7704,7 +7704,7 @@
         <v>45348</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7777,7 +7777,7 @@
         <v>44600</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7850,7 +7850,7 @@
         <v>45428</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7923,7 +7923,7 @@
         <v>45898</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7996,7 +7996,7 @@
         <v>45414</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8069,7 +8069,7 @@
         <v>44874</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8142,7 +8142,7 @@
         <v>45371</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8215,7 +8215,7 @@
         <v>45909</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8293,7 +8293,7 @@
         <v>45909</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8371,7 +8371,7 @@
         <v>45910</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8444,7 +8444,7 @@
         <v>44501</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8517,7 +8517,7 @@
         <v>45916</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8590,7 +8590,7 @@
         <v>44536</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8663,7 +8663,7 @@
         <v>45916</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8741,7 +8741,7 @@
         <v>45916</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8819,7 +8819,7 @@
         <v>45916</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8897,7 +8897,7 @@
         <v>45922</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8970,7 +8970,7 @@
         <v>45924</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9048,7 +9048,7 @@
         <v>46038</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9126,7 +9126,7 @@
         <v>45096</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9199,7 +9199,7 @@
         <v>44953</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9272,7 +9272,7 @@
         <v>45419</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9345,7 +9345,7 @@
         <v>44980</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9418,7 +9418,7 @@
         <v>45931</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9491,7 +9491,7 @@
         <v>45931</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9564,7 +9564,7 @@
         <v>45965</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9642,7 +9642,7 @@
         <v>46171</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9720,7 +9720,7 @@
         <v>45932</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9793,7 +9793,7 @@
         <v>45940</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9871,7 +9871,7 @@
         <v>45938</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9949,7 +9949,7 @@
         <v>45940</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10027,7 +10027,7 @@
         <v>45145</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10100,7 +10100,7 @@
         <v>44796</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10173,7 +10173,7 @@
         <v>45216</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10246,7 +10246,7 @@
         <v>45216</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10319,7 +10319,7 @@
         <v>46177</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10397,7 +10397,7 @@
         <v>45077</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10470,7 +10470,7 @@
         <v>45665</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10543,7 +10543,7 @@
         <v>45365</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10616,7 +10616,7 @@
         <v>46183</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10694,7 +10694,7 @@
         <v>45954</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10772,7 +10772,7 @@
         <v>45954</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10850,7 +10850,7 @@
         <v>45208</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10923,7 +10923,7 @@
         <v>45595</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10996,7 +10996,7 @@
         <v>45964</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11074,7 +11074,7 @@
         <v>45964</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11152,7 +11152,7 @@
         <v>45964</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11230,7 +11230,7 @@
         <v>45965</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11308,7 +11308,7 @@
         <v>45965</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11386,7 +11386,7 @@
         <v>45965</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11459,7 +11459,7 @@
         <v>46191</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11532,7 +11532,7 @@
         <v>45698</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11605,7 +11605,7 @@
         <v>45965</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11678,7 +11678,7 @@
         <v>46190</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11751,7 +11751,7 @@
         <v>45965</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11829,7 +11829,7 @@
         <v>45965</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11907,7 +11907,7 @@
         <v>45965</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11985,7 +11985,7 @@
         <v>45965</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12058,7 +12058,7 @@
         <v>45355</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12131,7 +12131,7 @@
         <v>45664</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12204,7 +12204,7 @@
         <v>45596</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12277,7 +12277,7 @@
         <v>45085</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12350,7 +12350,7 @@
         <v>44916</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12423,7 +12423,7 @@
         <v>45460</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12496,7 +12496,7 @@
         <v>46202</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12569,7 +12569,7 @@
         <v>45414</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12642,7 +12642,7 @@
         <v>45666</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12715,7 +12715,7 @@
         <v>44994</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12788,7 +12788,7 @@
         <v>44635</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12861,7 +12861,7 @@
         <v>46202</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12934,7 +12934,7 @@
         <v>46202</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13007,7 +13007,7 @@
         <v>46202</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13080,7 +13080,7 @@
         <v>46202</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13153,7 +13153,7 @@
         <v>45665</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13226,7 +13226,7 @@
         <v>45110</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13299,7 +13299,7 @@
         <v>45755</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13372,7 +13372,7 @@
         <v>45218</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13445,7 +13445,7 @@
         <v>45236</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13518,7 +13518,7 @@
         <v>45714</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13591,7 +13591,7 @@
         <v>45597</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13664,7 +13664,7 @@
         <v>45054</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13737,7 +13737,7 @@
         <v>45170</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13810,7 +13810,7 @@
         <v>45677</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13883,7 +13883,7 @@
         <v>45707</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13956,7 +13956,7 @@
         <v>45994</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14029,7 +14029,7 @@
         <v>45994</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14102,7 +14102,7 @@
         <v>45432</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14175,7 +14175,7 @@
         <v>45638</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14248,7 +14248,7 @@
         <v>45414</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14321,7 +14321,7 @@
         <v>45414</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14394,7 +14394,7 @@
         <v>45474</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14467,7 +14467,7 @@
         <v>45110</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14540,7 +14540,7 @@
         <v>45831</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14613,7 +14613,7 @@
         <v>45468</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14686,7 +14686,7 @@
         <v>45492</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14759,7 +14759,7 @@
         <v>46006</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14832,7 +14832,7 @@
         <v>46006</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14905,7 +14905,7 @@
         <v>46007</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14978,7 +14978,7 @@
         <v>46007</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15051,7 +15051,7 @@
         <v>46007</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15124,7 +15124,7 @@
         <v>45666</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15197,7 +15197,7 @@
         <v>46007</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15270,7 +15270,7 @@
         <v>46010</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15343,7 +15343,7 @@
         <v>46280</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15416,7 +15416,7 @@
         <v>46013</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15489,7 +15489,7 @@
         <v>46013</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15562,7 +15562,7 @@
         <v>46013</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15635,7 +15635,7 @@
         <v>45475</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15708,7 +15708,7 @@
         <v>45714</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15781,7 +15781,7 @@
         <v>46282</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15854,7 +15854,7 @@
         <v>45544</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15927,7 +15927,7 @@
         <v>46021</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16000,7 +16000,7 @@
         <v>45719</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16078,7 +16078,7 @@
         <v>46282</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16151,7 +16151,7 @@
         <v>46282</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16224,7 +16224,7 @@
         <v>46282</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16297,7 +16297,7 @@
         <v>46282</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16370,7 +16370,7 @@
         <v>46282</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16443,7 +16443,7 @@
         <v>46240</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16516,7 +16516,7 @@
         <v>45365</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16589,7 +16589,7 @@
         <v>46283</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16667,7 +16667,7 @@
         <v>46283</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16745,7 +16745,7 @@
         <v>46286</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16823,7 +16823,7 @@
         <v>46286</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16901,7 +16901,7 @@
         <v>46240</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16974,7 +16974,7 @@
         <v>46283</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17052,7 +17052,7 @@
         <v>46283</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17130,7 +17130,7 @@
         <v>45796</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17203,7 +17203,7 @@
         <v>46283</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17281,7 +17281,7 @@
         <v>46036</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17354,7 +17354,7 @@
         <v>45796</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17427,7 +17427,7 @@
         <v>45726</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17500,7 +17500,7 @@
         <v>46044</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17578,7 +17578,7 @@
         <v>46045</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17656,7 +17656,7 @@
         <v>46045</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17734,7 +17734,7 @@
         <v>46055</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17807,7 +17807,7 @@
         <v>45273</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17880,7 +17880,7 @@
         <v>46058</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17953,7 +17953,7 @@
         <v>45239</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18026,7 +18026,7 @@
         <v>46290</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18099,7 +18099,7 @@
         <v>46290</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18172,7 +18172,7 @@
         <v>46062</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18250,7 +18250,7 @@
         <v>45831</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18323,7 +18323,7 @@
         <v>46069</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18396,7 +18396,7 @@
         <v>46069</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18474,7 +18474,7 @@
         <v>46071</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18552,7 +18552,7 @@
         <v>45821</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18630,7 +18630,7 @@
         <v>45831</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18703,7 +18703,7 @@
         <v>45831</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18776,7 +18776,7 @@
         <v>45831</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18849,7 +18849,7 @@
         <v>45831</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18922,7 +18922,7 @@
         <v>46029</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18995,7 +18995,7 @@
         <v>45838</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19073,7 +19073,7 @@
         <v>46099</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19146,7 +19146,7 @@
         <v>46101</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19219,7 +19219,7 @@
         <v>46101</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19292,7 +19292,7 @@
         <v>45790</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19365,7 +19365,7 @@
         <v>45810</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19438,7 +19438,7 @@
         <v>46258</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19511,7 +19511,7 @@
         <v>46097</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19584,7 +19584,7 @@
         <v>46106</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19657,7 +19657,7 @@
         <v>45769</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19730,7 +19730,7 @@
         <v>45831</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19803,7 +19803,7 @@
         <v>44844</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19876,7 +19876,7 @@
         <v>46303</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19949,7 +19949,7 @@
         <v>46303</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20022,7 +20022,7 @@
         <v>46304</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20095,7 +20095,7 @@
         <v>46116</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20168,7 +20168,7 @@
         <v>46304</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20241,7 +20241,7 @@
         <v>46119</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20314,7 +20314,7 @@
         <v>46119</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20387,7 +20387,7 @@
         <v>46121</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20460,7 +20460,7 @@
         <v>46125</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20533,7 +20533,7 @@
         <v>46125</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20606,7 +20606,7 @@
         <v>45965</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20679,7 +20679,7 @@
         <v>45994</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20752,7 +20752,7 @@
         <v>46126</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20825,7 +20825,7 @@
         <v>45647</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20898,7 +20898,7 @@
         <v>45649</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20971,7 +20971,7 @@
         <v>45475</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21044,7 +21044,7 @@
         <v>46308</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21117,7 +21117,7 @@
         <v>45246</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21195,7 +21195,7 @@
         <v>45841</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21268,7 +21268,7 @@
         <v>45218</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21341,7 +21341,7 @@
         <v>45965</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21414,7 +21414,7 @@
         <v>45355</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21487,7 +21487,7 @@
         <v>45871</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21560,7 +21560,7 @@
         <v>45831</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21633,7 +21633,7 @@
         <v>46310</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21706,7 +21706,7 @@
         <v>45831</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21779,7 +21779,7 @@
         <v>45793</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21852,7 +21852,7 @@
         <v>45917</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21925,7 +21925,7 @@
         <v>45558</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21998,7 +21998,7 @@
         <v>44908</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -22071,7 +22071,7 @@
         <v>44908</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22144,7 +22144,7 @@
         <v>44624</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22217,7 +22217,7 @@
         <v>45831</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22290,7 +22290,7 @@
         <v>45510</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22363,7 +22363,7 @@
         <v>45916</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22436,7 +22436,7 @@
         <v>44966</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22509,7 +22509,7 @@
         <v>45355</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22582,7 +22582,7 @@
         <v>46269</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22655,7 +22655,7 @@
         <v>46269</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22728,7 +22728,7 @@
         <v>45099</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22801,7 +22801,7 @@
         <v>46273</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22874,7 +22874,7 @@
         <v>46273</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22947,7 +22947,7 @@
         <v>45616</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -23020,7 +23020,7 @@
         <v>45910</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -23093,7 +23093,7 @@
         <v>46273</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23166,7 +23166,7 @@
         <v>46275</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23239,7 +23239,7 @@
         <v>46314</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23312,7 +23312,7 @@
         <v>46317</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23390,7 +23390,7 @@
         <v>45701</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23463,7 +23463,7 @@
         <v>46146</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23536,7 +23536,7 @@
         <v>46146</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23609,7 +23609,7 @@
         <v>46146</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23682,7 +23682,7 @@
         <v>46146</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23755,7 +23755,7 @@
         <v>46146</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23828,7 +23828,7 @@
         <v>46146</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23901,7 +23901,7 @@
         <v>45000</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -23974,7 +23974,7 @@
         <v>44651</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -24047,7 +24047,7 @@
         <v>46154</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -24125,7 +24125,7 @@
         <v>46153</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24203,7 +24203,7 @@
         <v>44994</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24276,7 +24276,7 @@
         <v>44994</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24349,7 +24349,7 @@
         <v>44994</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24422,7 +24422,7 @@
         <v>45575</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24495,7 +24495,7 @@
         <v>45600</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24573,7 +24573,7 @@
         <v>45273</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24646,7 +24646,7 @@
         <v>45666</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24719,7 +24719,7 @@
         <v>45119</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24797,7 +24797,7 @@
         <v>45664</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24870,7 +24870,7 @@
         <v>44966</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -24943,7 +24943,7 @@
         <v>45575</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -25016,7 +25016,7 @@
         <v>45096</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -25089,7 +25089,7 @@
         <v>45596</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25162,7 +25162,7 @@
         <v>45016</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25240,7 +25240,7 @@
         <v>45634</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25313,7 +25313,7 @@
         <v>45649</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25386,7 +25386,7 @@
         <v>45736</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25464,7 +25464,7 @@
         <v>45666</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25537,7 +25537,7 @@
         <v>44816</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25610,7 +25610,7 @@
         <v>45170</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25683,7 +25683,7 @@
         <v>45692</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25756,7 +25756,7 @@
         <v>44562</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25829,7 +25829,7 @@
         <v>45091</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -25907,7 +25907,7 @@
         <v>44502</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -25980,7 +25980,7 @@
         <v>45707</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -26053,7 +26053,7 @@
         <v>44894</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -26126,7 +26126,7 @@
         <v>44980</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -26199,7 +26199,7 @@
         <v>45334</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -26272,7 +26272,7 @@
         <v>44908</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -26345,7 +26345,7 @@
         <v>44868</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -26423,7 +26423,7 @@
         <v>45264</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -26496,7 +26496,7 @@
         <v>45153</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26569,7 +26569,7 @@
         <v>45272</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26647,7 +26647,7 @@
         <v>45737</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26720,7 +26720,7 @@
         <v>45580</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -26793,7 +26793,7 @@
         <v>45701</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -26866,7 +26866,7 @@
         <v>45090</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -26944,7 +26944,7 @@
         <v>44994</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -27017,7 +27017,7 @@
         <v>45701</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -27090,7 +27090,7 @@
         <v>44572</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -27163,7 +27163,7 @@
         <v>44987</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -27236,7 +27236,7 @@
         <v>44831</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -27309,7 +27309,7 @@
         <v>45587</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -27387,7 +27387,7 @@
         <v>44530</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -27460,7 +27460,7 @@
         <v>45335</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -27533,7 +27533,7 @@
         <v>45398</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -27606,7 +27606,7 @@
         <v>45110</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -27679,7 +27679,7 @@
         <v>45138</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -27752,7 +27752,7 @@
         <v>44504</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -27825,7 +27825,7 @@
         <v>45159</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -27898,7 +27898,7 @@
         <v>44651</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -27971,7 +27971,7 @@
         <v>44503</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -28049,7 +28049,7 @@
         <v>45583</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -28122,7 +28122,7 @@
         <v>45436</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -28195,7 +28195,7 @@
         <v>44606</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -28268,7 +28268,7 @@
         <v>45170</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -28341,7 +28341,7 @@
         <v>45104</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -28414,7 +28414,7 @@
         <v>45054</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -28487,7 +28487,7 @@
         <v>45105</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -28560,7 +28560,7 @@
         <v>45194</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -28633,7 +28633,7 @@
         <v>44655</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -28706,7 +28706,7 @@
         <v>45762</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -28779,7 +28779,7 @@
         <v>44789</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -28857,7 +28857,7 @@
         <v>44576</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -28930,7 +28930,7 @@
         <v>45758</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -29003,7 +29003,7 @@
         <v>45434</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -29076,7 +29076,7 @@
         <v>45701</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -29149,7 +29149,7 @@
         <v>45460</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -29222,7 +29222,7 @@
         <v>44743</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -29295,7 +29295,7 @@
         <v>45159</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -29368,7 +29368,7 @@
         <v>44749</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -29441,7 +29441,7 @@
         <v>45414</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -29514,7 +29514,7 @@
         <v>45714</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -29587,7 +29587,7 @@
         <v>45278</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -29660,7 +29660,7 @@
         <v>44711</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -29738,7 +29738,7 @@
         <v>44670</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -29811,7 +29811,7 @@
         <v>45302</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -29884,7 +29884,7 @@
         <v>45310</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -29957,7 +29957,7 @@
         <v>45231</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -30030,7 +30030,7 @@
         <v>45261</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -30103,7 +30103,7 @@
         <v>45261</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -30176,7 +30176,7 @@
         <v>44939</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -30249,7 +30249,7 @@
         <v>45537</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -30322,7 +30322,7 @@
         <v>45194</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -30395,7 +30395,7 @@
         <v>44538</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -30468,7 +30468,7 @@
         <v>44987</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -30541,7 +30541,7 @@
         <v>45634</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -30614,7 +30614,7 @@
         <v>45671</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -30687,7 +30687,7 @@
         <v>44980</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -30760,7 +30760,7 @@
         <v>45406</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -30833,7 +30833,7 @@
         <v>44965</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -30906,7 +30906,7 @@
         <v>44908</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -30979,7 +30979,7 @@
         <v>45194</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -31052,7 +31052,7 @@
         <v>45335</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -31125,7 +31125,7 @@
         <v>45257</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -31198,7 +31198,7 @@
         <v>44592</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -31271,7 +31271,7 @@
         <v>44585</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -31344,7 +31344,7 @@
         <v>45839</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -31422,7 +31422,7 @@
         <v>45916</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -31500,7 +31500,7 @@
         <v>45964</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -31573,7 +31573,7 @@
         <v>46066</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -31646,7 +31646,7 @@
         <v>46287</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>

--- a/Översikt YDRE.xlsx
+++ b/Översikt YDRE.xlsx
@@ -601,7 +601,7 @@
         <v>44503</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -729,7 +729,7 @@
         <v>45153</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -848,7 +848,7 @@
         <v>44621</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -957,7 +957,7 @@
         <v>46282</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>45378</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1184,7 +1184,7 @@
         <v>45954</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1301,7 +1301,7 @@
         <v>46189</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1408,7 +1408,7 @@
         <v>45198</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1519,7 +1519,7 @@
         <v>45709</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1626,7 +1626,7 @@
         <v>45883</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1738,7 +1738,7 @@
         <v>44509</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1844,7 +1844,7 @@
         <v>44789</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1955,7 +1955,7 @@
         <v>45973</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2066,7 +2066,7 @@
         <v>44732</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2177,7 +2177,7 @@
         <v>45792</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2283,7 +2283,7 @@
         <v>44874</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2389,7 +2389,7 @@
         <v>45251</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2499,7 +2499,7 @@
         <v>45415</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2605,7 +2605,7 @@
         <v>45348</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2711,7 +2711,7 @@
         <v>45611</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2826,7 +2826,7 @@
         <v>45091</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2937,7 +2937,7 @@
         <v>45614</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3048,7 +3048,7 @@
         <v>45846</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3159,7 +3159,7 @@
         <v>44515</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3264,7 +3264,7 @@
         <v>45916</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3369,7 +3369,7 @@
         <v>45922</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3474,7 +3474,7 @@
         <v>45371</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3579,7 +3579,7 @@
         <v>45964</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3689,7 +3689,7 @@
         <v>45965</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3798,7 +3798,7 @@
         <v>46202</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3903,7 +3903,7 @@
         <v>45611</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4013,7 +4013,7 @@
         <v>45561</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4118,7 +4118,7 @@
         <v>46045</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4232,7 +4232,7 @@
         <v>46069</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4337,7 +4337,7 @@
         <v>46069</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4447,7 +4447,7 @@
         <v>45922</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4552,7 +4552,7 @@
         <v>45727</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4657,7 +4657,7 @@
         <v>45192</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4762,7 +4762,7 @@
         <v>45769</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4867,7 +4867,7 @@
         <v>45754</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4972,7 +4972,7 @@
         <v>44858</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5082,7 +5082,7 @@
         <v>45733</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5187,7 +5187,7 @@
         <v>45777</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5292,7 +5292,7 @@
         <v>46075</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5401,7 +5401,7 @@
         <v>44582</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5474,7 +5474,7 @@
         <v>44508</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5547,7 +5547,7 @@
         <v>44693</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5620,7 +5620,7 @@
         <v>44827</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5698,7 +5698,7 @@
         <v>44585</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5771,7 +5771,7 @@
         <v>44502</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5844,7 +5844,7 @@
         <v>44820</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5917,7 +5917,7 @@
         <v>44827</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5995,7 +5995,7 @@
         <v>44503</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6073,7 +6073,7 @@
         <v>44687</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6151,7 +6151,7 @@
         <v>44868</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6224,7 +6224,7 @@
         <v>44879</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6302,7 +6302,7 @@
         <v>44879</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6375,7 +6375,7 @@
         <v>44879</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6448,7 +6448,7 @@
         <v>44789</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6526,7 +6526,7 @@
         <v>44516</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6599,7 +6599,7 @@
         <v>44816</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6672,7 +6672,7 @@
         <v>44538</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6745,7 +6745,7 @@
         <v>44728</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6818,7 +6818,7 @@
         <v>44593</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6896,7 +6896,7 @@
         <v>44698</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6969,7 +6969,7 @@
         <v>44650</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7042,7 +7042,7 @@
         <v>44827</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7120,7 +7120,7 @@
         <v>44743</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7193,7 +7193,7 @@
         <v>44538</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7266,7 +7266,7 @@
         <v>44531</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7339,7 +7339,7 @@
         <v>44953</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7412,7 +7412,7 @@
         <v>44903</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7485,7 +7485,7 @@
         <v>45748</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7558,7 +7558,7 @@
         <v>45889</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7631,7 +7631,7 @@
         <v>45891</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7704,7 +7704,7 @@
         <v>45348</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7777,7 +7777,7 @@
         <v>44600</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7850,7 +7850,7 @@
         <v>45428</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7923,7 +7923,7 @@
         <v>45898</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7996,7 +7996,7 @@
         <v>45414</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8069,7 +8069,7 @@
         <v>44874</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8142,7 +8142,7 @@
         <v>45371</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8215,7 +8215,7 @@
         <v>45909</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8293,7 +8293,7 @@
         <v>45909</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8371,7 +8371,7 @@
         <v>45910</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8444,7 +8444,7 @@
         <v>44501</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8517,7 +8517,7 @@
         <v>45916</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8590,7 +8590,7 @@
         <v>44536</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8663,7 +8663,7 @@
         <v>45916</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8741,7 +8741,7 @@
         <v>45916</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8819,7 +8819,7 @@
         <v>45916</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8897,7 +8897,7 @@
         <v>45922</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8970,7 +8970,7 @@
         <v>45924</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9048,7 +9048,7 @@
         <v>46038</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9126,7 +9126,7 @@
         <v>45096</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9199,7 +9199,7 @@
         <v>44953</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9272,7 +9272,7 @@
         <v>45419</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9345,7 +9345,7 @@
         <v>44980</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9418,7 +9418,7 @@
         <v>45931</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9491,7 +9491,7 @@
         <v>45931</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9564,7 +9564,7 @@
         <v>45965</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9642,7 +9642,7 @@
         <v>46171</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9720,7 +9720,7 @@
         <v>45932</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9793,7 +9793,7 @@
         <v>45940</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9871,7 +9871,7 @@
         <v>45938</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9949,7 +9949,7 @@
         <v>45940</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10027,7 +10027,7 @@
         <v>45145</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10100,7 +10100,7 @@
         <v>44796</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10173,7 +10173,7 @@
         <v>45216</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10246,7 +10246,7 @@
         <v>45216</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10319,7 +10319,7 @@
         <v>46177</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10397,7 +10397,7 @@
         <v>45077</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10470,7 +10470,7 @@
         <v>45665</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10543,7 +10543,7 @@
         <v>45365</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10616,7 +10616,7 @@
         <v>46183</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10694,7 +10694,7 @@
         <v>45954</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10772,7 +10772,7 @@
         <v>45954</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10850,7 +10850,7 @@
         <v>45208</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10923,7 +10923,7 @@
         <v>45595</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10996,7 +10996,7 @@
         <v>45964</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11074,7 +11074,7 @@
         <v>45964</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11152,7 +11152,7 @@
         <v>45964</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11230,7 +11230,7 @@
         <v>45965</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11308,7 +11308,7 @@
         <v>45965</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11386,7 +11386,7 @@
         <v>45965</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11459,7 +11459,7 @@
         <v>46191</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11532,7 +11532,7 @@
         <v>45698</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11605,7 +11605,7 @@
         <v>45965</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11678,7 +11678,7 @@
         <v>46190</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11751,7 +11751,7 @@
         <v>45965</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11829,7 +11829,7 @@
         <v>45965</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11907,7 +11907,7 @@
         <v>45965</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11985,7 +11985,7 @@
         <v>45965</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12058,7 +12058,7 @@
         <v>45355</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12131,7 +12131,7 @@
         <v>45664</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12204,7 +12204,7 @@
         <v>45596</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12277,7 +12277,7 @@
         <v>45085</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12350,7 +12350,7 @@
         <v>44916</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12423,7 +12423,7 @@
         <v>45460</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12496,7 +12496,7 @@
         <v>46202</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12569,7 +12569,7 @@
         <v>45414</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12642,7 +12642,7 @@
         <v>45666</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12715,7 +12715,7 @@
         <v>44994</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12788,7 +12788,7 @@
         <v>44635</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12861,7 +12861,7 @@
         <v>46202</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12934,7 +12934,7 @@
         <v>46202</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13007,7 +13007,7 @@
         <v>46202</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13080,7 +13080,7 @@
         <v>46202</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13153,7 +13153,7 @@
         <v>45665</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13226,7 +13226,7 @@
         <v>45110</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13299,7 +13299,7 @@
         <v>45755</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13372,7 +13372,7 @@
         <v>45218</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13445,7 +13445,7 @@
         <v>45236</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13518,7 +13518,7 @@
         <v>45714</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13591,7 +13591,7 @@
         <v>45597</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13664,7 +13664,7 @@
         <v>45054</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13737,7 +13737,7 @@
         <v>45170</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13810,7 +13810,7 @@
         <v>45677</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13883,7 +13883,7 @@
         <v>45707</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13956,7 +13956,7 @@
         <v>45994</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14029,7 +14029,7 @@
         <v>45994</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14102,7 +14102,7 @@
         <v>45432</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14175,7 +14175,7 @@
         <v>45638</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14248,7 +14248,7 @@
         <v>45414</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14321,7 +14321,7 @@
         <v>45414</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14394,7 +14394,7 @@
         <v>45474</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14467,7 +14467,7 @@
         <v>45110</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14540,7 +14540,7 @@
         <v>45831</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14613,7 +14613,7 @@
         <v>45468</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14686,7 +14686,7 @@
         <v>45492</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14759,7 +14759,7 @@
         <v>46006</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14832,7 +14832,7 @@
         <v>46006</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14905,7 +14905,7 @@
         <v>46007</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14978,7 +14978,7 @@
         <v>46007</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15051,7 +15051,7 @@
         <v>46007</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15124,7 +15124,7 @@
         <v>45666</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15197,7 +15197,7 @@
         <v>46007</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15270,7 +15270,7 @@
         <v>46010</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15343,7 +15343,7 @@
         <v>46280</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15416,7 +15416,7 @@
         <v>46013</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15489,7 +15489,7 @@
         <v>46013</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15562,7 +15562,7 @@
         <v>46013</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15635,7 +15635,7 @@
         <v>45475</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15708,7 +15708,7 @@
         <v>45714</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15781,7 +15781,7 @@
         <v>46282</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15854,7 +15854,7 @@
         <v>45544</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15927,7 +15927,7 @@
         <v>46021</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16000,7 +16000,7 @@
         <v>45719</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16078,7 +16078,7 @@
         <v>46282</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16151,7 +16151,7 @@
         <v>46282</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16224,7 +16224,7 @@
         <v>46282</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16297,7 +16297,7 @@
         <v>46282</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16370,7 +16370,7 @@
         <v>46282</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16443,7 +16443,7 @@
         <v>46240</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16516,7 +16516,7 @@
         <v>45365</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16589,7 +16589,7 @@
         <v>46283</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16667,7 +16667,7 @@
         <v>46283</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16745,7 +16745,7 @@
         <v>46286</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16823,7 +16823,7 @@
         <v>46286</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16901,7 +16901,7 @@
         <v>46240</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16974,7 +16974,7 @@
         <v>46283</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17052,7 +17052,7 @@
         <v>46283</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17130,7 +17130,7 @@
         <v>45796</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17203,7 +17203,7 @@
         <v>46283</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17281,7 +17281,7 @@
         <v>46036</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17354,7 +17354,7 @@
         <v>45796</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17427,7 +17427,7 @@
         <v>45726</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17500,7 +17500,7 @@
         <v>46044</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17578,7 +17578,7 @@
         <v>46045</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17656,7 +17656,7 @@
         <v>46045</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17734,7 +17734,7 @@
         <v>46055</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17807,7 +17807,7 @@
         <v>45273</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17880,7 +17880,7 @@
         <v>46058</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17953,7 +17953,7 @@
         <v>45239</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18026,7 +18026,7 @@
         <v>46290</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18099,7 +18099,7 @@
         <v>46290</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18172,7 +18172,7 @@
         <v>46062</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18250,7 +18250,7 @@
         <v>45831</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18323,7 +18323,7 @@
         <v>46069</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18396,7 +18396,7 @@
         <v>46069</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18474,7 +18474,7 @@
         <v>46071</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18552,7 +18552,7 @@
         <v>45821</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18630,7 +18630,7 @@
         <v>45831</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18703,7 +18703,7 @@
         <v>45831</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18776,7 +18776,7 @@
         <v>45831</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18849,7 +18849,7 @@
         <v>45831</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18922,7 +18922,7 @@
         <v>46029</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18995,7 +18995,7 @@
         <v>45838</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19073,7 +19073,7 @@
         <v>46099</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19146,7 +19146,7 @@
         <v>46101</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19219,7 +19219,7 @@
         <v>46101</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19292,7 +19292,7 @@
         <v>45790</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19365,7 +19365,7 @@
         <v>45810</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19438,7 +19438,7 @@
         <v>46258</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19511,7 +19511,7 @@
         <v>46097</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19584,7 +19584,7 @@
         <v>46106</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19657,7 +19657,7 @@
         <v>45769</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19730,7 +19730,7 @@
         <v>45831</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19803,7 +19803,7 @@
         <v>44844</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19876,7 +19876,7 @@
         <v>46303</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19949,7 +19949,7 @@
         <v>46303</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20022,7 +20022,7 @@
         <v>46304</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20095,7 +20095,7 @@
         <v>46116</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20168,7 +20168,7 @@
         <v>46304</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20241,7 +20241,7 @@
         <v>46119</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20314,7 +20314,7 @@
         <v>46119</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20387,7 +20387,7 @@
         <v>46121</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20460,7 +20460,7 @@
         <v>46125</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20533,7 +20533,7 @@
         <v>46125</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20606,7 +20606,7 @@
         <v>45965</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20679,7 +20679,7 @@
         <v>45994</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20752,7 +20752,7 @@
         <v>46126</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20825,7 +20825,7 @@
         <v>45647</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20898,7 +20898,7 @@
         <v>45649</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20971,7 +20971,7 @@
         <v>45475</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21044,7 +21044,7 @@
         <v>46308</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21117,7 +21117,7 @@
         <v>45246</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21195,7 +21195,7 @@
         <v>45841</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21268,7 +21268,7 @@
         <v>45218</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21341,7 +21341,7 @@
         <v>45965</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21414,7 +21414,7 @@
         <v>45355</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21487,7 +21487,7 @@
         <v>45871</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21560,7 +21560,7 @@
         <v>45831</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21633,7 +21633,7 @@
         <v>46310</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21706,7 +21706,7 @@
         <v>45831</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21779,7 +21779,7 @@
         <v>45793</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21852,7 +21852,7 @@
         <v>45917</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21925,7 +21925,7 @@
         <v>45558</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21998,7 +21998,7 @@
         <v>44908</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -22071,7 +22071,7 @@
         <v>44908</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22144,7 +22144,7 @@
         <v>44624</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22217,7 +22217,7 @@
         <v>45831</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22290,7 +22290,7 @@
         <v>45510</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22363,7 +22363,7 @@
         <v>45916</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22436,7 +22436,7 @@
         <v>44966</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22509,7 +22509,7 @@
         <v>45355</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22582,7 +22582,7 @@
         <v>46269</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22655,7 +22655,7 @@
         <v>46269</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22728,7 +22728,7 @@
         <v>45099</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22801,7 +22801,7 @@
         <v>46273</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22874,7 +22874,7 @@
         <v>46273</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22947,7 +22947,7 @@
         <v>45616</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -23020,7 +23020,7 @@
         <v>45910</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -23093,7 +23093,7 @@
         <v>46273</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23166,7 +23166,7 @@
         <v>46275</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23239,7 +23239,7 @@
         <v>46314</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23312,7 +23312,7 @@
         <v>46317</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23390,7 +23390,7 @@
         <v>45701</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23463,7 +23463,7 @@
         <v>46146</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23536,7 +23536,7 @@
         <v>46146</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23609,7 +23609,7 @@
         <v>46146</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23682,7 +23682,7 @@
         <v>46146</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23755,7 +23755,7 @@
         <v>46146</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23828,7 +23828,7 @@
         <v>46146</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23901,7 +23901,7 @@
         <v>45000</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -23974,7 +23974,7 @@
         <v>44651</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -24047,7 +24047,7 @@
         <v>46154</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -24125,7 +24125,7 @@
         <v>46153</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24203,7 +24203,7 @@
         <v>44994</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24276,7 +24276,7 @@
         <v>44994</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24349,7 +24349,7 @@
         <v>44994</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24422,7 +24422,7 @@
         <v>45575</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24495,7 +24495,7 @@
         <v>45600</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24573,7 +24573,7 @@
         <v>45273</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24646,7 +24646,7 @@
         <v>45666</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24719,7 +24719,7 @@
         <v>45119</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24797,7 +24797,7 @@
         <v>45664</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24870,7 +24870,7 @@
         <v>44966</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -24943,7 +24943,7 @@
         <v>45575</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -25016,7 +25016,7 @@
         <v>45096</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -25089,7 +25089,7 @@
         <v>45596</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25162,7 +25162,7 @@
         <v>45016</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25240,7 +25240,7 @@
         <v>45634</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25313,7 +25313,7 @@
         <v>45649</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25386,7 +25386,7 @@
         <v>45736</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25464,7 +25464,7 @@
         <v>45666</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25537,7 +25537,7 @@
         <v>44816</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25610,7 +25610,7 @@
         <v>45170</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25683,7 +25683,7 @@
         <v>45692</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25756,7 +25756,7 @@
         <v>44562</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25829,7 +25829,7 @@
         <v>45091</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -25907,7 +25907,7 @@
         <v>44502</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -25980,7 +25980,7 @@
         <v>45707</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -26053,7 +26053,7 @@
         <v>44894</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -26126,7 +26126,7 @@
         <v>44980</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -26199,7 +26199,7 @@
         <v>45334</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -26272,7 +26272,7 @@
         <v>44908</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -26345,7 +26345,7 @@
         <v>44868</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -26423,7 +26423,7 @@
         <v>45264</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -26496,7 +26496,7 @@
         <v>45153</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26569,7 +26569,7 @@
         <v>45272</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26647,7 +26647,7 @@
         <v>45737</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26720,7 +26720,7 @@
         <v>45580</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -26793,7 +26793,7 @@
         <v>45701</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -26866,7 +26866,7 @@
         <v>45090</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -26944,7 +26944,7 @@
         <v>44994</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -27017,7 +27017,7 @@
         <v>45701</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -27090,7 +27090,7 @@
         <v>44572</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -27163,7 +27163,7 @@
         <v>44987</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -27236,7 +27236,7 @@
         <v>44831</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -27309,7 +27309,7 @@
         <v>45587</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -27387,7 +27387,7 @@
         <v>44530</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -27460,7 +27460,7 @@
         <v>45335</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -27533,7 +27533,7 @@
         <v>45398</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -27606,7 +27606,7 @@
         <v>45110</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -27679,7 +27679,7 @@
         <v>45138</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -27752,7 +27752,7 @@
         <v>44504</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -27825,7 +27825,7 @@
         <v>45159</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -27898,7 +27898,7 @@
         <v>44651</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -27971,7 +27971,7 @@
         <v>44503</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -28049,7 +28049,7 @@
         <v>45583</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -28122,7 +28122,7 @@
         <v>45436</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -28195,7 +28195,7 @@
         <v>44606</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -28268,7 +28268,7 @@
         <v>45170</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -28341,7 +28341,7 @@
         <v>45104</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -28414,7 +28414,7 @@
         <v>45054</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -28487,7 +28487,7 @@
         <v>45105</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -28560,7 +28560,7 @@
         <v>45194</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -28633,7 +28633,7 @@
         <v>44655</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -28706,7 +28706,7 @@
         <v>45762</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -28779,7 +28779,7 @@
         <v>44789</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -28857,7 +28857,7 @@
         <v>44576</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -28930,7 +28930,7 @@
         <v>45758</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -29003,7 +29003,7 @@
         <v>45434</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -29076,7 +29076,7 @@
         <v>45701</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -29149,7 +29149,7 @@
         <v>45460</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -29222,7 +29222,7 @@
         <v>44743</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -29295,7 +29295,7 @@
         <v>45159</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -29368,7 +29368,7 @@
         <v>44749</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -29441,7 +29441,7 @@
         <v>45414</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -29514,7 +29514,7 @@
         <v>45714</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -29587,7 +29587,7 @@
         <v>45278</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -29660,7 +29660,7 @@
         <v>44711</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -29738,7 +29738,7 @@
         <v>44670</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -29811,7 +29811,7 @@
         <v>45302</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -29884,7 +29884,7 @@
         <v>45310</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -29957,7 +29957,7 @@
         <v>45231</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -30030,7 +30030,7 @@
         <v>45261</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -30103,7 +30103,7 @@
         <v>45261</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -30176,7 +30176,7 @@
         <v>44939</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -30249,7 +30249,7 @@
         <v>45537</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -30322,7 +30322,7 @@
         <v>45194</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -30395,7 +30395,7 @@
         <v>44538</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -30468,7 +30468,7 @@
         <v>44987</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -30541,7 +30541,7 @@
         <v>45634</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -30614,7 +30614,7 @@
         <v>45671</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -30687,7 +30687,7 @@
         <v>44980</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -30760,7 +30760,7 @@
         <v>45406</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -30833,7 +30833,7 @@
         <v>44965</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -30906,7 +30906,7 @@
         <v>44908</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -30979,7 +30979,7 @@
         <v>45194</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -31052,7 +31052,7 @@
         <v>45335</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -31125,7 +31125,7 @@
         <v>45257</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -31198,7 +31198,7 @@
         <v>44592</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -31271,7 +31271,7 @@
         <v>44585</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -31344,7 +31344,7 @@
         <v>45839</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -31422,7 +31422,7 @@
         <v>45916</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -31500,7 +31500,7 @@
         <v>45964</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -31573,7 +31573,7 @@
         <v>46066</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -31646,7 +31646,7 @@
         <v>46287</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
